--- a/analytics-mvp/exports/orders_analytics_2026-07.xlsx
+++ b/analytics-mvp/exports/orders_analytics_2026-07.xlsx
@@ -668,10 +668,10 @@
         <v>7203</v>
       </c>
       <c r="N3" t="n">
-        <v>64925</v>
+        <v>64905</v>
       </c>
       <c r="O3" t="n">
-        <v>37975</v>
+        <v>37995</v>
       </c>
       <c r="P3" t="n">
         <v>1000</v>
@@ -683,19 +683,19 @@
         <v>15141</v>
       </c>
       <c r="S3" t="n">
-        <v>25533</v>
+        <v>25553</v>
       </c>
       <c r="T3" t="n">
-        <v>11392</v>
+        <v>11398</v>
       </c>
       <c r="U3" t="n">
-        <v>5696</v>
+        <v>5699</v>
       </c>
       <c r="V3" t="n">
-        <v>8444</v>
+        <v>8455</v>
       </c>
       <c r="W3" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="X3" t="inlineStr"/>
     </row>
@@ -740,16 +740,16 @@
         <v>2601</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
         <v>7063</v>
       </c>
       <c r="N4" t="n">
-        <v>64834</v>
+        <v>64844</v>
       </c>
       <c r="O4" t="n">
-        <v>36066</v>
+        <v>36056</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -761,16 +761,16 @@
         <v>13231</v>
       </c>
       <c r="S4" t="n">
-        <v>22835</v>
+        <v>22825</v>
       </c>
       <c r="T4" t="n">
-        <v>10820</v>
+        <v>10817</v>
       </c>
       <c r="U4" t="n">
-        <v>5410</v>
+        <v>5408</v>
       </c>
       <c r="V4" t="n">
-        <v>6605</v>
+        <v>6600</v>
       </c>
       <c r="W4" t="n">
         <v>18.3</v>
@@ -824,10 +824,10 @@
         <v>6923</v>
       </c>
       <c r="N5" t="n">
-        <v>62515</v>
+        <v>62495</v>
       </c>
       <c r="O5" t="n">
-        <v>36385</v>
+        <v>36405</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -839,16 +839,16 @@
         <v>13231</v>
       </c>
       <c r="S5" t="n">
-        <v>25753</v>
+        <v>25773</v>
       </c>
       <c r="T5" t="n">
-        <v>10916</v>
+        <v>10922</v>
       </c>
       <c r="U5" t="n">
-        <v>5458</v>
+        <v>5461</v>
       </c>
       <c r="V5" t="n">
-        <v>9380</v>
+        <v>9391</v>
       </c>
       <c r="W5" t="n">
         <v>25.8</v>
@@ -900,16 +900,16 @@
         <v>1896</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
         <v>5772</v>
       </c>
       <c r="N6" t="n">
-        <v>51161</v>
+        <v>51169</v>
       </c>
       <c r="O6" t="n">
-        <v>31292</v>
+        <v>31284</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -921,16 +921,16 @@
         <v>6945</v>
       </c>
       <c r="S6" t="n">
-        <v>24347</v>
+        <v>24339</v>
       </c>
       <c r="T6" t="n">
-        <v>9388</v>
+        <v>9385</v>
       </c>
       <c r="U6" t="n">
-        <v>4694</v>
+        <v>4693</v>
       </c>
       <c r="V6" t="n">
-        <v>10266</v>
+        <v>10261</v>
       </c>
       <c r="W6" t="n">
         <v>32.8</v>
@@ -1140,10 +1140,10 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>46221</v>
+        <v>46201</v>
       </c>
       <c r="O9" t="n">
-        <v>36004</v>
+        <v>36024</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1155,16 +1155,16 @@
         <v>8789</v>
       </c>
       <c r="S9" t="n">
-        <v>29914</v>
+        <v>29934</v>
       </c>
       <c r="T9" t="n">
-        <v>10801</v>
+        <v>10807</v>
       </c>
       <c r="U9" t="n">
-        <v>5401</v>
+        <v>5404</v>
       </c>
       <c r="V9" t="n">
-        <v>13712</v>
+        <v>13723</v>
       </c>
       <c r="W9" t="n">
         <v>38.1</v>
@@ -1222,10 +1222,10 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>43881</v>
+        <v>43861</v>
       </c>
       <c r="O10" t="n">
-        <v>37019</v>
+        <v>37039</v>
       </c>
       <c r="P10" t="n">
         <v>4347</v>
@@ -1237,16 +1237,16 @@
         <v>10715</v>
       </c>
       <c r="S10" t="n">
-        <v>26257</v>
+        <v>26277</v>
       </c>
       <c r="T10" t="n">
-        <v>11106</v>
+        <v>11112</v>
       </c>
       <c r="U10" t="n">
-        <v>5553</v>
+        <v>5556</v>
       </c>
       <c r="V10" t="n">
-        <v>9598</v>
+        <v>9609</v>
       </c>
       <c r="W10" t="n">
         <v>25.9</v>
@@ -1304,10 +1304,10 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>42587</v>
+        <v>42567</v>
       </c>
       <c r="O11" t="n">
-        <v>33313</v>
+        <v>33333</v>
       </c>
       <c r="P11" t="n">
         <v>4112</v>
@@ -1319,16 +1319,16 @@
         <v>11273</v>
       </c>
       <c r="S11" t="n">
-        <v>17928</v>
+        <v>17948</v>
       </c>
       <c r="T11" t="n">
-        <v>9994</v>
+        <v>10000</v>
       </c>
       <c r="U11" t="n">
-        <v>4997</v>
+        <v>5000</v>
       </c>
       <c r="V11" t="n">
-        <v>2937</v>
+        <v>2948</v>
       </c>
       <c r="W11" t="n">
         <v>8.800000000000001</v>
@@ -1464,10 +1464,10 @@
         <v>6651</v>
       </c>
       <c r="N13" t="n">
-        <v>47814</v>
+        <v>47794</v>
       </c>
       <c r="O13" t="n">
-        <v>26086</v>
+        <v>26106</v>
       </c>
       <c r="P13" t="n">
         <v>3251</v>
@@ -1479,19 +1479,19 @@
         <v>11827</v>
       </c>
       <c r="S13" t="n">
-        <v>13308</v>
+        <v>13328</v>
       </c>
       <c r="T13" t="n">
-        <v>7826</v>
+        <v>7832</v>
       </c>
       <c r="U13" t="n">
-        <v>3913</v>
+        <v>3916</v>
       </c>
       <c r="V13" t="n">
-        <v>1569</v>
+        <v>1580</v>
       </c>
       <c r="W13" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -1700,16 +1700,16 @@
         <v>1850</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M16" t="n">
         <v>4779</v>
       </c>
       <c r="N16" t="n">
-        <v>43667</v>
+        <v>43677</v>
       </c>
       <c r="O16" t="n">
-        <v>24609</v>
+        <v>24599</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1721,16 +1721,16 @@
         <v>8864</v>
       </c>
       <c r="S16" t="n">
-        <v>15745</v>
+        <v>15735</v>
       </c>
       <c r="T16" t="n">
-        <v>7383</v>
+        <v>7380</v>
       </c>
       <c r="U16" t="n">
-        <v>3691</v>
+        <v>3690</v>
       </c>
       <c r="V16" t="n">
-        <v>4671</v>
+        <v>4665</v>
       </c>
       <c r="W16" t="n">
         <v>19</v>
@@ -1934,16 +1934,16 @@
         <v>1447</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M19" t="n">
         <v>4403</v>
       </c>
       <c r="N19" t="n">
-        <v>38815</v>
+        <v>38824</v>
       </c>
       <c r="O19" t="n">
-        <v>24085</v>
+        <v>24076</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -1955,16 +1955,16 @@
         <v>8528</v>
       </c>
       <c r="S19" t="n">
-        <v>15557</v>
+        <v>15548</v>
       </c>
       <c r="T19" t="n">
-        <v>7226</v>
+        <v>7223</v>
       </c>
       <c r="U19" t="n">
-        <v>3613</v>
+        <v>3611</v>
       </c>
       <c r="V19" t="n">
-        <v>4719</v>
+        <v>4714</v>
       </c>
       <c r="W19" t="n">
         <v>19.6</v>
@@ -2012,16 +2012,16 @@
         <v>1427</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>35677</v>
+        <v>35687</v>
       </c>
       <c r="O20" t="n">
-        <v>26351</v>
+        <v>26341</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2033,16 +2033,16 @@
         <v>7673</v>
       </c>
       <c r="S20" t="n">
-        <v>18678</v>
+        <v>18668</v>
       </c>
       <c r="T20" t="n">
-        <v>7905</v>
+        <v>7902</v>
       </c>
       <c r="U20" t="n">
-        <v>3953</v>
+        <v>3951</v>
       </c>
       <c r="V20" t="n">
-        <v>6820</v>
+        <v>6815</v>
       </c>
       <c r="W20" t="n">
         <v>25.9</v>
@@ -2096,10 +2096,10 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>34251</v>
+        <v>34231</v>
       </c>
       <c r="O21" t="n">
-        <v>27649</v>
+        <v>27669</v>
       </c>
       <c r="P21" t="n">
         <v>1000</v>
@@ -2111,19 +2111,19 @@
         <v>8774</v>
       </c>
       <c r="S21" t="n">
-        <v>17875</v>
+        <v>17895</v>
       </c>
       <c r="T21" t="n">
-        <v>8295</v>
+        <v>8301</v>
       </c>
       <c r="U21" t="n">
-        <v>4147</v>
+        <v>4150</v>
       </c>
       <c r="V21" t="n">
-        <v>5433</v>
+        <v>5444</v>
       </c>
       <c r="W21" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -2172,16 +2172,16 @@
         <v>1704</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>34109</v>
+        <v>34117</v>
       </c>
       <c r="O22" t="n">
-        <v>27791</v>
+        <v>27783</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2193,16 +2193,16 @@
         <v>7835</v>
       </c>
       <c r="S22" t="n">
-        <v>19956</v>
+        <v>19948</v>
       </c>
       <c r="T22" t="n">
-        <v>8337</v>
+        <v>8335</v>
       </c>
       <c r="U22" t="n">
-        <v>4169</v>
+        <v>4167</v>
       </c>
       <c r="V22" t="n">
-        <v>7450</v>
+        <v>7446</v>
       </c>
       <c r="W22" t="n">
         <v>26.8</v>
@@ -2328,16 +2328,16 @@
         <v>1410</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M24" t="n">
-        <v>24640</v>
+        <v>24599</v>
       </c>
       <c r="N24" t="n">
-        <v>61756</v>
+        <v>61722</v>
       </c>
       <c r="O24" t="n">
-        <v>-442</v>
+        <v>-408</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2349,16 +2349,16 @@
         <v>7673</v>
       </c>
       <c r="S24" t="n">
-        <v>-8115</v>
+        <v>-8081</v>
       </c>
       <c r="T24" t="n">
-        <v>-133</v>
+        <v>-122</v>
       </c>
       <c r="U24" t="n">
-        <v>-66</v>
+        <v>-61</v>
       </c>
       <c r="V24" t="n">
-        <v>-7916</v>
+        <v>-7897</v>
       </c>
       <c r="X24" t="inlineStr"/>
     </row>
@@ -2403,16 +2403,16 @@
         <v>1410</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M25" t="n">
-        <v>24641</v>
+        <v>24599</v>
       </c>
       <c r="N25" t="n">
-        <v>61144</v>
+        <v>61110</v>
       </c>
       <c r="O25" t="n">
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2424,19 +2424,19 @@
         <v>7673</v>
       </c>
       <c r="S25" t="n">
-        <v>-7503</v>
+        <v>-7469</v>
       </c>
       <c r="T25" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="U25" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="V25" t="n">
-        <v>-7580</v>
+        <v>-7561</v>
       </c>
       <c r="W25" t="n">
-        <v>-4458.5</v>
+        <v>-3706.3</v>
       </c>
       <c r="X25" t="inlineStr"/>
     </row>
@@ -2481,16 +2481,16 @@
         <v>1410</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M26" t="n">
         <v>4292</v>
       </c>
       <c r="N26" t="n">
-        <v>37634</v>
+        <v>37645</v>
       </c>
       <c r="O26" t="n">
-        <v>23680</v>
+        <v>23669</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2502,16 +2502,16 @@
         <v>7673</v>
       </c>
       <c r="S26" t="n">
-        <v>16007</v>
+        <v>15996</v>
       </c>
       <c r="T26" t="n">
-        <v>7104</v>
+        <v>7101</v>
       </c>
       <c r="U26" t="n">
-        <v>3552</v>
+        <v>3550</v>
       </c>
       <c r="V26" t="n">
-        <v>5351</v>
+        <v>5345</v>
       </c>
       <c r="W26" t="n">
         <v>22.6</v>
@@ -2559,16 +2559,16 @@
         <v>2586</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M27" t="n">
         <v>4209</v>
       </c>
       <c r="N27" t="n">
-        <v>41224</v>
+        <v>41234</v>
       </c>
       <c r="O27" t="n">
-        <v>18909</v>
+        <v>18899</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2580,16 +2580,16 @@
         <v>7673</v>
       </c>
       <c r="S27" t="n">
-        <v>11236</v>
+        <v>11226</v>
       </c>
       <c r="T27" t="n">
-        <v>5673</v>
+        <v>5670</v>
       </c>
       <c r="U27" t="n">
-        <v>2836</v>
+        <v>2835</v>
       </c>
       <c r="V27" t="n">
-        <v>2727</v>
+        <v>2721</v>
       </c>
       <c r="W27" t="n">
         <v>14.4</v>
@@ -2643,10 +2643,10 @@
         <v>5391</v>
       </c>
       <c r="N28" t="n">
-        <v>38845</v>
+        <v>38825</v>
       </c>
       <c r="O28" t="n">
-        <v>21055</v>
+        <v>21075</v>
       </c>
       <c r="P28" t="n">
         <v>3986</v>
@@ -2658,19 +2658,19 @@
         <v>9241</v>
       </c>
       <c r="S28" t="n">
-        <v>10828</v>
+        <v>10848</v>
       </c>
       <c r="T28" t="n">
-        <v>6316</v>
+        <v>6322</v>
       </c>
       <c r="U28" t="n">
-        <v>3158</v>
+        <v>3161</v>
       </c>
       <c r="V28" t="n">
-        <v>1353</v>
+        <v>1364</v>
       </c>
       <c r="W28" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -2797,16 +2797,16 @@
         <v>1355</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M30" t="n">
-        <v>25649</v>
+        <v>25608</v>
       </c>
       <c r="N30" t="n">
-        <v>59087</v>
+        <v>59054</v>
       </c>
       <c r="O30" t="n">
-        <v>-187</v>
+        <v>-154</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -2818,16 +2818,16 @@
         <v>7673</v>
       </c>
       <c r="S30" t="n">
-        <v>-7860</v>
+        <v>-7827</v>
       </c>
       <c r="T30" t="n">
-        <v>-56</v>
+        <v>-46</v>
       </c>
       <c r="U30" t="n">
-        <v>-28</v>
+        <v>-23</v>
       </c>
       <c r="V30" t="n">
-        <v>-7776</v>
+        <v>-7758</v>
       </c>
       <c r="X30" t="inlineStr"/>
     </row>
@@ -2872,16 +2872,16 @@
         <v>1349</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M31" t="n">
         <v>8084</v>
       </c>
       <c r="N31" t="n">
-        <v>41742</v>
+        <v>41749</v>
       </c>
       <c r="O31" t="n">
-        <v>16915</v>
+        <v>16908</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -2893,16 +2893,16 @@
         <v>8528</v>
       </c>
       <c r="S31" t="n">
-        <v>8387</v>
+        <v>8380</v>
       </c>
       <c r="T31" t="n">
-        <v>5074</v>
+        <v>5072</v>
       </c>
       <c r="U31" t="n">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="V31" t="n">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="W31" t="n">
         <v>4.6</v>
@@ -2950,16 +2950,16 @@
         <v>1349</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M32" t="n">
         <v>8086</v>
       </c>
       <c r="N32" t="n">
-        <v>42357</v>
+        <v>42365</v>
       </c>
       <c r="O32" t="n">
-        <v>16300</v>
+        <v>16292</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -2971,16 +2971,16 @@
         <v>8528</v>
       </c>
       <c r="S32" t="n">
-        <v>7772</v>
+        <v>7764</v>
       </c>
       <c r="T32" t="n">
-        <v>4890</v>
+        <v>4888</v>
       </c>
       <c r="U32" t="n">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="V32" t="n">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="W32" t="n">
         <v>2.7</v>
@@ -3028,16 +3028,16 @@
         <v>1332</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2777</v>
       </c>
       <c r="M33" t="n">
         <v>7641</v>
       </c>
       <c r="N33" t="n">
-        <v>42802</v>
+        <v>42782</v>
       </c>
       <c r="O33" t="n">
-        <v>15098</v>
+        <v>15118</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -3049,16 +3049,16 @@
         <v>8295</v>
       </c>
       <c r="S33" t="n">
-        <v>7316</v>
+        <v>7336</v>
       </c>
       <c r="T33" t="n">
-        <v>4529</v>
+        <v>4535</v>
       </c>
       <c r="U33" t="n">
-        <v>2265</v>
+        <v>2268</v>
       </c>
       <c r="V33" t="n">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="W33" t="n">
         <v>3.5</v>
@@ -3110,16 +3110,16 @@
         <v>1315</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>4663</v>
       </c>
       <c r="M34" t="n">
         <v>6431</v>
       </c>
       <c r="N34" t="n">
-        <v>43075</v>
+        <v>43055</v>
       </c>
       <c r="O34" t="n">
-        <v>14096</v>
+        <v>14116</v>
       </c>
       <c r="P34" t="n">
         <v>4076</v>
@@ -3131,19 +3131,19 @@
         <v>8295</v>
       </c>
       <c r="S34" t="n">
-        <v>2559</v>
+        <v>2579</v>
       </c>
       <c r="T34" t="n">
-        <v>4229</v>
+        <v>4235</v>
       </c>
       <c r="U34" t="n">
-        <v>2114</v>
+        <v>2117</v>
       </c>
       <c r="V34" t="n">
-        <v>-3784</v>
+        <v>-3773</v>
       </c>
       <c r="W34" t="n">
-        <v>-26.8</v>
+        <v>-26.7</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -3198,10 +3198,10 @@
         <v>2430</v>
       </c>
       <c r="N35" t="n">
-        <v>34132</v>
+        <v>34112</v>
       </c>
       <c r="O35" t="n">
-        <v>22534</v>
+        <v>22554</v>
       </c>
       <c r="P35" t="n">
         <v>3687</v>
@@ -3213,16 +3213,16 @@
         <v>8295</v>
       </c>
       <c r="S35" t="n">
-        <v>15051</v>
+        <v>15071</v>
       </c>
       <c r="T35" t="n">
-        <v>6760</v>
+        <v>6766</v>
       </c>
       <c r="U35" t="n">
-        <v>3380</v>
+        <v>3383</v>
       </c>
       <c r="V35" t="n">
-        <v>4911</v>
+        <v>4922</v>
       </c>
       <c r="W35" t="n">
         <v>21.8</v>
@@ -3280,10 +3280,10 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>31422</v>
+        <v>31402</v>
       </c>
       <c r="O36" t="n">
-        <v>24478</v>
+        <v>24498</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -3295,16 +3295,16 @@
         <v>6616</v>
       </c>
       <c r="S36" t="n">
-        <v>20761</v>
+        <v>20781</v>
       </c>
       <c r="T36" t="n">
-        <v>7343</v>
+        <v>7349</v>
       </c>
       <c r="U36" t="n">
-        <v>3672</v>
+        <v>3675</v>
       </c>
       <c r="V36" t="n">
-        <v>9746</v>
+        <v>9757</v>
       </c>
       <c r="W36" t="n">
         <v>39.8</v>
@@ -3746,16 +3746,16 @@
         <v>1250</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>31862</v>
+        <v>31870</v>
       </c>
       <c r="O42" t="n">
-        <v>22465</v>
+        <v>22457</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
@@ -3767,16 +3767,16 @@
         <v>8528</v>
       </c>
       <c r="S42" t="n">
-        <v>13937</v>
+        <v>13929</v>
       </c>
       <c r="T42" t="n">
-        <v>6740</v>
+        <v>6737</v>
       </c>
       <c r="U42" t="n">
-        <v>3370</v>
+        <v>3369</v>
       </c>
       <c r="V42" t="n">
-        <v>3828</v>
+        <v>3823</v>
       </c>
       <c r="W42" t="n">
         <v>17</v>
@@ -3824,16 +3824,16 @@
         <v>1217</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>28493</v>
+        <v>28502</v>
       </c>
       <c r="O43" t="n">
-        <v>24407</v>
+        <v>24398</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
@@ -3845,16 +3845,16 @@
         <v>6448</v>
       </c>
       <c r="S43" t="n">
-        <v>17959</v>
+        <v>17950</v>
       </c>
       <c r="T43" t="n">
-        <v>7322</v>
+        <v>7319</v>
       </c>
       <c r="U43" t="n">
-        <v>3661</v>
+        <v>3660</v>
       </c>
       <c r="V43" t="n">
-        <v>6976</v>
+        <v>6971</v>
       </c>
       <c r="W43" t="n">
         <v>28.6</v>
@@ -3902,16 +3902,16 @@
         <v>1216</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>29169</v>
+        <v>29177</v>
       </c>
       <c r="O44" t="n">
-        <v>23709</v>
+        <v>23701</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -3923,16 +3923,16 @@
         <v>6380</v>
       </c>
       <c r="S44" t="n">
-        <v>17329</v>
+        <v>17321</v>
       </c>
       <c r="T44" t="n">
-        <v>7113</v>
+        <v>7110</v>
       </c>
       <c r="U44" t="n">
-        <v>3556</v>
+        <v>3555</v>
       </c>
       <c r="V44" t="n">
-        <v>6660</v>
+        <v>6656</v>
       </c>
       <c r="W44" t="n">
         <v>28.1</v>
@@ -3980,16 +3980,16 @@
         <v>1216</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M45" t="n">
         <v>3701</v>
       </c>
       <c r="N45" t="n">
-        <v>32249</v>
+        <v>32258</v>
       </c>
       <c r="O45" t="n">
-        <v>20629</v>
+        <v>20620</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
@@ -4001,16 +4001,16 @@
         <v>6380</v>
       </c>
       <c r="S45" t="n">
-        <v>14249</v>
+        <v>14240</v>
       </c>
       <c r="T45" t="n">
-        <v>6189</v>
+        <v>6186</v>
       </c>
       <c r="U45" t="n">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="V45" t="n">
-        <v>4966</v>
+        <v>4961</v>
       </c>
       <c r="W45" t="n">
         <v>24.1</v>
@@ -4058,16 +4058,16 @@
         <v>1216</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>28551</v>
+        <v>28560</v>
       </c>
       <c r="O46" t="n">
-        <v>24327</v>
+        <v>24318</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -4079,16 +4079,16 @@
         <v>6380</v>
       </c>
       <c r="S46" t="n">
-        <v>17947</v>
+        <v>17938</v>
       </c>
       <c r="T46" t="n">
-        <v>7298</v>
+        <v>7295</v>
       </c>
       <c r="U46" t="n">
-        <v>3649</v>
+        <v>3648</v>
       </c>
       <c r="V46" t="n">
-        <v>7000</v>
+        <v>6995</v>
       </c>
       <c r="W46" t="n">
         <v>28.8</v>
@@ -4136,16 +4136,16 @@
         <v>1190</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M47" t="n">
-        <v>12958</v>
+        <v>12944</v>
       </c>
       <c r="N47" t="n">
-        <v>44568</v>
+        <v>44572</v>
       </c>
       <c r="O47" t="n">
-        <v>7187</v>
+        <v>7183</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
@@ -4157,19 +4157,19 @@
         <v>7453</v>
       </c>
       <c r="S47" t="n">
-        <v>-266</v>
+        <v>-270</v>
       </c>
       <c r="T47" t="n">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="U47" t="n">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="V47" t="n">
-        <v>-3500</v>
+        <v>-3502</v>
       </c>
       <c r="W47" t="n">
-        <v>-48.7</v>
+        <v>-48.8</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -4221,13 +4221,13 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>12958</v>
+        <v>12944</v>
       </c>
       <c r="N48" t="n">
-        <v>44568</v>
+        <v>44554</v>
       </c>
       <c r="O48" t="n">
-        <v>7187</v>
+        <v>7201</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
@@ -4239,19 +4239,19 @@
         <v>7453</v>
       </c>
       <c r="S48" t="n">
-        <v>-266</v>
+        <v>-252</v>
       </c>
       <c r="T48" t="n">
-        <v>2156</v>
+        <v>2160</v>
       </c>
       <c r="U48" t="n">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="V48" t="n">
-        <v>-3500</v>
+        <v>-3492</v>
       </c>
       <c r="W48" t="n">
-        <v>-48.7</v>
+        <v>-48.5</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -4303,13 +4303,13 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>7265</v>
+        <v>7251</v>
       </c>
       <c r="N49" t="n">
-        <v>38971</v>
+        <v>38957</v>
       </c>
       <c r="O49" t="n">
-        <v>12784</v>
+        <v>12798</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
@@ -4321,19 +4321,19 @@
         <v>7453</v>
       </c>
       <c r="S49" t="n">
-        <v>5331</v>
+        <v>5345</v>
       </c>
       <c r="T49" t="n">
-        <v>3835</v>
+        <v>3839</v>
       </c>
       <c r="U49" t="n">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="V49" t="n">
-        <v>-422</v>
+        <v>-414</v>
       </c>
       <c r="W49" t="n">
-        <v>-3.3</v>
+        <v>-3.2</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -4382,16 +4382,16 @@
         <v>1190</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M50" t="n">
-        <v>7265</v>
+        <v>7251</v>
       </c>
       <c r="N50" t="n">
-        <v>38980</v>
+        <v>38975</v>
       </c>
       <c r="O50" t="n">
-        <v>12775</v>
+        <v>12780</v>
       </c>
       <c r="P50" t="n">
         <v>0</v>
@@ -4403,16 +4403,16 @@
         <v>7453</v>
       </c>
       <c r="S50" t="n">
-        <v>5322</v>
+        <v>5327</v>
       </c>
       <c r="T50" t="n">
-        <v>3832</v>
+        <v>3834</v>
       </c>
       <c r="U50" t="n">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="V50" t="n">
-        <v>-427</v>
+        <v>-424</v>
       </c>
       <c r="W50" t="n">
         <v>-3.3</v>
@@ -4467,13 +4467,13 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3642</v>
+        <v>3628</v>
       </c>
       <c r="N51" t="n">
-        <v>34856</v>
+        <v>34842</v>
       </c>
       <c r="O51" t="n">
-        <v>16899</v>
+        <v>16913</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
@@ -4485,16 +4485,16 @@
         <v>7453</v>
       </c>
       <c r="S51" t="n">
-        <v>9446</v>
+        <v>9460</v>
       </c>
       <c r="T51" t="n">
-        <v>5070</v>
+        <v>5074</v>
       </c>
       <c r="U51" t="n">
-        <v>2535</v>
+        <v>2537</v>
       </c>
       <c r="V51" t="n">
-        <v>1841</v>
+        <v>1849</v>
       </c>
       <c r="W51" t="n">
         <v>10.9</v>
@@ -4546,16 +4546,16 @@
         <v>1190</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M52" t="n">
-        <v>3642</v>
+        <v>3628</v>
       </c>
       <c r="N52" t="n">
-        <v>33241</v>
+        <v>33234</v>
       </c>
       <c r="O52" t="n">
-        <v>18514</v>
+        <v>18521</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
@@ -4567,19 +4567,19 @@
         <v>7453</v>
       </c>
       <c r="S52" t="n">
-        <v>11061</v>
+        <v>11068</v>
       </c>
       <c r="T52" t="n">
-        <v>5554</v>
+        <v>5556</v>
       </c>
       <c r="U52" t="n">
-        <v>2777</v>
+        <v>2778</v>
       </c>
       <c r="V52" t="n">
-        <v>2730</v>
+        <v>2734</v>
       </c>
       <c r="W52" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -4631,13 +4631,13 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3642</v>
+        <v>3628</v>
       </c>
       <c r="N53" t="n">
-        <v>32269</v>
+        <v>32255</v>
       </c>
       <c r="O53" t="n">
-        <v>19486</v>
+        <v>19500</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
@@ -4649,16 +4649,16 @@
         <v>7453</v>
       </c>
       <c r="S53" t="n">
-        <v>12033</v>
+        <v>12047</v>
       </c>
       <c r="T53" t="n">
-        <v>5846</v>
+        <v>5850</v>
       </c>
       <c r="U53" t="n">
-        <v>2923</v>
+        <v>2925</v>
       </c>
       <c r="V53" t="n">
-        <v>3264</v>
+        <v>3272</v>
       </c>
       <c r="W53" t="n">
         <v>16.8</v>
@@ -4710,10 +4710,10 @@
         <v>1190</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M54" t="n">
-        <v>7265</v>
+        <v>7251</v>
       </c>
       <c r="N54" t="n">
         <v>36941</v>
@@ -4792,16 +4792,16 @@
         <v>1174</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M55" t="n">
-        <v>3642</v>
+        <v>3628</v>
       </c>
       <c r="N55" t="n">
-        <v>32271</v>
+        <v>32266</v>
       </c>
       <c r="O55" t="n">
-        <v>18785</v>
+        <v>18790</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -4813,16 +4813,16 @@
         <v>7453</v>
       </c>
       <c r="S55" t="n">
-        <v>11332</v>
+        <v>11337</v>
       </c>
       <c r="T55" t="n">
-        <v>5636</v>
+        <v>5637</v>
       </c>
       <c r="U55" t="n">
         <v>2818</v>
       </c>
       <c r="V55" t="n">
-        <v>2879</v>
+        <v>2882</v>
       </c>
       <c r="W55" t="n">
         <v>15.3</v>
@@ -4880,10 +4880,10 @@
         <v>4581</v>
       </c>
       <c r="N56" t="n">
-        <v>33197</v>
+        <v>33177</v>
       </c>
       <c r="O56" t="n">
-        <v>17703</v>
+        <v>17723</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
@@ -4895,19 +4895,19 @@
         <v>9241</v>
       </c>
       <c r="S56" t="n">
-        <v>11261</v>
+        <v>11281</v>
       </c>
       <c r="T56" t="n">
-        <v>5311</v>
+        <v>5317</v>
       </c>
       <c r="U56" t="n">
-        <v>2655</v>
+        <v>2658</v>
       </c>
       <c r="V56" t="n">
-        <v>3295</v>
+        <v>3306</v>
       </c>
       <c r="W56" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="X56" t="inlineStr"/>
     </row>
@@ -4952,16 +4952,16 @@
         <v>1171</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>30119</v>
+        <v>30130</v>
       </c>
       <c r="O57" t="n">
-        <v>20781</v>
+        <v>20770</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
@@ -4973,16 +4973,16 @@
         <v>10434</v>
       </c>
       <c r="S57" t="n">
-        <v>10347</v>
+        <v>10336</v>
       </c>
       <c r="T57" t="n">
-        <v>6234</v>
+        <v>6231</v>
       </c>
       <c r="U57" t="n">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="V57" t="n">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="W57" t="n">
         <v>4.8</v>
@@ -5030,16 +5030,16 @@
         <v>1169</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M58" t="n">
         <v>4573</v>
       </c>
       <c r="N58" t="n">
-        <v>34183</v>
+        <v>34191</v>
       </c>
       <c r="O58" t="n">
-        <v>16632</v>
+        <v>16624</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
@@ -5051,19 +5051,19 @@
         <v>8173</v>
       </c>
       <c r="S58" t="n">
-        <v>8459</v>
+        <v>8451</v>
       </c>
       <c r="T58" t="n">
-        <v>4990</v>
+        <v>4987</v>
       </c>
       <c r="U58" t="n">
-        <v>2495</v>
+        <v>2494</v>
       </c>
       <c r="V58" t="n">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="W58" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="X58" t="inlineStr"/>
     </row>
@@ -5186,16 +5186,16 @@
         <v>1157</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M60" t="n">
         <v>3521</v>
       </c>
       <c r="N60" t="n">
-        <v>32641</v>
+        <v>32650</v>
       </c>
       <c r="O60" t="n">
-        <v>17664</v>
+        <v>17655</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
@@ -5207,16 +5207,16 @@
         <v>8173</v>
       </c>
       <c r="S60" t="n">
-        <v>9491</v>
+        <v>9482</v>
       </c>
       <c r="T60" t="n">
-        <v>5299</v>
+        <v>5296</v>
       </c>
       <c r="U60" t="n">
-        <v>2650</v>
+        <v>2648</v>
       </c>
       <c r="V60" t="n">
-        <v>1542</v>
+        <v>1537</v>
       </c>
       <c r="W60" t="n">
         <v>8.699999999999999</v>
@@ -5498,16 +5498,16 @@
         <v>1131</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M64" t="n">
-        <v>3638</v>
+        <v>3627</v>
       </c>
       <c r="N64" t="n">
-        <v>32417</v>
+        <v>32414</v>
       </c>
       <c r="O64" t="n">
-        <v>16751</v>
+        <v>16754</v>
       </c>
       <c r="P64" t="n">
         <v>0</v>
@@ -5519,16 +5519,16 @@
         <v>7453</v>
       </c>
       <c r="S64" t="n">
-        <v>9298</v>
+        <v>9301</v>
       </c>
       <c r="T64" t="n">
-        <v>5025</v>
+        <v>5026</v>
       </c>
       <c r="U64" t="n">
         <v>2513</v>
       </c>
       <c r="V64" t="n">
-        <v>1760</v>
+        <v>1762</v>
       </c>
       <c r="W64" t="n">
         <v>10.5</v>
@@ -5580,16 +5580,16 @@
         <v>1125</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>26638</v>
+        <v>26647</v>
       </c>
       <c r="O65" t="n">
-        <v>22262</v>
+        <v>22253</v>
       </c>
       <c r="P65" t="n">
         <v>0</v>
@@ -5601,16 +5601,16 @@
         <v>6380</v>
       </c>
       <c r="S65" t="n">
-        <v>15882</v>
+        <v>15873</v>
       </c>
       <c r="T65" t="n">
-        <v>6679</v>
+        <v>6676</v>
       </c>
       <c r="U65" t="n">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="V65" t="n">
-        <v>5864</v>
+        <v>5859</v>
       </c>
       <c r="W65" t="n">
         <v>26.3</v>
@@ -5736,16 +5736,16 @@
         <v>1102</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M67" t="n">
         <v>3355</v>
       </c>
       <c r="N67" t="n">
-        <v>30364</v>
+        <v>30372</v>
       </c>
       <c r="O67" t="n">
-        <v>17563</v>
+        <v>17555</v>
       </c>
       <c r="P67" t="n">
         <v>0</v>
@@ -5757,16 +5757,16 @@
         <v>6448</v>
       </c>
       <c r="S67" t="n">
-        <v>11115</v>
+        <v>11107</v>
       </c>
       <c r="T67" t="n">
-        <v>5269</v>
+        <v>5266</v>
       </c>
       <c r="U67" t="n">
-        <v>2634</v>
+        <v>2633</v>
       </c>
       <c r="V67" t="n">
-        <v>3212</v>
+        <v>3207</v>
       </c>
       <c r="W67" t="n">
         <v>18.3</v>
@@ -5814,16 +5814,16 @@
         <v>1102</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M68" t="n">
         <v>2395</v>
       </c>
       <c r="N68" t="n">
-        <v>30902</v>
+        <v>30912</v>
       </c>
       <c r="O68" t="n">
-        <v>16998</v>
+        <v>16988</v>
       </c>
       <c r="P68" t="n">
         <v>0</v>
@@ -5835,16 +5835,16 @@
         <v>5662</v>
       </c>
       <c r="S68" t="n">
-        <v>11336</v>
+        <v>11326</v>
       </c>
       <c r="T68" t="n">
-        <v>5099</v>
+        <v>5096</v>
       </c>
       <c r="U68" t="n">
-        <v>2550</v>
+        <v>2548</v>
       </c>
       <c r="V68" t="n">
-        <v>3687</v>
+        <v>3681</v>
       </c>
       <c r="W68" t="n">
         <v>21.7</v>
@@ -5892,16 +5892,16 @@
         <v>1102</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M69" t="n">
         <v>4311</v>
       </c>
       <c r="N69" t="n">
-        <v>30430</v>
+        <v>30438</v>
       </c>
       <c r="O69" t="n">
-        <v>17470</v>
+        <v>17462</v>
       </c>
       <c r="P69" t="n">
         <v>0</v>
@@ -5913,19 +5913,19 @@
         <v>9092</v>
       </c>
       <c r="S69" t="n">
-        <v>8378</v>
+        <v>8370</v>
       </c>
       <c r="T69" t="n">
-        <v>5241</v>
+        <v>5239</v>
       </c>
       <c r="U69" t="n">
-        <v>2620</v>
+        <v>2619</v>
       </c>
       <c r="V69" t="n">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="W69" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="X69" t="inlineStr"/>
     </row>
@@ -5970,16 +5970,16 @@
         <v>1102</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M70" t="n">
         <v>4311</v>
       </c>
       <c r="N70" t="n">
-        <v>30907</v>
+        <v>30915</v>
       </c>
       <c r="O70" t="n">
-        <v>16993</v>
+        <v>16985</v>
       </c>
       <c r="P70" t="n">
         <v>0</v>
@@ -5991,16 +5991,16 @@
         <v>5882</v>
       </c>
       <c r="S70" t="n">
-        <v>11111</v>
+        <v>11103</v>
       </c>
       <c r="T70" t="n">
-        <v>5098</v>
+        <v>5096</v>
       </c>
       <c r="U70" t="n">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="V70" t="n">
-        <v>3464</v>
+        <v>3460</v>
       </c>
       <c r="W70" t="n">
         <v>20.4</v>
@@ -6048,16 +6048,16 @@
         <v>1102</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>26691</v>
+        <v>26699</v>
       </c>
       <c r="O71" t="n">
-        <v>21209</v>
+        <v>21201</v>
       </c>
       <c r="P71" t="n">
         <v>0</v>
@@ -6069,16 +6069,16 @@
         <v>9092</v>
       </c>
       <c r="S71" t="n">
-        <v>12117</v>
+        <v>12109</v>
       </c>
       <c r="T71" t="n">
-        <v>6363</v>
+        <v>6360</v>
       </c>
       <c r="U71" t="n">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="V71" t="n">
-        <v>2573</v>
+        <v>2569</v>
       </c>
       <c r="W71" t="n">
         <v>12.1</v>
@@ -6126,16 +6126,16 @@
         <v>1102</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M72" t="n">
         <v>3353</v>
       </c>
       <c r="N72" t="n">
-        <v>31860</v>
+        <v>31870</v>
       </c>
       <c r="O72" t="n">
-        <v>16040</v>
+        <v>16030</v>
       </c>
       <c r="P72" t="n">
         <v>0</v>
@@ -6147,16 +6147,16 @@
         <v>5662</v>
       </c>
       <c r="S72" t="n">
-        <v>10378</v>
+        <v>10368</v>
       </c>
       <c r="T72" t="n">
-        <v>4812</v>
+        <v>4809</v>
       </c>
       <c r="U72" t="n">
-        <v>2406</v>
+        <v>2404</v>
       </c>
       <c r="V72" t="n">
-        <v>3160</v>
+        <v>3154</v>
       </c>
       <c r="W72" t="n">
         <v>19.7</v>
@@ -6364,16 +6364,16 @@
         <v>1056</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M75" t="n">
         <v>1285</v>
       </c>
       <c r="N75" t="n">
-        <v>27298</v>
+        <v>27305</v>
       </c>
       <c r="O75" t="n">
-        <v>18602</v>
+        <v>18595</v>
       </c>
       <c r="P75" t="n">
         <v>0</v>
@@ -6385,16 +6385,16 @@
         <v>4971</v>
       </c>
       <c r="S75" t="n">
-        <v>13631</v>
+        <v>13624</v>
       </c>
       <c r="T75" t="n">
-        <v>5581</v>
+        <v>5578</v>
       </c>
       <c r="U75" t="n">
-        <v>2790</v>
+        <v>2789</v>
       </c>
       <c r="V75" t="n">
-        <v>5260</v>
+        <v>5256</v>
       </c>
       <c r="W75" t="n">
         <v>28.3</v>
@@ -6446,16 +6446,16 @@
         <v>1010</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M76" t="n">
         <v>5236</v>
       </c>
       <c r="N76" t="n">
-        <v>30155</v>
+        <v>30166</v>
       </c>
       <c r="O76" t="n">
-        <v>13745</v>
+        <v>13734</v>
       </c>
       <c r="P76" t="n">
         <v>0</v>
@@ -6467,16 +6467,16 @@
         <v>4971</v>
       </c>
       <c r="S76" t="n">
-        <v>8774</v>
+        <v>8763</v>
       </c>
       <c r="T76" t="n">
-        <v>4124</v>
+        <v>4120</v>
       </c>
       <c r="U76" t="n">
-        <v>2062</v>
+        <v>2060</v>
       </c>
       <c r="V76" t="n">
-        <v>2589</v>
+        <v>2583</v>
       </c>
       <c r="W76" t="n">
         <v>18.8</v>
@@ -6528,16 +6528,16 @@
         <v>1010</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M77" t="n">
         <v>1285</v>
       </c>
       <c r="N77" t="n">
-        <v>26641</v>
+        <v>26650</v>
       </c>
       <c r="O77" t="n">
-        <v>17259</v>
+        <v>17250</v>
       </c>
       <c r="P77" t="n">
         <v>0</v>
@@ -6549,16 +6549,16 @@
         <v>4971</v>
       </c>
       <c r="S77" t="n">
-        <v>12288</v>
+        <v>12279</v>
       </c>
       <c r="T77" t="n">
-        <v>5178</v>
+        <v>5175</v>
       </c>
       <c r="U77" t="n">
-        <v>2589</v>
+        <v>2588</v>
       </c>
       <c r="V77" t="n">
-        <v>4521</v>
+        <v>4516</v>
       </c>
       <c r="W77" t="n">
         <v>26.2</v>
@@ -6610,16 +6610,16 @@
         <v>1010</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M78" t="n">
         <v>4358</v>
       </c>
       <c r="N78" t="n">
-        <v>35293</v>
+        <v>35301</v>
       </c>
       <c r="O78" t="n">
-        <v>8607</v>
+        <v>8599</v>
       </c>
       <c r="P78" t="n">
         <v>0</v>
@@ -6631,16 +6631,16 @@
         <v>4971</v>
       </c>
       <c r="S78" t="n">
-        <v>3636</v>
+        <v>3628</v>
       </c>
       <c r="T78" t="n">
-        <v>2582</v>
+        <v>2580</v>
       </c>
       <c r="U78" t="n">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="V78" t="n">
-        <v>-237</v>
+        <v>-242</v>
       </c>
       <c r="W78" t="n">
         <v>-2.8</v>
@@ -6692,16 +6692,16 @@
         <v>1010</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>23990</v>
+        <v>24003</v>
       </c>
       <c r="O79" t="n">
-        <v>19910</v>
+        <v>19897</v>
       </c>
       <c r="P79" t="n">
         <v>0</v>
@@ -6713,16 +6713,16 @@
         <v>5538</v>
       </c>
       <c r="S79" t="n">
-        <v>14372</v>
+        <v>14359</v>
       </c>
       <c r="T79" t="n">
-        <v>5973</v>
+        <v>5969</v>
       </c>
       <c r="U79" t="n">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="V79" t="n">
-        <v>5412</v>
+        <v>5405</v>
       </c>
       <c r="W79" t="n">
         <v>27.2</v>
@@ -6770,16 +6770,16 @@
         <v>1010</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M80" t="n">
         <v>6146</v>
       </c>
       <c r="N80" t="n">
-        <v>33453</v>
+        <v>33466</v>
       </c>
       <c r="O80" t="n">
-        <v>10447</v>
+        <v>10434</v>
       </c>
       <c r="P80" t="n">
         <v>0</v>
@@ -6791,19 +6791,19 @@
         <v>4565</v>
       </c>
       <c r="S80" t="n">
-        <v>5882</v>
+        <v>5869</v>
       </c>
       <c r="T80" t="n">
-        <v>3134</v>
+        <v>3130</v>
       </c>
       <c r="U80" t="n">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="V80" t="n">
-        <v>1181</v>
+        <v>1174</v>
       </c>
       <c r="W80" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="X80" t="inlineStr"/>
     </row>
@@ -6926,16 +6926,16 @@
         <v>1010</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M82" t="n">
         <v>4358</v>
       </c>
       <c r="N82" t="n">
-        <v>38999</v>
+        <v>39016</v>
       </c>
       <c r="O82" t="n">
-        <v>4901</v>
+        <v>4884</v>
       </c>
       <c r="P82" t="n">
         <v>0</v>
@@ -6947,19 +6947,19 @@
         <v>4971</v>
       </c>
       <c r="S82" t="n">
-        <v>-70</v>
+        <v>-87</v>
       </c>
       <c r="T82" t="n">
-        <v>1470</v>
+        <v>1465</v>
       </c>
       <c r="U82" t="n">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="V82" t="n">
-        <v>-2275</v>
+        <v>-2285</v>
       </c>
       <c r="W82" t="n">
-        <v>-46.4</v>
+        <v>-46.8</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -7320,10 +7320,10 @@
         <v>1007</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M87" t="n">
-        <v>18777</v>
+        <v>18760</v>
       </c>
       <c r="N87" t="n">
         <v>44199</v>
@@ -7395,16 +7395,16 @@
         <v>1007</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M88" t="n">
-        <v>10346</v>
+        <v>10329</v>
       </c>
       <c r="N88" t="n">
-        <v>37133</v>
+        <v>37132</v>
       </c>
       <c r="O88" t="n">
-        <v>6645</v>
+        <v>6646</v>
       </c>
       <c r="P88" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>4565</v>
       </c>
       <c r="S88" t="n">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="T88" t="n">
         <v>1994</v>
@@ -7476,13 +7476,13 @@
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>10346</v>
+        <v>10329</v>
       </c>
       <c r="N89" t="n">
-        <v>37133</v>
+        <v>37116</v>
       </c>
       <c r="O89" t="n">
-        <v>6645</v>
+        <v>6662</v>
       </c>
       <c r="P89" t="n">
         <v>0</v>
@@ -7494,19 +7494,19 @@
         <v>4565</v>
       </c>
       <c r="S89" t="n">
-        <v>2080</v>
+        <v>2097</v>
       </c>
       <c r="T89" t="n">
-        <v>1994</v>
+        <v>1999</v>
       </c>
       <c r="U89" t="n">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="V89" t="n">
-        <v>-910</v>
+        <v>-901</v>
       </c>
       <c r="W89" t="n">
-        <v>-13.7</v>
+        <v>-13.5</v>
       </c>
       <c r="X89" t="inlineStr"/>
     </row>
@@ -7551,16 +7551,16 @@
         <v>1007</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M90" t="n">
-        <v>10346</v>
+        <v>10327</v>
       </c>
       <c r="N90" t="n">
-        <v>36352</v>
+        <v>36339</v>
       </c>
       <c r="O90" t="n">
-        <v>7426</v>
+        <v>7439</v>
       </c>
       <c r="P90" t="n">
         <v>0</v>
@@ -7572,19 +7572,19 @@
         <v>4565</v>
       </c>
       <c r="S90" t="n">
-        <v>2861</v>
+        <v>2874</v>
       </c>
       <c r="T90" t="n">
-        <v>2228</v>
+        <v>2232</v>
       </c>
       <c r="U90" t="n">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="V90" t="n">
-        <v>-481</v>
+        <v>-474</v>
       </c>
       <c r="W90" t="n">
-        <v>-6.5</v>
+        <v>-6.4</v>
       </c>
       <c r="X90" t="inlineStr"/>
     </row>
@@ -7629,16 +7629,16 @@
         <v>979</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M91" t="n">
-        <v>14177</v>
+        <v>14160</v>
       </c>
       <c r="N91" t="n">
-        <v>38954</v>
+        <v>38947</v>
       </c>
       <c r="O91" t="n">
-        <v>3609</v>
+        <v>3616</v>
       </c>
       <c r="P91" t="n">
         <v>0</v>
@@ -7650,19 +7650,19 @@
         <v>4565</v>
       </c>
       <c r="S91" t="n">
-        <v>-956</v>
+        <v>-949</v>
       </c>
       <c r="T91" t="n">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="U91" t="n">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="V91" t="n">
-        <v>-2580</v>
+        <v>-2576</v>
       </c>
       <c r="W91" t="n">
-        <v>-71.5</v>
+        <v>-71.2</v>
       </c>
       <c r="X91" t="inlineStr"/>
     </row>
@@ -7863,16 +7863,16 @@
         <v>918</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M94" t="n">
         <v>3591</v>
       </c>
       <c r="N94" t="n">
-        <v>25473</v>
+        <v>25482</v>
       </c>
       <c r="O94" t="n">
-        <v>14427</v>
+        <v>14418</v>
       </c>
       <c r="P94" t="n">
         <v>0</v>
@@ -7884,16 +7884,16 @@
         <v>4196</v>
       </c>
       <c r="S94" t="n">
-        <v>10231</v>
+        <v>10222</v>
       </c>
       <c r="T94" t="n">
-        <v>4328</v>
+        <v>4325</v>
       </c>
       <c r="U94" t="n">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="V94" t="n">
-        <v>3739</v>
+        <v>3734</v>
       </c>
       <c r="W94" t="n">
         <v>25.9</v>
@@ -7941,16 +7941,16 @@
         <v>849</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M95" t="n">
         <v>2583</v>
       </c>
       <c r="N95" t="n">
-        <v>24280</v>
+        <v>24290</v>
       </c>
       <c r="O95" t="n">
-        <v>12620</v>
+        <v>12610</v>
       </c>
       <c r="P95" t="n">
         <v>0</v>
@@ -7962,19 +7962,19 @@
         <v>5318</v>
       </c>
       <c r="S95" t="n">
-        <v>7302</v>
+        <v>7292</v>
       </c>
       <c r="T95" t="n">
-        <v>3786</v>
+        <v>3783</v>
       </c>
       <c r="U95" t="n">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="V95" t="n">
-        <v>1623</v>
+        <v>1618</v>
       </c>
       <c r="W95" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="X95" t="inlineStr"/>
     </row>
@@ -8019,16 +8019,16 @@
         <v>849</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M96" t="n">
         <v>2583</v>
       </c>
       <c r="N96" t="n">
-        <v>23062</v>
+        <v>23071</v>
       </c>
       <c r="O96" t="n">
-        <v>13838</v>
+        <v>13829</v>
       </c>
       <c r="P96" t="n">
         <v>0</v>
@@ -8040,19 +8040,19 @@
         <v>5318</v>
       </c>
       <c r="S96" t="n">
-        <v>8520</v>
+        <v>8511</v>
       </c>
       <c r="T96" t="n">
-        <v>4151</v>
+        <v>4149</v>
       </c>
       <c r="U96" t="n">
-        <v>2076</v>
+        <v>2074</v>
       </c>
       <c r="V96" t="n">
-        <v>2293</v>
+        <v>2288</v>
       </c>
       <c r="W96" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="X96" t="inlineStr"/>
     </row>
@@ -8097,16 +8097,16 @@
         <v>812</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M97" t="n">
         <v>3177</v>
       </c>
       <c r="N97" t="n">
-        <v>22816</v>
+        <v>22827</v>
       </c>
       <c r="O97" t="n">
-        <v>12489</v>
+        <v>12478</v>
       </c>
       <c r="P97" t="n">
         <v>0</v>
@@ -8118,16 +8118,16 @@
         <v>4030</v>
       </c>
       <c r="S97" t="n">
-        <v>8459</v>
+        <v>8448</v>
       </c>
       <c r="T97" t="n">
-        <v>3747</v>
+        <v>3743</v>
       </c>
       <c r="U97" t="n">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="V97" t="n">
-        <v>2839</v>
+        <v>2833</v>
       </c>
       <c r="W97" t="n">
         <v>22.7</v>
@@ -8181,10 +8181,10 @@
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>19795</v>
+        <v>19775</v>
       </c>
       <c r="O98" t="n">
-        <v>15470</v>
+        <v>15490</v>
       </c>
       <c r="P98" t="n">
         <v>4434</v>
@@ -8196,19 +8196,19 @@
         <v>4471</v>
       </c>
       <c r="S98" t="n">
-        <v>6565</v>
+        <v>6585</v>
       </c>
       <c r="T98" t="n">
-        <v>4641</v>
+        <v>4647</v>
       </c>
       <c r="U98" t="n">
-        <v>2320</v>
+        <v>2324</v>
       </c>
       <c r="V98" t="n">
-        <v>-396</v>
+        <v>-386</v>
       </c>
       <c r="W98" t="n">
-        <v>-2.6</v>
+        <v>-2.5</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -8413,16 +8413,16 @@
         <v>725</v>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M101" t="n">
         <v>2836</v>
       </c>
       <c r="N101" t="n">
-        <v>20055</v>
+        <v>20064</v>
       </c>
       <c r="O101" t="n">
-        <v>11457</v>
+        <v>11448</v>
       </c>
       <c r="P101" t="n">
         <v>0</v>
@@ -8434,19 +8434,19 @@
         <v>3419</v>
       </c>
       <c r="S101" t="n">
-        <v>8038</v>
+        <v>8029</v>
       </c>
       <c r="T101" t="n">
-        <v>3437</v>
+        <v>3434</v>
       </c>
       <c r="U101" t="n">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="V101" t="n">
-        <v>2882</v>
+        <v>2877</v>
       </c>
       <c r="W101" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="X101" t="inlineStr"/>
     </row>
@@ -8491,16 +8491,16 @@
         <v>704</v>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M102" t="n">
         <v>2143</v>
       </c>
       <c r="N102" t="n">
-        <v>18848</v>
+        <v>18856</v>
       </c>
       <c r="O102" t="n">
-        <v>11767</v>
+        <v>11759</v>
       </c>
       <c r="P102" t="n">
         <v>0</v>
@@ -8512,16 +8512,16 @@
         <v>3497</v>
       </c>
       <c r="S102" t="n">
-        <v>8270</v>
+        <v>8262</v>
       </c>
       <c r="T102" t="n">
-        <v>3530</v>
+        <v>3528</v>
       </c>
       <c r="U102" t="n">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="V102" t="n">
-        <v>2975</v>
+        <v>2970</v>
       </c>
       <c r="W102" t="n">
         <v>25.3</v>
@@ -8569,16 +8569,16 @@
         <v>619</v>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>15513</v>
+        <v>15523</v>
       </c>
       <c r="O103" t="n">
-        <v>11387</v>
+        <v>11377</v>
       </c>
       <c r="P103" t="n">
         <v>0</v>
@@ -8590,16 +8590,16 @@
         <v>2889</v>
       </c>
       <c r="S103" t="n">
-        <v>8498</v>
+        <v>8488</v>
       </c>
       <c r="T103" t="n">
-        <v>3416</v>
+        <v>3413</v>
       </c>
       <c r="U103" t="n">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="V103" t="n">
-        <v>3374</v>
+        <v>3368</v>
       </c>
       <c r="W103" t="n">
         <v>29.6</v>
@@ -8647,16 +8647,16 @@
         <v>582</v>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M104" t="n">
         <v>1771</v>
       </c>
       <c r="N104" t="n">
-        <v>15747</v>
+        <v>15756</v>
       </c>
       <c r="O104" t="n">
-        <v>9553</v>
+        <v>9544</v>
       </c>
       <c r="P104" t="n">
         <v>0</v>
@@ -8668,19 +8668,19 @@
         <v>2889</v>
       </c>
       <c r="S104" t="n">
-        <v>6664</v>
+        <v>6655</v>
       </c>
       <c r="T104" t="n">
-        <v>2866</v>
+        <v>2863</v>
       </c>
       <c r="U104" t="n">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="V104" t="n">
-        <v>2365</v>
+        <v>2360</v>
       </c>
       <c r="W104" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="X104" t="inlineStr"/>
     </row>
@@ -8725,16 +8725,16 @@
         <v>550</v>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M105" t="n">
         <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>13715</v>
+        <v>13725</v>
       </c>
       <c r="O105" t="n">
-        <v>10185</v>
+        <v>10175</v>
       </c>
       <c r="P105" t="n">
         <v>0</v>
@@ -8746,16 +8746,16 @@
         <v>2889</v>
       </c>
       <c r="S105" t="n">
-        <v>7296</v>
+        <v>7286</v>
       </c>
       <c r="T105" t="n">
-        <v>3056</v>
+        <v>3052</v>
       </c>
       <c r="U105" t="n">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="V105" t="n">
-        <v>2713</v>
+        <v>2707</v>
       </c>
       <c r="W105" t="n">
         <v>26.6</v>
@@ -8953,16 +8953,16 @@
         <v>964</v>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M108" t="n">
         <v>2933</v>
       </c>
       <c r="N108" t="n">
-        <v>4573</v>
+        <v>4584</v>
       </c>
       <c r="O108" t="n">
-        <v>-4573</v>
+        <v>-4584</v>
       </c>
       <c r="P108" t="n">
         <v>0</v>
@@ -8974,16 +8974,16 @@
         <v>4768</v>
       </c>
       <c r="S108" t="n">
-        <v>-9341</v>
+        <v>-9352</v>
       </c>
       <c r="T108" t="n">
-        <v>-1372</v>
+        <v>-1375</v>
       </c>
       <c r="U108" t="n">
-        <v>-686</v>
+        <v>-688</v>
       </c>
       <c r="V108" t="n">
-        <v>-7283</v>
+        <v>-7289</v>
       </c>
       <c r="X108" t="inlineStr"/>
     </row>
@@ -9028,16 +9028,16 @@
         <v>613</v>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M109" t="n">
         <v>1864</v>
       </c>
       <c r="N109" t="n">
-        <v>3071</v>
+        <v>3083</v>
       </c>
       <c r="O109" t="n">
-        <v>-3071</v>
+        <v>-3083</v>
       </c>
       <c r="P109" t="n">
         <v>0</v>
@@ -9049,16 +9049,16 @@
         <v>2889</v>
       </c>
       <c r="S109" t="n">
-        <v>-5960</v>
+        <v>-5972</v>
       </c>
       <c r="T109" t="n">
-        <v>-921</v>
+        <v>-925</v>
       </c>
       <c r="U109" t="n">
-        <v>-461</v>
+        <v>-462</v>
       </c>
       <c r="V109" t="n">
-        <v>-4578</v>
+        <v>-4585</v>
       </c>
       <c r="X109" t="inlineStr"/>
     </row>
@@ -9139,10 +9139,10 @@
         <v>11776</v>
       </c>
       <c r="N111" t="n">
-        <v>74993</v>
+        <v>74973</v>
       </c>
       <c r="O111" t="n">
-        <v>55850</v>
+        <v>55870</v>
       </c>
       <c r="P111" t="n">
         <v>3978</v>
@@ -9154,16 +9154,16 @@
         <v>26077</v>
       </c>
       <c r="S111" t="n">
-        <v>30195</v>
+        <v>30215</v>
       </c>
       <c r="T111" t="n">
-        <v>16755</v>
+        <v>16761</v>
       </c>
       <c r="U111" t="n">
-        <v>8378</v>
+        <v>8380</v>
       </c>
       <c r="V111" t="n">
-        <v>5062</v>
+        <v>5074</v>
       </c>
       <c r="W111" t="n">
         <v>9.1</v>
@@ -9215,16 +9215,16 @@
         <v>3009</v>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>22714</v>
       </c>
       <c r="M112" t="n">
         <v>11776</v>
       </c>
       <c r="N112" t="n">
-        <v>97707</v>
+        <v>97687</v>
       </c>
       <c r="O112" t="n">
-        <v>33136</v>
+        <v>33156</v>
       </c>
       <c r="P112" t="n">
         <v>0</v>
@@ -9236,16 +9236,16 @@
         <v>26077</v>
       </c>
       <c r="S112" t="n">
-        <v>26321</v>
+        <v>26341</v>
       </c>
       <c r="T112" t="n">
-        <v>9941</v>
+        <v>9947</v>
       </c>
       <c r="U112" t="n">
-        <v>4970</v>
+        <v>4973</v>
       </c>
       <c r="V112" t="n">
-        <v>11410</v>
+        <v>11421</v>
       </c>
       <c r="W112" t="n">
         <v>34.4</v>
@@ -9303,10 +9303,10 @@
         <v>5033</v>
       </c>
       <c r="N113" t="n">
-        <v>43621</v>
+        <v>43601</v>
       </c>
       <c r="O113" t="n">
-        <v>28279</v>
+        <v>28299</v>
       </c>
       <c r="P113" t="n">
         <v>3555</v>
@@ -9318,16 +9318,16 @@
         <v>11477</v>
       </c>
       <c r="S113" t="n">
-        <v>15947</v>
+        <v>15967</v>
       </c>
       <c r="T113" t="n">
-        <v>8484</v>
+        <v>8490</v>
       </c>
       <c r="U113" t="n">
-        <v>4242</v>
+        <v>4245</v>
       </c>
       <c r="V113" t="n">
-        <v>3221</v>
+        <v>3232</v>
       </c>
       <c r="W113" t="n">
         <v>11.4</v>
@@ -9625,16 +9625,16 @@
         <v>1099</v>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M117" t="n">
         <v>3346</v>
       </c>
       <c r="N117" t="n">
-        <v>30495</v>
+        <v>30512</v>
       </c>
       <c r="O117" t="n">
-        <v>17305</v>
+        <v>17288</v>
       </c>
       <c r="P117" t="n">
         <v>0</v>
@@ -9646,19 +9646,19 @@
         <v>8574</v>
       </c>
       <c r="S117" t="n">
-        <v>8731</v>
+        <v>8714</v>
       </c>
       <c r="T117" t="n">
-        <v>5192</v>
+        <v>5186</v>
       </c>
       <c r="U117" t="n">
-        <v>2596</v>
+        <v>2593</v>
       </c>
       <c r="V117" t="n">
-        <v>944</v>
+        <v>934</v>
       </c>
       <c r="W117" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="X117" t="inlineStr"/>
     </row>
@@ -9785,16 +9785,16 @@
         <v>1274</v>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M119" t="n">
         <v>3025</v>
       </c>
       <c r="N119" t="n">
-        <v>27263</v>
+        <v>27271</v>
       </c>
       <c r="O119" t="n">
-        <v>15946</v>
+        <v>15938</v>
       </c>
       <c r="P119" t="n">
         <v>0</v>
@@ -9806,16 +9806,16 @@
         <v>10263</v>
       </c>
       <c r="S119" t="n">
-        <v>5683</v>
+        <v>5675</v>
       </c>
       <c r="T119" t="n">
-        <v>4784</v>
+        <v>4781</v>
       </c>
       <c r="U119" t="n">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="V119" t="n">
-        <v>-1493</v>
+        <v>-1497</v>
       </c>
       <c r="W119" t="n">
         <v>-9.4</v>
@@ -9863,16 +9863,16 @@
         <v>941</v>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M120" t="n">
         <v>2863</v>
       </c>
       <c r="N120" t="n">
-        <v>30117</v>
+        <v>30125</v>
       </c>
       <c r="O120" t="n">
-        <v>10783</v>
+        <v>10775</v>
       </c>
       <c r="P120" t="n">
         <v>0</v>
@@ -9884,19 +9884,19 @@
         <v>7962</v>
       </c>
       <c r="S120" t="n">
-        <v>2821</v>
+        <v>2813</v>
       </c>
       <c r="T120" t="n">
-        <v>3235</v>
+        <v>3232</v>
       </c>
       <c r="U120" t="n">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="V120" t="n">
-        <v>-2031</v>
+        <v>-2036</v>
       </c>
       <c r="W120" t="n">
-        <v>-18.8</v>
+        <v>-18.9</v>
       </c>
       <c r="X120" t="inlineStr"/>
     </row>
@@ -9941,16 +9941,16 @@
         <v>941</v>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M121" t="n">
         <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>28236</v>
+        <v>28245</v>
       </c>
       <c r="O121" t="n">
-        <v>12664</v>
+        <v>12655</v>
       </c>
       <c r="P121" t="n">
         <v>0</v>
@@ -9962,16 +9962,16 @@
         <v>7962</v>
       </c>
       <c r="S121" t="n">
-        <v>4702</v>
+        <v>4693</v>
       </c>
       <c r="T121" t="n">
-        <v>3799</v>
+        <v>3796</v>
       </c>
       <c r="U121" t="n">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="V121" t="n">
-        <v>-997</v>
+        <v>-1002</v>
       </c>
       <c r="W121" t="n">
         <v>-7.9</v>
@@ -10263,10 +10263,10 @@
         <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>20935</v>
+        <v>20915</v>
       </c>
       <c r="O125" t="n">
-        <v>17965</v>
+        <v>17985</v>
       </c>
       <c r="P125" t="n">
         <v>1734</v>
@@ -10278,19 +10278,19 @@
         <v>8990</v>
       </c>
       <c r="S125" t="n">
-        <v>10641</v>
+        <v>10661</v>
       </c>
       <c r="T125" t="n">
-        <v>5390</v>
+        <v>5396</v>
       </c>
       <c r="U125" t="n">
-        <v>2695</v>
+        <v>2698</v>
       </c>
       <c r="V125" t="n">
-        <v>2557</v>
+        <v>2568</v>
       </c>
       <c r="W125" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
@@ -10339,16 +10339,16 @@
         <v>894</v>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M126" t="n">
         <v>2720</v>
       </c>
       <c r="N126" t="n">
-        <v>26473</v>
+        <v>26481</v>
       </c>
       <c r="O126" t="n">
-        <v>12382</v>
+        <v>12374</v>
       </c>
       <c r="P126" t="n">
         <v>0</v>
@@ -10360,16 +10360,16 @@
         <v>7962</v>
       </c>
       <c r="S126" t="n">
-        <v>4420</v>
+        <v>4412</v>
       </c>
       <c r="T126" t="n">
-        <v>3715</v>
+        <v>3712</v>
       </c>
       <c r="U126" t="n">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="V126" t="n">
-        <v>-1152</v>
+        <v>-1156</v>
       </c>
       <c r="W126" t="n">
         <v>-9.300000000000001</v>
@@ -10417,16 +10417,16 @@
         <v>1152</v>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M127" t="n">
         <v>2653</v>
       </c>
       <c r="N127" t="n">
-        <v>24848</v>
+        <v>24858</v>
       </c>
       <c r="O127" t="n">
-        <v>13052</v>
+        <v>13042</v>
       </c>
       <c r="P127" t="n">
         <v>0</v>
@@ -10438,19 +10438,19 @@
         <v>6061</v>
       </c>
       <c r="S127" t="n">
-        <v>6991</v>
+        <v>6981</v>
       </c>
       <c r="T127" t="n">
-        <v>3916</v>
+        <v>3913</v>
       </c>
       <c r="U127" t="n">
-        <v>1958</v>
+        <v>1956</v>
       </c>
       <c r="V127" t="n">
-        <v>1118</v>
+        <v>1112</v>
       </c>
       <c r="W127" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
@@ -10499,16 +10499,16 @@
         <v>1152</v>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M128" t="n">
         <v>3411</v>
       </c>
       <c r="N128" t="n">
-        <v>24098</v>
+        <v>24110</v>
       </c>
       <c r="O128" t="n">
-        <v>13802</v>
+        <v>13790</v>
       </c>
       <c r="P128" t="n">
         <v>0</v>
@@ -10520,19 +10520,19 @@
         <v>6061</v>
       </c>
       <c r="S128" t="n">
-        <v>7741</v>
+        <v>7729</v>
       </c>
       <c r="T128" t="n">
-        <v>4141</v>
+        <v>4137</v>
       </c>
       <c r="U128" t="n">
-        <v>2070</v>
+        <v>2068</v>
       </c>
       <c r="V128" t="n">
-        <v>1530</v>
+        <v>1524</v>
       </c>
       <c r="W128" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="X128" t="inlineStr">
         <is>
@@ -10581,16 +10581,16 @@
         <v>1139</v>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M129" t="n">
         <v>2615</v>
       </c>
       <c r="N129" t="n">
-        <v>25389</v>
+        <v>25398</v>
       </c>
       <c r="O129" t="n">
-        <v>11961</v>
+        <v>11952</v>
       </c>
       <c r="P129" t="n">
         <v>0</v>
@@ -10602,16 +10602,16 @@
         <v>6061</v>
       </c>
       <c r="S129" t="n">
-        <v>5900</v>
+        <v>5891</v>
       </c>
       <c r="T129" t="n">
-        <v>3588</v>
+        <v>3586</v>
       </c>
       <c r="U129" t="n">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="V129" t="n">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="W129" t="n">
         <v>4.3</v>
@@ -10909,16 +10909,16 @@
         <v>1108</v>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M133" t="n">
         <v>2520</v>
       </c>
       <c r="N133" t="n">
-        <v>22618</v>
+        <v>22626</v>
       </c>
       <c r="O133" t="n">
-        <v>13388</v>
+        <v>13380</v>
       </c>
       <c r="P133" t="n">
         <v>0</v>
@@ -10930,16 +10930,16 @@
         <v>6061</v>
       </c>
       <c r="S133" t="n">
-        <v>7327</v>
+        <v>7319</v>
       </c>
       <c r="T133" t="n">
-        <v>4016</v>
+        <v>4014</v>
       </c>
       <c r="U133" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="V133" t="n">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="W133" t="n">
         <v>9.699999999999999</v>
@@ -11079,10 +11079,10 @@
         <v>2023</v>
       </c>
       <c r="N135" t="n">
-        <v>16283</v>
+        <v>16263</v>
       </c>
       <c r="O135" t="n">
-        <v>12617</v>
+        <v>12637</v>
       </c>
       <c r="P135" t="n">
         <v>2972</v>
@@ -11094,19 +11094,19 @@
         <v>5720</v>
       </c>
       <c r="S135" t="n">
-        <v>6425</v>
+        <v>6445</v>
       </c>
       <c r="T135" t="n">
-        <v>3785</v>
+        <v>3791</v>
       </c>
       <c r="U135" t="n">
-        <v>1893</v>
+        <v>1896</v>
       </c>
       <c r="V135" t="n">
-        <v>747</v>
+        <v>758</v>
       </c>
       <c r="W135" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="X135" t="inlineStr">
         <is>
@@ -11155,16 +11155,16 @@
         <v>550</v>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M136" t="n">
         <v>2151</v>
       </c>
       <c r="N136" t="n">
-        <v>15464</v>
+        <v>15474</v>
       </c>
       <c r="O136" t="n">
-        <v>8436</v>
+        <v>8426</v>
       </c>
       <c r="P136" t="n">
         <v>0</v>
@@ -11176,19 +11176,19 @@
         <v>4287</v>
       </c>
       <c r="S136" t="n">
-        <v>4149</v>
+        <v>4139</v>
       </c>
       <c r="T136" t="n">
-        <v>2531</v>
+        <v>2528</v>
       </c>
       <c r="U136" t="n">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="V136" t="n">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="W136" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="X136" t="inlineStr"/>
     </row>
@@ -11233,16 +11233,16 @@
         <v>550</v>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M137" t="n">
         <v>2151</v>
       </c>
       <c r="N137" t="n">
-        <v>15031</v>
+        <v>15042</v>
       </c>
       <c r="O137" t="n">
-        <v>8869</v>
+        <v>8858</v>
       </c>
       <c r="P137" t="n">
         <v>0</v>
@@ -11254,19 +11254,19 @@
         <v>4287</v>
       </c>
       <c r="S137" t="n">
-        <v>4582</v>
+        <v>4571</v>
       </c>
       <c r="T137" t="n">
-        <v>2661</v>
+        <v>2657</v>
       </c>
       <c r="U137" t="n">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="V137" t="n">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="W137" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="X137" t="inlineStr"/>
     </row>
@@ -11311,16 +11311,16 @@
         <v>550</v>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M138" t="n">
         <v>2151</v>
       </c>
       <c r="N138" t="n">
-        <v>15444</v>
+        <v>15454</v>
       </c>
       <c r="O138" t="n">
-        <v>8456</v>
+        <v>8446</v>
       </c>
       <c r="P138" t="n">
         <v>0</v>
@@ -11332,19 +11332,19 @@
         <v>4287</v>
       </c>
       <c r="S138" t="n">
-        <v>4169</v>
+        <v>4159</v>
       </c>
       <c r="T138" t="n">
-        <v>2537</v>
+        <v>2534</v>
       </c>
       <c r="U138" t="n">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="V138" t="n">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="W138" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="X138" t="inlineStr"/>
     </row>
@@ -11395,10 +11395,10 @@
         <v>1463</v>
       </c>
       <c r="N139" t="n">
-        <v>11736</v>
+        <v>11716</v>
       </c>
       <c r="O139" t="n">
-        <v>9164</v>
+        <v>9184</v>
       </c>
       <c r="P139" t="n">
         <v>3956</v>
@@ -11410,19 +11410,19 @@
         <v>4605</v>
       </c>
       <c r="S139" t="n">
-        <v>4803</v>
+        <v>4823</v>
       </c>
       <c r="T139" t="n">
-        <v>2749</v>
+        <v>2755</v>
       </c>
       <c r="U139" t="n">
-        <v>1375</v>
+        <v>1378</v>
       </c>
       <c r="V139" t="n">
-        <v>679</v>
+        <v>690</v>
       </c>
       <c r="W139" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X139" t="inlineStr">
         <is>
@@ -11477,10 +11477,10 @@
         <v>1463</v>
       </c>
       <c r="N140" t="n">
-        <v>11735</v>
+        <v>11715</v>
       </c>
       <c r="O140" t="n">
-        <v>9165</v>
+        <v>9185</v>
       </c>
       <c r="P140" t="n">
         <v>2911</v>
@@ -11492,19 +11492,19 @@
         <v>4605</v>
       </c>
       <c r="S140" t="n">
-        <v>4149</v>
+        <v>4169</v>
       </c>
       <c r="T140" t="n">
-        <v>2750</v>
+        <v>2756</v>
       </c>
       <c r="U140" t="n">
-        <v>1375</v>
+        <v>1378</v>
       </c>
       <c r="V140" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="W140" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="X140" t="inlineStr">
         <is>
@@ -11559,10 +11559,10 @@
         <v>1393</v>
       </c>
       <c r="N141" t="n">
-        <v>11025</v>
+        <v>11005</v>
       </c>
       <c r="O141" t="n">
-        <v>8875</v>
+        <v>8895</v>
       </c>
       <c r="P141" t="n">
         <v>4740</v>
@@ -11574,19 +11574,19 @@
         <v>3802</v>
       </c>
       <c r="S141" t="n">
-        <v>2833</v>
+        <v>2853</v>
       </c>
       <c r="T141" t="n">
-        <v>2662</v>
+        <v>2668</v>
       </c>
       <c r="U141" t="n">
-        <v>1331</v>
+        <v>1334</v>
       </c>
       <c r="V141" t="n">
-        <v>-1161</v>
+        <v>-1150</v>
       </c>
       <c r="W141" t="n">
-        <v>-13.1</v>
+        <v>-12.9</v>
       </c>
       <c r="X141" t="inlineStr">
         <is>
@@ -11641,10 +11641,10 @@
         <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>9825</v>
+        <v>9805</v>
       </c>
       <c r="O142" t="n">
-        <v>10075</v>
+        <v>10095</v>
       </c>
       <c r="P142" t="n">
         <v>3133</v>
@@ -11656,19 +11656,19 @@
         <v>3802</v>
       </c>
       <c r="S142" t="n">
-        <v>7439</v>
+        <v>7459</v>
       </c>
       <c r="T142" t="n">
-        <v>3022</v>
+        <v>3028</v>
       </c>
       <c r="U142" t="n">
-        <v>1511</v>
+        <v>1514</v>
       </c>
       <c r="V142" t="n">
-        <v>2905</v>
+        <v>2916</v>
       </c>
       <c r="W142" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="X142" t="inlineStr">
         <is>
@@ -11873,16 +11873,16 @@
         <v>623</v>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M145" t="n">
         <v>1043</v>
       </c>
       <c r="N145" t="n">
-        <v>9471</v>
+        <v>9478</v>
       </c>
       <c r="O145" t="n">
-        <v>5429</v>
+        <v>5422</v>
       </c>
       <c r="P145" t="n">
         <v>0</v>
@@ -11894,19 +11894,19 @@
         <v>3254</v>
       </c>
       <c r="S145" t="n">
-        <v>2175</v>
+        <v>2168</v>
       </c>
       <c r="T145" t="n">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="U145" t="n">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="V145" t="n">
-        <v>-268</v>
+        <v>-272</v>
       </c>
       <c r="W145" t="n">
-        <v>-4.9</v>
+        <v>-5</v>
       </c>
       <c r="X145" t="inlineStr"/>
     </row>
@@ -11951,16 +11951,16 @@
         <v>623</v>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M146" t="n">
         <v>1043</v>
       </c>
       <c r="N146" t="n">
-        <v>10201</v>
+        <v>10221</v>
       </c>
       <c r="O146" t="n">
-        <v>4699</v>
+        <v>4679</v>
       </c>
       <c r="P146" t="n">
         <v>0</v>
@@ -11972,19 +11972,19 @@
         <v>3254</v>
       </c>
       <c r="S146" t="n">
-        <v>1445</v>
+        <v>1425</v>
       </c>
       <c r="T146" t="n">
-        <v>1410</v>
+        <v>1404</v>
       </c>
       <c r="U146" t="n">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="V146" t="n">
-        <v>-670</v>
+        <v>-681</v>
       </c>
       <c r="W146" t="n">
-        <v>-14.2</v>
+        <v>-14.5</v>
       </c>
       <c r="X146" t="inlineStr"/>
     </row>
@@ -12029,16 +12029,16 @@
         <v>623</v>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M147" t="n">
         <v>1043</v>
       </c>
       <c r="N147" t="n">
-        <v>9423</v>
+        <v>9432</v>
       </c>
       <c r="O147" t="n">
-        <v>5477</v>
+        <v>5468</v>
       </c>
       <c r="P147" t="n">
         <v>0</v>
@@ -12050,19 +12050,19 @@
         <v>3254</v>
       </c>
       <c r="S147" t="n">
-        <v>2223</v>
+        <v>2214</v>
       </c>
       <c r="T147" t="n">
-        <v>1643</v>
+        <v>1640</v>
       </c>
       <c r="U147" t="n">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="V147" t="n">
-        <v>-242</v>
+        <v>-247</v>
       </c>
       <c r="W147" t="n">
-        <v>-4.4</v>
+        <v>-4.5</v>
       </c>
       <c r="X147" t="inlineStr"/>
     </row>
@@ -12107,16 +12107,16 @@
         <v>600</v>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M148" t="n">
         <v>973</v>
       </c>
       <c r="N148" t="n">
-        <v>8920</v>
+        <v>8929</v>
       </c>
       <c r="O148" t="n">
-        <v>4980</v>
+        <v>4971</v>
       </c>
       <c r="P148" t="n">
         <v>0</v>
@@ -12128,19 +12128,19 @@
         <v>2564</v>
       </c>
       <c r="S148" t="n">
-        <v>2416</v>
+        <v>2407</v>
       </c>
       <c r="T148" t="n">
-        <v>1494</v>
+        <v>1491</v>
       </c>
       <c r="U148" t="n">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="V148" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="W148" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="X148" t="inlineStr"/>
     </row>
@@ -12263,16 +12263,16 @@
         <v>587</v>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M150" t="n">
         <v>935</v>
       </c>
       <c r="N150" t="n">
-        <v>7815</v>
+        <v>7825</v>
       </c>
       <c r="O150" t="n">
-        <v>5535</v>
+        <v>5525</v>
       </c>
       <c r="P150" t="n">
         <v>0</v>
@@ -12284,19 +12284,19 @@
         <v>2564</v>
       </c>
       <c r="S150" t="n">
-        <v>2971</v>
+        <v>2961</v>
       </c>
       <c r="T150" t="n">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="U150" t="n">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="V150" t="n">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="W150" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X150" t="inlineStr"/>
     </row>
@@ -12420,16 +12420,16 @@
         <v>692</v>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M152" t="n">
         <v>1611</v>
       </c>
       <c r="N152" t="n">
-        <v>3961</v>
+        <v>3970</v>
       </c>
       <c r="O152" t="n">
-        <v>-3961</v>
+        <v>-3970</v>
       </c>
       <c r="P152" t="n">
         <v>0</v>
@@ -12441,16 +12441,16 @@
         <v>3652</v>
       </c>
       <c r="S152" t="n">
-        <v>-7613</v>
+        <v>-7622</v>
       </c>
       <c r="T152" t="n">
-        <v>-1188</v>
+        <v>-1191</v>
       </c>
       <c r="U152" t="n">
-        <v>-594</v>
+        <v>-596</v>
       </c>
       <c r="V152" t="n">
-        <v>-5831</v>
+        <v>-5836</v>
       </c>
       <c r="X152" t="inlineStr"/>
     </row>
@@ -12604,16 +12604,16 @@
         <v>1895</v>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M155" t="n">
         <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>34015</v>
+        <v>34023</v>
       </c>
       <c r="O155" t="n">
-        <v>36197</v>
+        <v>36189</v>
       </c>
       <c r="P155" t="n">
         <v>0</v>
@@ -12625,16 +12625,16 @@
         <v>7340</v>
       </c>
       <c r="S155" t="n">
-        <v>28857</v>
+        <v>28849</v>
       </c>
       <c r="T155" t="n">
-        <v>10859</v>
+        <v>10857</v>
       </c>
       <c r="U155" t="n">
-        <v>5430</v>
+        <v>5428</v>
       </c>
       <c r="V155" t="n">
-        <v>12568</v>
+        <v>12564</v>
       </c>
       <c r="W155" t="n">
         <v>34.7</v>
@@ -12688,10 +12688,10 @@
         <v>4753</v>
       </c>
       <c r="N156" t="n">
-        <v>37725</v>
+        <v>37705</v>
       </c>
       <c r="O156" t="n">
-        <v>30175</v>
+        <v>30195</v>
       </c>
       <c r="P156" t="n">
         <v>5915</v>
@@ -12703,16 +12703,16 @@
         <v>8494</v>
       </c>
       <c r="S156" t="n">
-        <v>26016</v>
+        <v>26036</v>
       </c>
       <c r="T156" t="n">
-        <v>9052</v>
+        <v>9058</v>
       </c>
       <c r="U156" t="n">
-        <v>4526</v>
+        <v>4529</v>
       </c>
       <c r="V156" t="n">
-        <v>12437</v>
+        <v>12448</v>
       </c>
       <c r="W156" t="n">
         <v>41.2</v>
@@ -12767,13 +12767,13 @@
         <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>8614</v>
+        <v>8605</v>
       </c>
       <c r="N157" t="n">
-        <v>29588</v>
+        <v>29579</v>
       </c>
       <c r="O157" t="n">
-        <v>15105</v>
+        <v>15114</v>
       </c>
       <c r="P157" t="n">
         <v>0</v>
@@ -12785,16 +12785,16 @@
         <v>7340</v>
       </c>
       <c r="S157" t="n">
-        <v>7765</v>
+        <v>7774</v>
       </c>
       <c r="T157" t="n">
-        <v>4532</v>
+        <v>4534</v>
       </c>
       <c r="U157" t="n">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="V157" t="n">
-        <v>968</v>
+        <v>973</v>
       </c>
       <c r="W157" t="n">
         <v>6.4</v>
@@ -12846,10 +12846,10 @@
         <v>1308</v>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M158" t="n">
-        <v>11743</v>
+        <v>11734</v>
       </c>
       <c r="N158" t="n">
         <v>33620</v>
@@ -12928,16 +12928,16 @@
         <v>1308</v>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M159" t="n">
-        <v>11743</v>
+        <v>11734</v>
       </c>
       <c r="N159" t="n">
-        <v>34030</v>
+        <v>34027</v>
       </c>
       <c r="O159" t="n">
-        <v>10663</v>
+        <v>10666</v>
       </c>
       <c r="P159" t="n">
         <v>0</v>
@@ -12949,16 +12949,16 @@
         <v>7340</v>
       </c>
       <c r="S159" t="n">
-        <v>3323</v>
+        <v>3326</v>
       </c>
       <c r="T159" t="n">
-        <v>3199</v>
+        <v>3200</v>
       </c>
       <c r="U159" t="n">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="V159" t="n">
-        <v>-1475</v>
+        <v>-1474</v>
       </c>
       <c r="W159" t="n">
         <v>-13.8</v>
@@ -13013,13 +13013,13 @@
         <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>8616</v>
+        <v>8604</v>
       </c>
       <c r="N160" t="n">
-        <v>30480</v>
+        <v>30468</v>
       </c>
       <c r="O160" t="n">
-        <v>14213</v>
+        <v>14225</v>
       </c>
       <c r="P160" t="n">
         <v>0</v>
@@ -13031,16 +13031,16 @@
         <v>7340</v>
       </c>
       <c r="S160" t="n">
-        <v>6873</v>
+        <v>6885</v>
       </c>
       <c r="T160" t="n">
-        <v>4264</v>
+        <v>4268</v>
       </c>
       <c r="U160" t="n">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="V160" t="n">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="W160" t="n">
         <v>3.4</v>
@@ -13128,10 +13128,10 @@
         <v>13522</v>
       </c>
       <c r="N162" t="n">
-        <v>86957</v>
+        <v>86937</v>
       </c>
       <c r="O162" t="n">
-        <v>63283</v>
+        <v>63303</v>
       </c>
       <c r="P162" t="n">
         <v>3015</v>
@@ -13143,16 +13143,16 @@
         <v>26964</v>
       </c>
       <c r="S162" t="n">
-        <v>36103</v>
+        <v>36123</v>
       </c>
       <c r="T162" t="n">
-        <v>18985</v>
+        <v>18991</v>
       </c>
       <c r="U162" t="n">
-        <v>9492</v>
+        <v>9495</v>
       </c>
       <c r="V162" t="n">
-        <v>7626</v>
+        <v>7637</v>
       </c>
       <c r="W162" t="n">
         <v>12.1</v>
@@ -13210,10 +13210,10 @@
         <v>10103</v>
       </c>
       <c r="N163" t="n">
-        <v>81177</v>
+        <v>81157</v>
       </c>
       <c r="O163" t="n">
-        <v>63148</v>
+        <v>63168</v>
       </c>
       <c r="P163" t="n">
         <v>3666</v>
@@ -13225,16 +13225,16 @@
         <v>27107</v>
       </c>
       <c r="S163" t="n">
-        <v>35874</v>
+        <v>35894</v>
       </c>
       <c r="T163" t="n">
-        <v>18944</v>
+        <v>18950</v>
       </c>
       <c r="U163" t="n">
-        <v>9472</v>
+        <v>9475</v>
       </c>
       <c r="V163" t="n">
-        <v>7457</v>
+        <v>7468</v>
       </c>
       <c r="W163" t="n">
         <v>11.8</v>
@@ -13286,16 +13286,16 @@
         <v>2804</v>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>6703</v>
       </c>
       <c r="M164" t="n">
         <v>10971</v>
       </c>
       <c r="N164" t="n">
-        <v>77550</v>
+        <v>77530</v>
       </c>
       <c r="O164" t="n">
-        <v>44350</v>
+        <v>44370</v>
       </c>
       <c r="P164" t="n">
         <v>0</v>
@@ -13307,16 +13307,16 @@
         <v>16933</v>
       </c>
       <c r="S164" t="n">
-        <v>33909</v>
+        <v>33929</v>
       </c>
       <c r="T164" t="n">
-        <v>13305</v>
+        <v>13311</v>
       </c>
       <c r="U164" t="n">
-        <v>6652</v>
+        <v>6656</v>
       </c>
       <c r="V164" t="n">
-        <v>13952</v>
+        <v>13962</v>
       </c>
       <c r="W164" t="n">
         <v>31.5</v>
@@ -13374,10 +13374,10 @@
         <v>8506</v>
       </c>
       <c r="N165" t="n">
-        <v>68038</v>
+        <v>68018</v>
       </c>
       <c r="O165" t="n">
-        <v>53482</v>
+        <v>53502</v>
       </c>
       <c r="P165" t="n">
         <v>18369</v>
@@ -13389,16 +13389,16 @@
         <v>16933</v>
       </c>
       <c r="S165" t="n">
-        <v>21080</v>
+        <v>21100</v>
       </c>
       <c r="T165" t="n">
-        <v>16045</v>
+        <v>16051</v>
       </c>
       <c r="U165" t="n">
-        <v>8022</v>
+        <v>8025</v>
       </c>
       <c r="V165" t="n">
-        <v>-2987</v>
+        <v>-2976</v>
       </c>
       <c r="W165" t="n">
         <v>-5.6</v>
@@ -13456,10 +13456,10 @@
         <v>10071</v>
       </c>
       <c r="N166" t="n">
-        <v>64980</v>
+        <v>64960</v>
       </c>
       <c r="O166" t="n">
-        <v>46920</v>
+        <v>46940</v>
       </c>
       <c r="P166" t="n">
         <v>4242</v>
@@ -13471,16 +13471,16 @@
         <v>17189</v>
       </c>
       <c r="S166" t="n">
-        <v>28188</v>
+        <v>28208</v>
       </c>
       <c r="T166" t="n">
-        <v>14076</v>
+        <v>14082</v>
       </c>
       <c r="U166" t="n">
-        <v>7038</v>
+        <v>7041</v>
       </c>
       <c r="V166" t="n">
-        <v>7074</v>
+        <v>7085</v>
       </c>
       <c r="W166" t="n">
         <v>15.1</v>
@@ -13538,10 +13538,10 @@
         <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>48274</v>
+        <v>48254</v>
       </c>
       <c r="O167" t="n">
-        <v>49626</v>
+        <v>49646</v>
       </c>
       <c r="P167" t="n">
         <v>3099</v>
@@ -13553,16 +13553,16 @@
         <v>13664</v>
       </c>
       <c r="S167" t="n">
-        <v>35362</v>
+        <v>35382</v>
       </c>
       <c r="T167" t="n">
-        <v>14888</v>
+        <v>14894</v>
       </c>
       <c r="U167" t="n">
-        <v>7444</v>
+        <v>7447</v>
       </c>
       <c r="V167" t="n">
-        <v>13030</v>
+        <v>13041</v>
       </c>
       <c r="W167" t="n">
         <v>26.3</v>
@@ -13620,10 +13620,10 @@
         <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>47767</v>
+        <v>47747</v>
       </c>
       <c r="O168" t="n">
-        <v>49133</v>
+        <v>49153</v>
       </c>
       <c r="P168" t="n">
         <v>2948</v>
@@ -13635,16 +13635,16 @@
         <v>19034</v>
       </c>
       <c r="S168" t="n">
-        <v>29850</v>
+        <v>29870</v>
       </c>
       <c r="T168" t="n">
-        <v>14740</v>
+        <v>14746</v>
       </c>
       <c r="U168" t="n">
-        <v>7370</v>
+        <v>7373</v>
       </c>
       <c r="V168" t="n">
-        <v>7740</v>
+        <v>7751</v>
       </c>
       <c r="W168" t="n">
         <v>15.8</v>
@@ -13702,10 +13702,10 @@
         <v>2774</v>
       </c>
       <c r="N169" t="n">
-        <v>48599</v>
+        <v>48579</v>
       </c>
       <c r="O169" t="n">
-        <v>45301</v>
+        <v>45321</v>
       </c>
       <c r="P169" t="n">
         <v>3932</v>
@@ -13717,16 +13717,16 @@
         <v>13482</v>
       </c>
       <c r="S169" t="n">
-        <v>32087</v>
+        <v>32107</v>
       </c>
       <c r="T169" t="n">
-        <v>13590</v>
+        <v>13596</v>
       </c>
       <c r="U169" t="n">
-        <v>6795</v>
+        <v>6798</v>
       </c>
       <c r="V169" t="n">
-        <v>11702</v>
+        <v>11713</v>
       </c>
       <c r="W169" t="n">
         <v>25.8</v>
@@ -13784,10 +13784,10 @@
         <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>45799</v>
+        <v>45779</v>
       </c>
       <c r="O170" t="n">
-        <v>48101</v>
+        <v>48121</v>
       </c>
       <c r="P170" t="n">
         <v>4008</v>
@@ -13799,16 +13799,16 @@
         <v>13482</v>
       </c>
       <c r="S170" t="n">
-        <v>34311</v>
+        <v>34331</v>
       </c>
       <c r="T170" t="n">
-        <v>14430</v>
+        <v>14436</v>
       </c>
       <c r="U170" t="n">
-        <v>7215</v>
+        <v>7218</v>
       </c>
       <c r="V170" t="n">
-        <v>12666</v>
+        <v>12677</v>
       </c>
       <c r="W170" t="n">
         <v>26.3</v>
@@ -13860,16 +13860,16 @@
         <v>2151</v>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>4704</v>
       </c>
       <c r="M171" t="n">
         <v>16074</v>
       </c>
       <c r="N171" t="n">
-        <v>66320</v>
+        <v>66300</v>
       </c>
       <c r="O171" t="n">
-        <v>27200</v>
+        <v>27220</v>
       </c>
       <c r="P171" t="n">
         <v>0</v>
@@ -13881,19 +13881,19 @@
         <v>17660</v>
       </c>
       <c r="S171" t="n">
-        <v>11056</v>
+        <v>11076</v>
       </c>
       <c r="T171" t="n">
-        <v>8160</v>
+        <v>8166</v>
       </c>
       <c r="U171" t="n">
-        <v>4080</v>
+        <v>4083</v>
       </c>
       <c r="V171" t="n">
-        <v>-1184</v>
+        <v>-1173</v>
       </c>
       <c r="W171" t="n">
-        <v>-4.4</v>
+        <v>-4.3</v>
       </c>
       <c r="X171" t="inlineStr">
         <is>
@@ -13948,10 +13948,10 @@
         <v>8361</v>
       </c>
       <c r="N172" t="n">
-        <v>54075</v>
+        <v>54055</v>
       </c>
       <c r="O172" t="n">
-        <v>38825</v>
+        <v>38845</v>
       </c>
       <c r="P172" t="n">
         <v>4020</v>
@@ -13963,16 +13963,16 @@
         <v>17660</v>
       </c>
       <c r="S172" t="n">
-        <v>21345</v>
+        <v>21365</v>
       </c>
       <c r="T172" t="n">
-        <v>11648</v>
+        <v>11654</v>
       </c>
       <c r="U172" t="n">
-        <v>5824</v>
+        <v>5827</v>
       </c>
       <c r="V172" t="n">
-        <v>3874</v>
+        <v>3885</v>
       </c>
       <c r="W172" t="n">
         <v>10</v>
@@ -14030,10 +14030,10 @@
         <v>17889</v>
       </c>
       <c r="N173" t="n">
-        <v>63133</v>
+        <v>63113</v>
       </c>
       <c r="O173" t="n">
-        <v>29767</v>
+        <v>29787</v>
       </c>
       <c r="P173" t="n">
         <v>3666</v>
@@ -14045,16 +14045,16 @@
         <v>17660</v>
       </c>
       <c r="S173" t="n">
-        <v>11841</v>
+        <v>11861</v>
       </c>
       <c r="T173" t="n">
-        <v>8930</v>
+        <v>8936</v>
       </c>
       <c r="U173" t="n">
-        <v>4465</v>
+        <v>4468</v>
       </c>
       <c r="V173" t="n">
-        <v>-1554</v>
+        <v>-1543</v>
       </c>
       <c r="W173" t="n">
         <v>-5.2</v>
@@ -14112,10 +14112,10 @@
         <v>6293</v>
       </c>
       <c r="N174" t="n">
-        <v>50602</v>
+        <v>50582</v>
       </c>
       <c r="O174" t="n">
-        <v>39298</v>
+        <v>39318</v>
       </c>
       <c r="P174" t="n">
         <v>5086</v>
@@ -14127,16 +14127,16 @@
         <v>11912</v>
       </c>
       <c r="S174" t="n">
-        <v>27599</v>
+        <v>27619</v>
       </c>
       <c r="T174" t="n">
-        <v>11789</v>
+        <v>11795</v>
       </c>
       <c r="U174" t="n">
-        <v>5895</v>
+        <v>5898</v>
       </c>
       <c r="V174" t="n">
-        <v>9915</v>
+        <v>9926</v>
       </c>
       <c r="W174" t="n">
         <v>25.2</v>
@@ -14194,10 +14194,10 @@
         <v>6266</v>
       </c>
       <c r="N175" t="n">
-        <v>50402</v>
+        <v>50382</v>
       </c>
       <c r="O175" t="n">
-        <v>39118</v>
+        <v>39138</v>
       </c>
       <c r="P175" t="n">
         <v>12800</v>
@@ -14209,16 +14209,16 @@
         <v>17189</v>
       </c>
       <c r="S175" t="n">
-        <v>17978</v>
+        <v>17998</v>
       </c>
       <c r="T175" t="n">
-        <v>11735</v>
+        <v>11741</v>
       </c>
       <c r="U175" t="n">
-        <v>5868</v>
+        <v>5871</v>
       </c>
       <c r="V175" t="n">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="W175" t="n">
         <v>1</v>
@@ -14276,10 +14276,10 @@
         <v>6266</v>
       </c>
       <c r="N176" t="n">
-        <v>50364</v>
+        <v>50344</v>
       </c>
       <c r="O176" t="n">
-        <v>39156</v>
+        <v>39176</v>
       </c>
       <c r="P176" t="n">
         <v>5859</v>
@@ -14291,16 +14291,16 @@
         <v>17189</v>
       </c>
       <c r="S176" t="n">
-        <v>21258</v>
+        <v>21278</v>
       </c>
       <c r="T176" t="n">
-        <v>11747</v>
+        <v>11753</v>
       </c>
       <c r="U176" t="n">
-        <v>5873</v>
+        <v>5876</v>
       </c>
       <c r="V176" t="n">
-        <v>3638</v>
+        <v>3649</v>
       </c>
       <c r="W176" t="n">
         <v>9.300000000000001</v>
@@ -14358,10 +14358,10 @@
         <v>6223</v>
       </c>
       <c r="N177" t="n">
-        <v>50041</v>
+        <v>50021</v>
       </c>
       <c r="O177" t="n">
-        <v>38859</v>
+        <v>38879</v>
       </c>
       <c r="P177" t="n">
         <v>2948</v>
@@ -14373,16 +14373,16 @@
         <v>16167</v>
       </c>
       <c r="S177" t="n">
-        <v>22543</v>
+        <v>22563</v>
       </c>
       <c r="T177" t="n">
-        <v>11658</v>
+        <v>11664</v>
       </c>
       <c r="U177" t="n">
-        <v>5829</v>
+        <v>5832</v>
       </c>
       <c r="V177" t="n">
-        <v>5056</v>
+        <v>5067</v>
       </c>
       <c r="W177" t="n">
         <v>13</v>
@@ -14440,10 +14440,10 @@
         <v>0</v>
       </c>
       <c r="N178" t="n">
-        <v>43688</v>
+        <v>43668</v>
       </c>
       <c r="O178" t="n">
-        <v>44692</v>
+        <v>44712</v>
       </c>
       <c r="P178" t="n">
         <v>11906</v>
@@ -14455,19 +14455,19 @@
         <v>16933</v>
       </c>
       <c r="S178" t="n">
-        <v>20753</v>
+        <v>20773</v>
       </c>
       <c r="T178" t="n">
-        <v>13408</v>
+        <v>13414</v>
       </c>
       <c r="U178" t="n">
-        <v>6704</v>
+        <v>6707</v>
       </c>
       <c r="V178" t="n">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="W178" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="X178" t="inlineStr">
         <is>
@@ -14522,10 +14522,10 @@
         <v>6186</v>
       </c>
       <c r="N179" t="n">
-        <v>49711</v>
+        <v>49691</v>
       </c>
       <c r="O179" t="n">
-        <v>38664</v>
+        <v>38684</v>
       </c>
       <c r="P179" t="n">
         <v>0</v>
@@ -14537,16 +14537,16 @@
         <v>16167</v>
       </c>
       <c r="S179" t="n">
-        <v>24897</v>
+        <v>24917</v>
       </c>
       <c r="T179" t="n">
-        <v>11599</v>
+        <v>11605</v>
       </c>
       <c r="U179" t="n">
-        <v>5800</v>
+        <v>5803</v>
       </c>
       <c r="V179" t="n">
-        <v>7498</v>
+        <v>7509</v>
       </c>
       <c r="W179" t="n">
         <v>19.4</v>
@@ -14604,10 +14604,10 @@
         <v>7925</v>
       </c>
       <c r="N180" t="n">
-        <v>51291</v>
+        <v>51271</v>
       </c>
       <c r="O180" t="n">
-        <v>36759</v>
+        <v>36779</v>
       </c>
       <c r="P180" t="n">
         <v>18370</v>
@@ -14619,19 +14619,19 @@
         <v>16933</v>
       </c>
       <c r="S180" t="n">
-        <v>4056</v>
+        <v>4076</v>
       </c>
       <c r="T180" t="n">
-        <v>11028</v>
+        <v>11034</v>
       </c>
       <c r="U180" t="n">
-        <v>5514</v>
+        <v>5517</v>
       </c>
       <c r="V180" t="n">
-        <v>-12486</v>
+        <v>-12475</v>
       </c>
       <c r="W180" t="n">
-        <v>-34</v>
+        <v>-33.9</v>
       </c>
       <c r="X180" t="inlineStr">
         <is>
@@ -14686,10 +14686,10 @@
         <v>6161</v>
       </c>
       <c r="N181" t="n">
-        <v>49515</v>
+        <v>49495</v>
       </c>
       <c r="O181" t="n">
-        <v>38505</v>
+        <v>38525</v>
       </c>
       <c r="P181" t="n">
         <v>4170</v>
@@ -14701,16 +14701,16 @@
         <v>16167</v>
       </c>
       <c r="S181" t="n">
-        <v>23167</v>
+        <v>23187</v>
       </c>
       <c r="T181" t="n">
-        <v>11552</v>
+        <v>11558</v>
       </c>
       <c r="U181" t="n">
-        <v>5776</v>
+        <v>5779</v>
       </c>
       <c r="V181" t="n">
-        <v>5840</v>
+        <v>5851</v>
       </c>
       <c r="W181" t="n">
         <v>15.2</v>
@@ -14768,10 +14768,10 @@
         <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>44992</v>
+        <v>44972</v>
       </c>
       <c r="O182" t="n">
-        <v>37908</v>
+        <v>37928</v>
       </c>
       <c r="P182" t="n">
         <v>2668</v>
@@ -14783,16 +14783,16 @@
         <v>11909</v>
       </c>
       <c r="S182" t="n">
-        <v>29381</v>
+        <v>29401</v>
       </c>
       <c r="T182" t="n">
-        <v>11372</v>
+        <v>11378</v>
       </c>
       <c r="U182" t="n">
-        <v>5686</v>
+        <v>5689</v>
       </c>
       <c r="V182" t="n">
-        <v>12322</v>
+        <v>12333</v>
       </c>
       <c r="W182" t="n">
         <v>32.5</v>
@@ -14850,10 +14850,10 @@
         <v>7409</v>
       </c>
       <c r="N183" t="n">
-        <v>47915</v>
+        <v>47895</v>
       </c>
       <c r="O183" t="n">
-        <v>34405</v>
+        <v>34425</v>
       </c>
       <c r="P183" t="n">
         <v>5592</v>
@@ -14865,19 +14865,19 @@
         <v>14537</v>
       </c>
       <c r="S183" t="n">
-        <v>18176</v>
+        <v>18196</v>
       </c>
       <c r="T183" t="n">
-        <v>10322</v>
+        <v>10328</v>
       </c>
       <c r="U183" t="n">
-        <v>5161</v>
+        <v>5164</v>
       </c>
       <c r="V183" t="n">
-        <v>2694</v>
+        <v>2705</v>
       </c>
       <c r="W183" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X183" t="inlineStr">
         <is>
@@ -14932,10 +14932,10 @@
         <v>7409</v>
       </c>
       <c r="N184" t="n">
-        <v>47880</v>
+        <v>47860</v>
       </c>
       <c r="O184" t="n">
-        <v>34440</v>
+        <v>34460</v>
       </c>
       <c r="P184" t="n">
         <v>2948</v>
@@ -14947,16 +14947,16 @@
         <v>14537</v>
       </c>
       <c r="S184" t="n">
-        <v>19455</v>
+        <v>19475</v>
       </c>
       <c r="T184" t="n">
-        <v>10332</v>
+        <v>10338</v>
       </c>
       <c r="U184" t="n">
-        <v>5166</v>
+        <v>5169</v>
       </c>
       <c r="V184" t="n">
-        <v>3957</v>
+        <v>3968</v>
       </c>
       <c r="W184" t="n">
         <v>11.5</v>
@@ -15014,10 +15014,10 @@
         <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>40471</v>
+        <v>40451</v>
       </c>
       <c r="O185" t="n">
-        <v>41849</v>
+        <v>41869</v>
       </c>
       <c r="P185" t="n">
         <v>1000</v>
@@ -15029,16 +15029,16 @@
         <v>14537</v>
       </c>
       <c r="S185" t="n">
-        <v>29012</v>
+        <v>29032</v>
       </c>
       <c r="T185" t="n">
-        <v>12555</v>
+        <v>12561</v>
       </c>
       <c r="U185" t="n">
-        <v>6277</v>
+        <v>6280</v>
       </c>
       <c r="V185" t="n">
-        <v>10180</v>
+        <v>10191</v>
       </c>
       <c r="W185" t="n">
         <v>24.3</v>
@@ -15096,10 +15096,10 @@
         <v>7409</v>
       </c>
       <c r="N186" t="n">
-        <v>47880</v>
+        <v>47860</v>
       </c>
       <c r="O186" t="n">
-        <v>34440</v>
+        <v>34460</v>
       </c>
       <c r="P186" t="n">
         <v>1000</v>
@@ -15111,19 +15111,19 @@
         <v>14537</v>
       </c>
       <c r="S186" t="n">
-        <v>21502</v>
+        <v>21522</v>
       </c>
       <c r="T186" t="n">
-        <v>10332</v>
+        <v>10338</v>
       </c>
       <c r="U186" t="n">
-        <v>5166</v>
+        <v>5169</v>
       </c>
       <c r="V186" t="n">
-        <v>6004</v>
+        <v>6015</v>
       </c>
       <c r="W186" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="X186" t="inlineStr">
         <is>
@@ -15178,10 +15178,10 @@
         <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>40471</v>
+        <v>40451</v>
       </c>
       <c r="O187" t="n">
-        <v>41849</v>
+        <v>41869</v>
       </c>
       <c r="P187" t="n">
         <v>2948</v>
@@ -15193,16 +15193,16 @@
         <v>14537</v>
       </c>
       <c r="S187" t="n">
-        <v>27063</v>
+        <v>27083</v>
       </c>
       <c r="T187" t="n">
-        <v>12555</v>
+        <v>12561</v>
       </c>
       <c r="U187" t="n">
-        <v>6277</v>
+        <v>6280</v>
       </c>
       <c r="V187" t="n">
-        <v>8231</v>
+        <v>8242</v>
       </c>
       <c r="W187" t="n">
         <v>19.7</v>
@@ -15260,10 +15260,10 @@
         <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>40471</v>
+        <v>40451</v>
       </c>
       <c r="O188" t="n">
-        <v>41849</v>
+        <v>41869</v>
       </c>
       <c r="P188" t="n">
         <v>4349</v>
@@ -15275,19 +15275,19 @@
         <v>14537</v>
       </c>
       <c r="S188" t="n">
-        <v>27762</v>
+        <v>27782</v>
       </c>
       <c r="T188" t="n">
-        <v>12555</v>
+        <v>12561</v>
       </c>
       <c r="U188" t="n">
-        <v>6277</v>
+        <v>6280</v>
       </c>
       <c r="V188" t="n">
-        <v>8930</v>
+        <v>8941</v>
       </c>
       <c r="W188" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="X188" t="inlineStr">
         <is>
@@ -15342,10 +15342,10 @@
         <v>7381</v>
       </c>
       <c r="N189" t="n">
-        <v>47760</v>
+        <v>47740</v>
       </c>
       <c r="O189" t="n">
-        <v>34247</v>
+        <v>34267</v>
       </c>
       <c r="P189" t="n">
         <v>0</v>
@@ -15357,16 +15357,16 @@
         <v>14537</v>
       </c>
       <c r="S189" t="n">
-        <v>22110</v>
+        <v>22130</v>
       </c>
       <c r="T189" t="n">
-        <v>10274</v>
+        <v>10280</v>
       </c>
       <c r="U189" t="n">
-        <v>5137</v>
+        <v>5140</v>
       </c>
       <c r="V189" t="n">
-        <v>6699</v>
+        <v>6710</v>
       </c>
       <c r="W189" t="n">
         <v>19.6</v>
@@ -15424,10 +15424,10 @@
         <v>7381</v>
       </c>
       <c r="N190" t="n">
-        <v>47803</v>
+        <v>47783</v>
       </c>
       <c r="O190" t="n">
-        <v>34204</v>
+        <v>34224</v>
       </c>
       <c r="P190" t="n">
         <v>5275</v>
@@ -15439,19 +15439,19 @@
         <v>14537</v>
       </c>
       <c r="S190" t="n">
-        <v>17592</v>
+        <v>17612</v>
       </c>
       <c r="T190" t="n">
-        <v>10261</v>
+        <v>10267</v>
       </c>
       <c r="U190" t="n">
-        <v>5131</v>
+        <v>5134</v>
       </c>
       <c r="V190" t="n">
-        <v>2200</v>
+        <v>2211</v>
       </c>
       <c r="W190" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X190" t="inlineStr">
         <is>
@@ -15506,10 +15506,10 @@
         <v>0</v>
       </c>
       <c r="N191" t="n">
-        <v>40519</v>
+        <v>40499</v>
       </c>
       <c r="O191" t="n">
-        <v>41488</v>
+        <v>41508</v>
       </c>
       <c r="P191" t="n">
         <v>2948</v>
@@ -15521,16 +15521,16 @@
         <v>14537</v>
       </c>
       <c r="S191" t="n">
-        <v>26503</v>
+        <v>26523</v>
       </c>
       <c r="T191" t="n">
-        <v>12446</v>
+        <v>12452</v>
       </c>
       <c r="U191" t="n">
-        <v>6223</v>
+        <v>6226</v>
       </c>
       <c r="V191" t="n">
-        <v>7833</v>
+        <v>7844</v>
       </c>
       <c r="W191" t="n">
         <v>18.9</v>
@@ -15588,10 +15588,10 @@
         <v>7381</v>
       </c>
       <c r="N192" t="n">
-        <v>47900</v>
+        <v>47880</v>
       </c>
       <c r="O192" t="n">
-        <v>34107</v>
+        <v>34127</v>
       </c>
       <c r="P192" t="n">
         <v>0</v>
@@ -15603,19 +15603,19 @@
         <v>14537</v>
       </c>
       <c r="S192" t="n">
-        <v>21670</v>
+        <v>21690</v>
       </c>
       <c r="T192" t="n">
-        <v>10232</v>
+        <v>10238</v>
       </c>
       <c r="U192" t="n">
-        <v>5116</v>
+        <v>5119</v>
       </c>
       <c r="V192" t="n">
-        <v>6322</v>
+        <v>6333</v>
       </c>
       <c r="W192" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="X192" t="inlineStr">
         <is>
@@ -15670,10 +15670,10 @@
         <v>5725</v>
       </c>
       <c r="N193" t="n">
-        <v>45938</v>
+        <v>45918</v>
       </c>
       <c r="O193" t="n">
-        <v>35848</v>
+        <v>35868</v>
       </c>
       <c r="P193" t="n">
         <v>3099</v>
@@ -15685,16 +15685,16 @@
         <v>14537</v>
       </c>
       <c r="S193" t="n">
-        <v>20512</v>
+        <v>20532</v>
       </c>
       <c r="T193" t="n">
-        <v>10754</v>
+        <v>10760</v>
       </c>
       <c r="U193" t="n">
-        <v>5377</v>
+        <v>5380</v>
       </c>
       <c r="V193" t="n">
-        <v>4380</v>
+        <v>4391</v>
       </c>
       <c r="W193" t="n">
         <v>12.2</v>
@@ -15752,10 +15752,10 @@
         <v>5663</v>
       </c>
       <c r="N194" t="n">
-        <v>45578</v>
+        <v>45558</v>
       </c>
       <c r="O194" t="n">
-        <v>35322</v>
+        <v>35342</v>
       </c>
       <c r="P194" t="n">
         <v>4136</v>
@@ -15767,16 +15767,16 @@
         <v>16167</v>
       </c>
       <c r="S194" t="n">
-        <v>19518</v>
+        <v>19538</v>
       </c>
       <c r="T194" t="n">
-        <v>10597</v>
+        <v>10603</v>
       </c>
       <c r="U194" t="n">
-        <v>5298</v>
+        <v>5301</v>
       </c>
       <c r="V194" t="n">
-        <v>3623</v>
+        <v>3634</v>
       </c>
       <c r="W194" t="n">
         <v>10.3</v>
@@ -15834,10 +15834,10 @@
         <v>0</v>
       </c>
       <c r="N195" t="n">
-        <v>38957</v>
+        <v>38937</v>
       </c>
       <c r="O195" t="n">
-        <v>40639</v>
+        <v>40659</v>
       </c>
       <c r="P195" t="n">
         <v>2948</v>
@@ -15849,16 +15849,16 @@
         <v>10587</v>
       </c>
       <c r="S195" t="n">
-        <v>29504</v>
+        <v>29524</v>
       </c>
       <c r="T195" t="n">
-        <v>12192</v>
+        <v>12198</v>
       </c>
       <c r="U195" t="n">
-        <v>6096</v>
+        <v>6099</v>
       </c>
       <c r="V195" t="n">
-        <v>11216</v>
+        <v>11227</v>
       </c>
       <c r="W195" t="n">
         <v>27.6</v>
@@ -15913,13 +15913,13 @@
         <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>11403</v>
+        <v>11382</v>
       </c>
       <c r="N196" t="n">
-        <v>50479</v>
+        <v>50438</v>
       </c>
       <c r="O196" t="n">
-        <v>29094</v>
+        <v>29135</v>
       </c>
       <c r="P196" t="n">
         <v>4965</v>
@@ -15931,19 +15931,19 @@
         <v>17660</v>
       </c>
       <c r="S196" t="n">
-        <v>11768</v>
+        <v>11809</v>
       </c>
       <c r="T196" t="n">
-        <v>8728</v>
+        <v>8740</v>
       </c>
       <c r="U196" t="n">
-        <v>4364</v>
+        <v>4370</v>
       </c>
       <c r="V196" t="n">
-        <v>-1324</v>
+        <v>-1302</v>
       </c>
       <c r="W196" t="n">
-        <v>-4.6</v>
+        <v>-4.5</v>
       </c>
       <c r="X196" t="inlineStr">
         <is>
@@ -15995,13 +15995,13 @@
         <v>0</v>
       </c>
       <c r="M197" t="n">
-        <v>11403</v>
+        <v>11382</v>
       </c>
       <c r="N197" t="n">
-        <v>50479</v>
+        <v>50438</v>
       </c>
       <c r="O197" t="n">
-        <v>29094</v>
+        <v>29135</v>
       </c>
       <c r="P197" t="n">
         <v>4386</v>
@@ -16013,19 +16013,19 @@
         <v>17660</v>
       </c>
       <c r="S197" t="n">
-        <v>11848</v>
+        <v>11889</v>
       </c>
       <c r="T197" t="n">
-        <v>8728</v>
+        <v>8740</v>
       </c>
       <c r="U197" t="n">
-        <v>4364</v>
+        <v>4370</v>
       </c>
       <c r="V197" t="n">
-        <v>-1244</v>
+        <v>-1222</v>
       </c>
       <c r="W197" t="n">
-        <v>-4.3</v>
+        <v>-4.2</v>
       </c>
       <c r="X197" t="inlineStr">
         <is>
@@ -16077,13 +16077,13 @@
         <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>11403</v>
+        <v>11382</v>
       </c>
       <c r="N198" t="n">
-        <v>50479</v>
+        <v>50438</v>
       </c>
       <c r="O198" t="n">
-        <v>29094</v>
+        <v>29135</v>
       </c>
       <c r="P198" t="n">
         <v>6009</v>
@@ -16095,19 +16095,19 @@
         <v>17660</v>
       </c>
       <c r="S198" t="n">
-        <v>11475</v>
+        <v>11516</v>
       </c>
       <c r="T198" t="n">
-        <v>8728</v>
+        <v>8740</v>
       </c>
       <c r="U198" t="n">
-        <v>4364</v>
+        <v>4370</v>
       </c>
       <c r="V198" t="n">
-        <v>-1617</v>
+        <v>-1595</v>
       </c>
       <c r="W198" t="n">
-        <v>-5.6</v>
+        <v>-5.5</v>
       </c>
       <c r="X198" t="inlineStr">
         <is>
@@ -16159,13 +16159,13 @@
         <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>11403</v>
+        <v>11382</v>
       </c>
       <c r="N199" t="n">
-        <v>50479</v>
+        <v>50438</v>
       </c>
       <c r="O199" t="n">
-        <v>29094</v>
+        <v>29135</v>
       </c>
       <c r="P199" t="n">
         <v>3794</v>
@@ -16177,19 +16177,19 @@
         <v>17660</v>
       </c>
       <c r="S199" t="n">
-        <v>11340</v>
+        <v>11381</v>
       </c>
       <c r="T199" t="n">
-        <v>8728</v>
+        <v>8740</v>
       </c>
       <c r="U199" t="n">
-        <v>4364</v>
+        <v>4370</v>
       </c>
       <c r="V199" t="n">
-        <v>-1752</v>
+        <v>-1730</v>
       </c>
       <c r="W199" t="n">
-        <v>-6</v>
+        <v>-5.9</v>
       </c>
       <c r="X199" t="inlineStr">
         <is>
@@ -16241,13 +16241,13 @@
         <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>11403</v>
+        <v>11382</v>
       </c>
       <c r="N200" t="n">
-        <v>50479</v>
+        <v>50438</v>
       </c>
       <c r="O200" t="n">
-        <v>29094</v>
+        <v>29135</v>
       </c>
       <c r="P200" t="n">
         <v>5464</v>
@@ -16259,19 +16259,19 @@
         <v>17660</v>
       </c>
       <c r="S200" t="n">
-        <v>10070</v>
+        <v>10111</v>
       </c>
       <c r="T200" t="n">
-        <v>8728</v>
+        <v>8740</v>
       </c>
       <c r="U200" t="n">
-        <v>4364</v>
+        <v>4370</v>
       </c>
       <c r="V200" t="n">
-        <v>-3022</v>
+        <v>-3000</v>
       </c>
       <c r="W200" t="n">
-        <v>-10.4</v>
+        <v>-10.3</v>
       </c>
       <c r="X200" t="inlineStr">
         <is>
@@ -16323,13 +16323,13 @@
         <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>11403</v>
+        <v>11382</v>
       </c>
       <c r="N201" t="n">
-        <v>50479</v>
+        <v>50438</v>
       </c>
       <c r="O201" t="n">
-        <v>29094</v>
+        <v>29135</v>
       </c>
       <c r="P201" t="n">
         <v>0</v>
@@ -16341,16 +16341,16 @@
         <v>17660</v>
       </c>
       <c r="S201" t="n">
-        <v>16484</v>
+        <v>16525</v>
       </c>
       <c r="T201" t="n">
-        <v>8728</v>
+        <v>8740</v>
       </c>
       <c r="U201" t="n">
-        <v>4364</v>
+        <v>4370</v>
       </c>
       <c r="V201" t="n">
-        <v>3392</v>
+        <v>3414</v>
       </c>
       <c r="W201" t="n">
         <v>11.7</v>
@@ -16405,13 +16405,13 @@
         <v>0</v>
       </c>
       <c r="M202" t="n">
-        <v>11403</v>
+        <v>11382</v>
       </c>
       <c r="N202" t="n">
-        <v>50479</v>
+        <v>50438</v>
       </c>
       <c r="O202" t="n">
-        <v>29094</v>
+        <v>29135</v>
       </c>
       <c r="P202" t="n">
         <v>2924</v>
@@ -16423,19 +16423,19 @@
         <v>17660</v>
       </c>
       <c r="S202" t="n">
-        <v>11610</v>
+        <v>11651</v>
       </c>
       <c r="T202" t="n">
-        <v>8728</v>
+        <v>8740</v>
       </c>
       <c r="U202" t="n">
-        <v>4364</v>
+        <v>4370</v>
       </c>
       <c r="V202" t="n">
-        <v>-1482</v>
+        <v>-1460</v>
       </c>
       <c r="W202" t="n">
-        <v>-5.1</v>
+        <v>-5</v>
       </c>
       <c r="X202" t="inlineStr">
         <is>
@@ -16487,13 +16487,13 @@
         <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>11403</v>
+        <v>11382</v>
       </c>
       <c r="N203" t="n">
-        <v>50479</v>
+        <v>50438</v>
       </c>
       <c r="O203" t="n">
-        <v>29094</v>
+        <v>29135</v>
       </c>
       <c r="P203" t="n">
         <v>8040</v>
@@ -16505,19 +16505,19 @@
         <v>17660</v>
       </c>
       <c r="S203" t="n">
-        <v>7894</v>
+        <v>7935</v>
       </c>
       <c r="T203" t="n">
-        <v>8728</v>
+        <v>8740</v>
       </c>
       <c r="U203" t="n">
-        <v>4364</v>
+        <v>4370</v>
       </c>
       <c r="V203" t="n">
-        <v>-5198</v>
+        <v>-5176</v>
       </c>
       <c r="W203" t="n">
-        <v>-17.9</v>
+        <v>-17.8</v>
       </c>
       <c r="X203" t="inlineStr">
         <is>
@@ -16569,13 +16569,13 @@
         <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>12995</v>
+        <v>12974</v>
       </c>
       <c r="N204" t="n">
-        <v>52071</v>
+        <v>52030</v>
       </c>
       <c r="O204" t="n">
-        <v>27502</v>
+        <v>27543</v>
       </c>
       <c r="P204" t="n">
         <v>3932</v>
@@ -16587,19 +16587,19 @@
         <v>17660</v>
       </c>
       <c r="S204" t="n">
-        <v>10110</v>
+        <v>10151</v>
       </c>
       <c r="T204" t="n">
-        <v>8251</v>
+        <v>8263</v>
       </c>
       <c r="U204" t="n">
-        <v>4125</v>
+        <v>4131</v>
       </c>
       <c r="V204" t="n">
-        <v>-2266</v>
+        <v>-2243</v>
       </c>
       <c r="W204" t="n">
-        <v>-8.199999999999999</v>
+        <v>-8.1</v>
       </c>
       <c r="X204" t="inlineStr">
         <is>
@@ -16651,13 +16651,13 @@
         <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>5833</v>
+        <v>5812</v>
       </c>
       <c r="N205" t="n">
-        <v>44909</v>
+        <v>44868</v>
       </c>
       <c r="O205" t="n">
-        <v>34664</v>
+        <v>34705</v>
       </c>
       <c r="P205" t="n">
         <v>1000</v>
@@ -16669,16 +16669,16 @@
         <v>17660</v>
       </c>
       <c r="S205" t="n">
-        <v>18703</v>
+        <v>18744</v>
       </c>
       <c r="T205" t="n">
-        <v>10399</v>
+        <v>10412</v>
       </c>
       <c r="U205" t="n">
-        <v>5200</v>
+        <v>5206</v>
       </c>
       <c r="V205" t="n">
-        <v>3104</v>
+        <v>3127</v>
       </c>
       <c r="W205" t="n">
         <v>9</v>
@@ -16733,13 +16733,13 @@
         <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>11403</v>
+        <v>11382</v>
       </c>
       <c r="N206" t="n">
-        <v>50479</v>
+        <v>50438</v>
       </c>
       <c r="O206" t="n">
-        <v>29094</v>
+        <v>29135</v>
       </c>
       <c r="P206" t="n">
         <v>0</v>
@@ -16751,19 +16751,19 @@
         <v>17660</v>
       </c>
       <c r="S206" t="n">
-        <v>16934</v>
+        <v>16975</v>
       </c>
       <c r="T206" t="n">
-        <v>8728</v>
+        <v>8740</v>
       </c>
       <c r="U206" t="n">
-        <v>4364</v>
+        <v>4370</v>
       </c>
       <c r="V206" t="n">
-        <v>3842</v>
+        <v>3864</v>
       </c>
       <c r="W206" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="X206" t="inlineStr">
         <is>
@@ -16815,13 +16815,13 @@
         <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>12995</v>
+        <v>12974</v>
       </c>
       <c r="N207" t="n">
-        <v>52071</v>
+        <v>52030</v>
       </c>
       <c r="O207" t="n">
-        <v>27502</v>
+        <v>27543</v>
       </c>
       <c r="P207" t="n">
         <v>3998</v>
@@ -16833,19 +16833,19 @@
         <v>17660</v>
       </c>
       <c r="S207" t="n">
-        <v>9344</v>
+        <v>9385</v>
       </c>
       <c r="T207" t="n">
-        <v>8251</v>
+        <v>8263</v>
       </c>
       <c r="U207" t="n">
-        <v>4125</v>
+        <v>4131</v>
       </c>
       <c r="V207" t="n">
-        <v>-3032</v>
+        <v>-3009</v>
       </c>
       <c r="W207" t="n">
-        <v>-11</v>
+        <v>-10.9</v>
       </c>
       <c r="X207" t="inlineStr">
         <is>
@@ -16897,13 +16897,13 @@
         <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>12995</v>
+        <v>12974</v>
       </c>
       <c r="N208" t="n">
-        <v>55800</v>
+        <v>55759</v>
       </c>
       <c r="O208" t="n">
-        <v>23773</v>
+        <v>23814</v>
       </c>
       <c r="P208" t="n">
         <v>3904</v>
@@ -16915,19 +16915,19 @@
         <v>17660</v>
       </c>
       <c r="S208" t="n">
-        <v>5609</v>
+        <v>5650</v>
       </c>
       <c r="T208" t="n">
-        <v>7132</v>
+        <v>7144</v>
       </c>
       <c r="U208" t="n">
-        <v>3566</v>
+        <v>3572</v>
       </c>
       <c r="V208" t="n">
-        <v>-5089</v>
+        <v>-5066</v>
       </c>
       <c r="W208" t="n">
-        <v>-21.4</v>
+        <v>-21.3</v>
       </c>
       <c r="X208" t="inlineStr">
         <is>
@@ -16979,13 +16979,13 @@
         <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>12995</v>
+        <v>12974</v>
       </c>
       <c r="N209" t="n">
-        <v>52071</v>
+        <v>52030</v>
       </c>
       <c r="O209" t="n">
-        <v>27502</v>
+        <v>27543</v>
       </c>
       <c r="P209" t="n">
         <v>0</v>
@@ -16997,19 +16997,19 @@
         <v>17660</v>
       </c>
       <c r="S209" t="n">
-        <v>14892</v>
+        <v>14933</v>
       </c>
       <c r="T209" t="n">
-        <v>8251</v>
+        <v>8263</v>
       </c>
       <c r="U209" t="n">
-        <v>4125</v>
+        <v>4131</v>
       </c>
       <c r="V209" t="n">
-        <v>2516</v>
+        <v>2539</v>
       </c>
       <c r="W209" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X209" t="inlineStr">
         <is>
@@ -17061,13 +17061,13 @@
         <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>5833</v>
+        <v>5812</v>
       </c>
       <c r="N210" t="n">
-        <v>44909</v>
+        <v>44868</v>
       </c>
       <c r="O210" t="n">
-        <v>34664</v>
+        <v>34705</v>
       </c>
       <c r="P210" t="n">
         <v>1000</v>
@@ -17079,16 +17079,16 @@
         <v>17660</v>
       </c>
       <c r="S210" t="n">
-        <v>18704</v>
+        <v>18745</v>
       </c>
       <c r="T210" t="n">
-        <v>10399</v>
+        <v>10412</v>
       </c>
       <c r="U210" t="n">
-        <v>5200</v>
+        <v>5206</v>
       </c>
       <c r="V210" t="n">
-        <v>3105</v>
+        <v>3128</v>
       </c>
       <c r="W210" t="n">
         <v>9</v>
@@ -17143,13 +17143,13 @@
         <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>11403</v>
+        <v>11382</v>
       </c>
       <c r="N211" t="n">
-        <v>50479</v>
+        <v>50438</v>
       </c>
       <c r="O211" t="n">
-        <v>29094</v>
+        <v>29135</v>
       </c>
       <c r="P211" t="n">
         <v>4286</v>
@@ -17161,19 +17161,19 @@
         <v>17660</v>
       </c>
       <c r="S211" t="n">
-        <v>10748</v>
+        <v>10789</v>
       </c>
       <c r="T211" t="n">
-        <v>8728</v>
+        <v>8740</v>
       </c>
       <c r="U211" t="n">
-        <v>4364</v>
+        <v>4370</v>
       </c>
       <c r="V211" t="n">
-        <v>-2344</v>
+        <v>-2322</v>
       </c>
       <c r="W211" t="n">
-        <v>-8.1</v>
+        <v>-8</v>
       </c>
       <c r="X211" t="inlineStr">
         <is>
@@ -17225,13 +17225,13 @@
         <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>5833</v>
+        <v>5812</v>
       </c>
       <c r="N212" t="n">
-        <v>44909</v>
+        <v>44868</v>
       </c>
       <c r="O212" t="n">
-        <v>34664</v>
+        <v>34705</v>
       </c>
       <c r="P212" t="n">
         <v>4564</v>
@@ -17243,16 +17243,16 @@
         <v>17660</v>
       </c>
       <c r="S212" t="n">
-        <v>17739</v>
+        <v>17780</v>
       </c>
       <c r="T212" t="n">
-        <v>10399</v>
+        <v>10412</v>
       </c>
       <c r="U212" t="n">
-        <v>5200</v>
+        <v>5206</v>
       </c>
       <c r="V212" t="n">
-        <v>2140</v>
+        <v>2163</v>
       </c>
       <c r="W212" t="n">
         <v>6.2</v>
@@ -17307,13 +17307,13 @@
         <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>11403</v>
+        <v>11382</v>
       </c>
       <c r="N213" t="n">
-        <v>50479</v>
+        <v>50438</v>
       </c>
       <c r="O213" t="n">
-        <v>29094</v>
+        <v>29135</v>
       </c>
       <c r="P213" t="n">
         <v>4998</v>
@@ -17325,19 +17325,19 @@
         <v>17660</v>
       </c>
       <c r="S213" t="n">
-        <v>11435</v>
+        <v>11476</v>
       </c>
       <c r="T213" t="n">
-        <v>8728</v>
+        <v>8740</v>
       </c>
       <c r="U213" t="n">
-        <v>4364</v>
+        <v>4370</v>
       </c>
       <c r="V213" t="n">
-        <v>-1657</v>
+        <v>-1635</v>
       </c>
       <c r="W213" t="n">
-        <v>-5.7</v>
+        <v>-5.6</v>
       </c>
       <c r="X213" t="inlineStr">
         <is>
@@ -17389,13 +17389,13 @@
         <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>12995</v>
+        <v>12974</v>
       </c>
       <c r="N214" t="n">
-        <v>52071</v>
+        <v>52030</v>
       </c>
       <c r="O214" t="n">
-        <v>27502</v>
+        <v>27543</v>
       </c>
       <c r="P214" t="n">
         <v>5895</v>
@@ -17407,19 +17407,19 @@
         <v>17660</v>
       </c>
       <c r="S214" t="n">
-        <v>6747</v>
+        <v>6788</v>
       </c>
       <c r="T214" t="n">
-        <v>8251</v>
+        <v>8263</v>
       </c>
       <c r="U214" t="n">
-        <v>4125</v>
+        <v>4131</v>
       </c>
       <c r="V214" t="n">
-        <v>-5629</v>
+        <v>-5606</v>
       </c>
       <c r="W214" t="n">
-        <v>-20.5</v>
+        <v>-20.4</v>
       </c>
       <c r="X214" t="inlineStr">
         <is>
@@ -17471,13 +17471,13 @@
         <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>11403</v>
+        <v>11382</v>
       </c>
       <c r="N215" t="n">
-        <v>50479</v>
+        <v>50438</v>
       </c>
       <c r="O215" t="n">
-        <v>29094</v>
+        <v>29135</v>
       </c>
       <c r="P215" t="n">
         <v>10275</v>
@@ -17489,19 +17489,19 @@
         <v>17660</v>
       </c>
       <c r="S215" t="n">
-        <v>6459</v>
+        <v>6500</v>
       </c>
       <c r="T215" t="n">
-        <v>8728</v>
+        <v>8740</v>
       </c>
       <c r="U215" t="n">
-        <v>4364</v>
+        <v>4370</v>
       </c>
       <c r="V215" t="n">
-        <v>-6633</v>
+        <v>-6611</v>
       </c>
       <c r="W215" t="n">
-        <v>-22.8</v>
+        <v>-22.7</v>
       </c>
       <c r="X215" t="inlineStr">
         <is>
@@ -17553,13 +17553,13 @@
         <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>11403</v>
+        <v>11382</v>
       </c>
       <c r="N216" t="n">
-        <v>54134</v>
+        <v>54093</v>
       </c>
       <c r="O216" t="n">
-        <v>25439</v>
+        <v>25480</v>
       </c>
       <c r="P216" t="n">
         <v>5919</v>
@@ -17571,19 +17571,19 @@
         <v>17660</v>
       </c>
       <c r="S216" t="n">
-        <v>4659</v>
+        <v>4700</v>
       </c>
       <c r="T216" t="n">
-        <v>7632</v>
+        <v>7644</v>
       </c>
       <c r="U216" t="n">
-        <v>3816</v>
+        <v>3822</v>
       </c>
       <c r="V216" t="n">
-        <v>-6789</v>
+        <v>-6766</v>
       </c>
       <c r="W216" t="n">
-        <v>-26.7</v>
+        <v>-26.6</v>
       </c>
       <c r="X216" t="inlineStr">
         <is>
@@ -17632,16 +17632,16 @@
         <v>1830</v>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>6870</v>
       </c>
       <c r="M217" t="n">
-        <v>11412</v>
+        <v>11387</v>
       </c>
       <c r="N217" t="n">
-        <v>57354</v>
+        <v>57309</v>
       </c>
       <c r="O217" t="n">
-        <v>22219</v>
+        <v>22264</v>
       </c>
       <c r="P217" t="n">
         <v>0</v>
@@ -17653,19 +17653,19 @@
         <v>17660</v>
       </c>
       <c r="S217" t="n">
-        <v>8397</v>
+        <v>8442</v>
       </c>
       <c r="T217" t="n">
-        <v>6666</v>
+        <v>6679</v>
       </c>
       <c r="U217" t="n">
-        <v>3333</v>
+        <v>3340</v>
       </c>
       <c r="V217" t="n">
-        <v>-1602</v>
+        <v>-1577</v>
       </c>
       <c r="W217" t="n">
-        <v>-7.2</v>
+        <v>-7.1</v>
       </c>
       <c r="X217" t="inlineStr">
         <is>
@@ -17717,13 +17717,13 @@
         <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>12939</v>
+        <v>12918</v>
       </c>
       <c r="N218" t="n">
-        <v>51719</v>
+        <v>51678</v>
       </c>
       <c r="O218" t="n">
-        <v>27242</v>
+        <v>27283</v>
       </c>
       <c r="P218" t="n">
         <v>4935</v>
@@ -17735,19 +17735,19 @@
         <v>17660</v>
       </c>
       <c r="S218" t="n">
-        <v>9247</v>
+        <v>9288</v>
       </c>
       <c r="T218" t="n">
-        <v>8173</v>
+        <v>8185</v>
       </c>
       <c r="U218" t="n">
-        <v>4086</v>
+        <v>4092</v>
       </c>
       <c r="V218" t="n">
-        <v>-3012</v>
+        <v>-2989</v>
       </c>
       <c r="W218" t="n">
-        <v>-11.1</v>
+        <v>-11</v>
       </c>
       <c r="X218" t="inlineStr">
         <is>
@@ -17802,10 +17802,10 @@
         <v>5482</v>
       </c>
       <c r="N219" t="n">
-        <v>43960</v>
+        <v>43940</v>
       </c>
       <c r="O219" t="n">
-        <v>34360</v>
+        <v>34380</v>
       </c>
       <c r="P219" t="n">
         <v>1508</v>
@@ -17817,16 +17817,16 @@
         <v>13664</v>
       </c>
       <c r="S219" t="n">
-        <v>21987</v>
+        <v>22007</v>
       </c>
       <c r="T219" t="n">
-        <v>10308</v>
+        <v>10314</v>
       </c>
       <c r="U219" t="n">
-        <v>5154</v>
+        <v>5157</v>
       </c>
       <c r="V219" t="n">
-        <v>6525</v>
+        <v>6536</v>
       </c>
       <c r="W219" t="n">
         <v>19</v>
@@ -17884,10 +17884,10 @@
         <v>0</v>
       </c>
       <c r="N220" t="n">
-        <v>38584</v>
+        <v>38564</v>
       </c>
       <c r="O220" t="n">
-        <v>39736</v>
+        <v>39756</v>
       </c>
       <c r="P220" t="n">
         <v>4170</v>
@@ -17899,16 +17899,16 @@
         <v>13664</v>
       </c>
       <c r="S220" t="n">
-        <v>26502</v>
+        <v>26522</v>
       </c>
       <c r="T220" t="n">
-        <v>11921</v>
+        <v>11927</v>
       </c>
       <c r="U220" t="n">
-        <v>5960</v>
+        <v>5963</v>
       </c>
       <c r="V220" t="n">
-        <v>8621</v>
+        <v>8632</v>
       </c>
       <c r="W220" t="n">
         <v>21.7</v>
@@ -17966,10 +17966,10 @@
         <v>7012</v>
       </c>
       <c r="N221" t="n">
-        <v>45551</v>
+        <v>45531</v>
       </c>
       <c r="O221" t="n">
-        <v>32356</v>
+        <v>32376</v>
       </c>
       <c r="P221" t="n">
         <v>4935</v>
@@ -17981,16 +17981,16 @@
         <v>14537</v>
       </c>
       <c r="S221" t="n">
-        <v>17784</v>
+        <v>17804</v>
       </c>
       <c r="T221" t="n">
-        <v>9707</v>
+        <v>9713</v>
       </c>
       <c r="U221" t="n">
-        <v>4853</v>
+        <v>4856</v>
       </c>
       <c r="V221" t="n">
-        <v>3224</v>
+        <v>3235</v>
       </c>
       <c r="W221" t="n">
         <v>10</v>
@@ -18048,10 +18048,10 @@
         <v>0</v>
       </c>
       <c r="N222" t="n">
-        <v>33751</v>
+        <v>33731</v>
       </c>
       <c r="O222" t="n">
-        <v>44149</v>
+        <v>44169</v>
       </c>
       <c r="P222" t="n">
         <v>3099</v>
@@ -18063,16 +18063,16 @@
         <v>17660</v>
       </c>
       <c r="S222" t="n">
-        <v>25690</v>
+        <v>25710</v>
       </c>
       <c r="T222" t="n">
-        <v>13245</v>
+        <v>13251</v>
       </c>
       <c r="U222" t="n">
-        <v>6622</v>
+        <v>6625</v>
       </c>
       <c r="V222" t="n">
-        <v>5823</v>
+        <v>5834</v>
       </c>
       <c r="W222" t="n">
         <v>13.2</v>
@@ -18130,10 +18130,10 @@
         <v>5425</v>
       </c>
       <c r="N223" t="n">
-        <v>43630</v>
+        <v>43610</v>
       </c>
       <c r="O223" t="n">
-        <v>33865</v>
+        <v>33885</v>
       </c>
       <c r="P223" t="n">
         <v>5935</v>
@@ -18145,16 +18145,16 @@
         <v>13664</v>
       </c>
       <c r="S223" t="n">
-        <v>19165</v>
+        <v>19185</v>
       </c>
       <c r="T223" t="n">
-        <v>10160</v>
+        <v>10166</v>
       </c>
       <c r="U223" t="n">
-        <v>5080</v>
+        <v>5083</v>
       </c>
       <c r="V223" t="n">
-        <v>3926</v>
+        <v>3937</v>
       </c>
       <c r="W223" t="n">
         <v>11.6</v>
@@ -18212,10 +18212,10 @@
         <v>6955</v>
       </c>
       <c r="N224" t="n">
-        <v>45140</v>
+        <v>45120</v>
       </c>
       <c r="O224" t="n">
-        <v>32138</v>
+        <v>32158</v>
       </c>
       <c r="P224" t="n">
         <v>12202</v>
@@ -18227,16 +18227,16 @@
         <v>17189</v>
       </c>
       <c r="S224" t="n">
-        <v>6647</v>
+        <v>6667</v>
       </c>
       <c r="T224" t="n">
-        <v>9641</v>
+        <v>9647</v>
       </c>
       <c r="U224" t="n">
-        <v>4821</v>
+        <v>4824</v>
       </c>
       <c r="V224" t="n">
-        <v>-7815</v>
+        <v>-7804</v>
       </c>
       <c r="W224" t="n">
         <v>-24.3</v>
@@ -18288,16 +18288,16 @@
         <v>1776</v>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>5361</v>
       </c>
       <c r="M225" t="n">
         <v>5406</v>
       </c>
       <c r="N225" t="n">
-        <v>48926</v>
+        <v>48906</v>
       </c>
       <c r="O225" t="n">
-        <v>28298</v>
+        <v>28318</v>
       </c>
       <c r="P225" t="n">
         <v>1295</v>
@@ -18309,16 +18309,16 @@
         <v>17189</v>
       </c>
       <c r="S225" t="n">
-        <v>12340</v>
+        <v>12360</v>
       </c>
       <c r="T225" t="n">
-        <v>8489</v>
+        <v>8495</v>
       </c>
       <c r="U225" t="n">
-        <v>4245</v>
+        <v>4248</v>
       </c>
       <c r="V225" t="n">
-        <v>-394</v>
+        <v>-383</v>
       </c>
       <c r="W225" t="n">
         <v>-1.4</v>
@@ -18376,10 +18376,10 @@
         <v>9535</v>
       </c>
       <c r="N226" t="n">
-        <v>46289</v>
+        <v>46269</v>
       </c>
       <c r="O226" t="n">
-        <v>28831</v>
+        <v>28851</v>
       </c>
       <c r="P226" t="n">
         <v>4136</v>
@@ -18391,16 +18391,16 @@
         <v>13482</v>
       </c>
       <c r="S226" t="n">
-        <v>15413</v>
+        <v>15433</v>
       </c>
       <c r="T226" t="n">
-        <v>8649</v>
+        <v>8655</v>
       </c>
       <c r="U226" t="n">
-        <v>4325</v>
+        <v>4328</v>
       </c>
       <c r="V226" t="n">
-        <v>2439</v>
+        <v>2450</v>
       </c>
       <c r="W226" t="n">
         <v>8.5</v>
@@ -18458,10 +18458,10 @@
         <v>6741</v>
       </c>
       <c r="N227" t="n">
-        <v>43132</v>
+        <v>43112</v>
       </c>
       <c r="O227" t="n">
-        <v>31768</v>
+        <v>31788</v>
       </c>
       <c r="P227" t="n">
         <v>6414</v>
@@ -18473,16 +18473,16 @@
         <v>12464</v>
       </c>
       <c r="S227" t="n">
-        <v>17940</v>
+        <v>17960</v>
       </c>
       <c r="T227" t="n">
-        <v>9530</v>
+        <v>9536</v>
       </c>
       <c r="U227" t="n">
-        <v>4765</v>
+        <v>4768</v>
       </c>
       <c r="V227" t="n">
-        <v>3644</v>
+        <v>3655</v>
       </c>
       <c r="W227" t="n">
         <v>11.5</v>
@@ -18540,10 +18540,10 @@
         <v>8316</v>
       </c>
       <c r="N228" t="n">
-        <v>44868</v>
+        <v>44848</v>
       </c>
       <c r="O228" t="n">
-        <v>30032</v>
+        <v>30052</v>
       </c>
       <c r="P228" t="n">
         <v>10553</v>
@@ -18555,19 +18555,19 @@
         <v>12464</v>
       </c>
       <c r="S228" t="n">
-        <v>11415</v>
+        <v>11435</v>
       </c>
       <c r="T228" t="n">
-        <v>9010</v>
+        <v>9016</v>
       </c>
       <c r="U228" t="n">
-        <v>4505</v>
+        <v>4508</v>
       </c>
       <c r="V228" t="n">
-        <v>-2099</v>
+        <v>-2088</v>
       </c>
       <c r="W228" t="n">
-        <v>-7</v>
+        <v>-6.9</v>
       </c>
       <c r="X228" t="inlineStr">
         <is>
@@ -18623,10 +18623,10 @@
         <v>9509</v>
       </c>
       <c r="N229" t="n">
-        <v>46126</v>
+        <v>46106</v>
       </c>
       <c r="O229" t="n">
-        <v>28708</v>
+        <v>28728</v>
       </c>
       <c r="P229" t="n">
         <v>2948</v>
@@ -18638,19 +18638,19 @@
         <v>13482</v>
       </c>
       <c r="S229" t="n">
-        <v>15078</v>
+        <v>15098</v>
       </c>
       <c r="T229" t="n">
-        <v>8612</v>
+        <v>8618</v>
       </c>
       <c r="U229" t="n">
-        <v>4306</v>
+        <v>4309</v>
       </c>
       <c r="V229" t="n">
-        <v>2159</v>
+        <v>2170</v>
       </c>
       <c r="W229" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X229" t="inlineStr">
         <is>
@@ -18705,10 +18705,10 @@
         <v>5189</v>
       </c>
       <c r="N230" t="n">
-        <v>41686</v>
+        <v>41666</v>
       </c>
       <c r="O230" t="n">
-        <v>32436</v>
+        <v>32456</v>
       </c>
       <c r="P230" t="n">
         <v>2948</v>
@@ -18720,16 +18720,16 @@
         <v>13664</v>
       </c>
       <c r="S230" t="n">
-        <v>18523</v>
+        <v>18543</v>
       </c>
       <c r="T230" t="n">
-        <v>9731</v>
+        <v>9737</v>
       </c>
       <c r="U230" t="n">
-        <v>4865</v>
+        <v>4868</v>
       </c>
       <c r="V230" t="n">
-        <v>3927</v>
+        <v>3938</v>
       </c>
       <c r="W230" t="n">
         <v>12.1</v>
@@ -18787,10 +18787,10 @@
         <v>0</v>
       </c>
       <c r="N231" t="n">
-        <v>36432</v>
+        <v>36412</v>
       </c>
       <c r="O231" t="n">
-        <v>37468</v>
+        <v>37488</v>
       </c>
       <c r="P231" t="n">
         <v>8060</v>
@@ -18802,16 +18802,16 @@
         <v>11912</v>
       </c>
       <c r="S231" t="n">
-        <v>26346</v>
+        <v>26366</v>
       </c>
       <c r="T231" t="n">
-        <v>11240</v>
+        <v>11246</v>
       </c>
       <c r="U231" t="n">
-        <v>5620</v>
+        <v>5623</v>
       </c>
       <c r="V231" t="n">
-        <v>9485</v>
+        <v>9496</v>
       </c>
       <c r="W231" t="n">
         <v>25.3</v>
@@ -18869,10 +18869,10 @@
         <v>0</v>
       </c>
       <c r="N232" t="n">
-        <v>37810</v>
+        <v>37790</v>
       </c>
       <c r="O232" t="n">
-        <v>33090</v>
+        <v>33110</v>
       </c>
       <c r="P232" t="n">
         <v>3608</v>
@@ -18884,16 +18884,16 @@
         <v>14260</v>
       </c>
       <c r="S232" t="n">
-        <v>18922</v>
+        <v>18942</v>
       </c>
       <c r="T232" t="n">
-        <v>9927</v>
+        <v>9933</v>
       </c>
       <c r="U232" t="n">
-        <v>4964</v>
+        <v>4966</v>
       </c>
       <c r="V232" t="n">
-        <v>4032</v>
+        <v>4042</v>
       </c>
       <c r="W232" t="n">
         <v>12.2</v>
@@ -18951,10 +18951,10 @@
         <v>12658</v>
       </c>
       <c r="N233" t="n">
-        <v>47368</v>
+        <v>47348</v>
       </c>
       <c r="O233" t="n">
-        <v>22952</v>
+        <v>22972</v>
       </c>
       <c r="P233" t="n">
         <v>0</v>
@@ -18966,16 +18966,16 @@
         <v>12490</v>
       </c>
       <c r="S233" t="n">
-        <v>14162</v>
+        <v>14182</v>
       </c>
       <c r="T233" t="n">
-        <v>6886</v>
+        <v>6892</v>
       </c>
       <c r="U233" t="n">
-        <v>3443</v>
+        <v>3446</v>
       </c>
       <c r="V233" t="n">
-        <v>3834</v>
+        <v>3845</v>
       </c>
       <c r="W233" t="n">
         <v>16.7</v>
@@ -19033,10 +19033,10 @@
         <v>12658</v>
       </c>
       <c r="N234" t="n">
-        <v>47368</v>
+        <v>47348</v>
       </c>
       <c r="O234" t="n">
-        <v>22952</v>
+        <v>22972</v>
       </c>
       <c r="P234" t="n">
         <v>4075</v>
@@ -19048,19 +19048,19 @@
         <v>12490</v>
       </c>
       <c r="S234" t="n">
-        <v>6387</v>
+        <v>6407</v>
       </c>
       <c r="T234" t="n">
-        <v>6886</v>
+        <v>6892</v>
       </c>
       <c r="U234" t="n">
-        <v>3443</v>
+        <v>3446</v>
       </c>
       <c r="V234" t="n">
-        <v>-3941</v>
+        <v>-3930</v>
       </c>
       <c r="W234" t="n">
-        <v>-17.2</v>
+        <v>-17.1</v>
       </c>
       <c r="X234" t="inlineStr">
         <is>
@@ -19115,10 +19115,10 @@
         <v>4893</v>
       </c>
       <c r="N235" t="n">
-        <v>39365</v>
+        <v>39345</v>
       </c>
       <c r="O235" t="n">
-        <v>30535</v>
+        <v>30555</v>
       </c>
       <c r="P235" t="n">
         <v>2948</v>
@@ -19130,16 +19130,16 @@
         <v>10373</v>
       </c>
       <c r="S235" t="n">
-        <v>20214</v>
+        <v>20234</v>
       </c>
       <c r="T235" t="n">
-        <v>9160</v>
+        <v>9166</v>
       </c>
       <c r="U235" t="n">
-        <v>4580</v>
+        <v>4583</v>
       </c>
       <c r="V235" t="n">
-        <v>6473</v>
+        <v>6484</v>
       </c>
       <c r="W235" t="n">
         <v>21.2</v>
@@ -19197,10 +19197,10 @@
         <v>6201</v>
       </c>
       <c r="N236" t="n">
-        <v>40224</v>
+        <v>40204</v>
       </c>
       <c r="O236" t="n">
-        <v>28676</v>
+        <v>28696</v>
       </c>
       <c r="P236" t="n">
         <v>5974</v>
@@ -19212,19 +19212,19 @@
         <v>14537</v>
       </c>
       <c r="S236" t="n">
-        <v>11765</v>
+        <v>11785</v>
       </c>
       <c r="T236" t="n">
-        <v>8603</v>
+        <v>8609</v>
       </c>
       <c r="U236" t="n">
-        <v>4301</v>
+        <v>4304</v>
       </c>
       <c r="V236" t="n">
-        <v>-1139</v>
+        <v>-1128</v>
       </c>
       <c r="W236" t="n">
-        <v>-4</v>
+        <v>-3.9</v>
       </c>
       <c r="X236" t="inlineStr">
         <is>
@@ -19279,10 +19279,10 @@
         <v>4753</v>
       </c>
       <c r="N237" t="n">
-        <v>41558</v>
+        <v>41538</v>
       </c>
       <c r="O237" t="n">
-        <v>26342</v>
+        <v>26362</v>
       </c>
       <c r="P237" t="n">
         <v>1000</v>
@@ -19294,16 +19294,16 @@
         <v>13577</v>
       </c>
       <c r="S237" t="n">
-        <v>14065</v>
+        <v>14085</v>
       </c>
       <c r="T237" t="n">
-        <v>7903</v>
+        <v>7909</v>
       </c>
       <c r="U237" t="n">
-        <v>3951</v>
+        <v>3954</v>
       </c>
       <c r="V237" t="n">
-        <v>2211</v>
+        <v>2222</v>
       </c>
       <c r="W237" t="n">
         <v>8.4</v>
@@ -19361,10 +19361,10 @@
         <v>4698</v>
       </c>
       <c r="N238" t="n">
-        <v>37740</v>
+        <v>37720</v>
       </c>
       <c r="O238" t="n">
-        <v>29380</v>
+        <v>29400</v>
       </c>
       <c r="P238" t="n">
         <v>3294</v>
@@ -19376,16 +19376,16 @@
         <v>11225</v>
       </c>
       <c r="S238" t="n">
-        <v>18061</v>
+        <v>18081</v>
       </c>
       <c r="T238" t="n">
-        <v>8814</v>
+        <v>8820</v>
       </c>
       <c r="U238" t="n">
-        <v>4407</v>
+        <v>4410</v>
       </c>
       <c r="V238" t="n">
-        <v>4840</v>
+        <v>4851</v>
       </c>
       <c r="W238" t="n">
         <v>16.5</v>
@@ -19443,10 +19443,10 @@
         <v>4698</v>
       </c>
       <c r="N239" t="n">
-        <v>37818</v>
+        <v>37798</v>
       </c>
       <c r="O239" t="n">
-        <v>29302</v>
+        <v>29322</v>
       </c>
       <c r="P239" t="n">
         <v>4564</v>
@@ -19458,16 +19458,16 @@
         <v>11225</v>
       </c>
       <c r="S239" t="n">
-        <v>18813</v>
+        <v>18833</v>
       </c>
       <c r="T239" t="n">
-        <v>8791</v>
+        <v>8797</v>
       </c>
       <c r="U239" t="n">
-        <v>4395</v>
+        <v>4398</v>
       </c>
       <c r="V239" t="n">
-        <v>5627</v>
+        <v>5638</v>
       </c>
       <c r="W239" t="n">
         <v>19.2</v>
@@ -19522,13 +19522,13 @@
         <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>5439</v>
+        <v>5430</v>
       </c>
       <c r="N240" t="n">
-        <v>37082</v>
+        <v>37053</v>
       </c>
       <c r="O240" t="n">
-        <v>27312</v>
+        <v>27341</v>
       </c>
       <c r="P240" t="n">
         <v>6163</v>
@@ -19540,19 +19540,19 @@
         <v>14537</v>
       </c>
       <c r="S240" t="n">
-        <v>11612</v>
+        <v>11641</v>
       </c>
       <c r="T240" t="n">
-        <v>8194</v>
+        <v>8202</v>
       </c>
       <c r="U240" t="n">
-        <v>4097</v>
+        <v>4101</v>
       </c>
       <c r="V240" t="n">
-        <v>-678</v>
+        <v>-662</v>
       </c>
       <c r="W240" t="n">
-        <v>-2.5</v>
+        <v>-2.4</v>
       </c>
       <c r="X240" t="inlineStr">
         <is>
@@ -19604,13 +19604,13 @@
         <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>9947</v>
+        <v>9938</v>
       </c>
       <c r="N241" t="n">
-        <v>41590</v>
+        <v>41561</v>
       </c>
       <c r="O241" t="n">
-        <v>22804</v>
+        <v>22833</v>
       </c>
       <c r="P241" t="n">
         <v>1753</v>
@@ -19622,16 +19622,16 @@
         <v>14537</v>
       </c>
       <c r="S241" t="n">
-        <v>9113</v>
+        <v>9142</v>
       </c>
       <c r="T241" t="n">
-        <v>6841</v>
+        <v>6850</v>
       </c>
       <c r="U241" t="n">
-        <v>3421</v>
+        <v>3425</v>
       </c>
       <c r="V241" t="n">
-        <v>-1149</v>
+        <v>-1133</v>
       </c>
       <c r="W241" t="n">
         <v>-5</v>
@@ -19683,16 +19683,16 @@
         <v>1481</v>
       </c>
       <c r="L242" t="n">
-        <v>0</v>
+        <v>4208</v>
       </c>
       <c r="M242" t="n">
-        <v>9947</v>
+        <v>9938</v>
       </c>
       <c r="N242" t="n">
-        <v>45798</v>
+        <v>45769</v>
       </c>
       <c r="O242" t="n">
-        <v>18596</v>
+        <v>18625</v>
       </c>
       <c r="P242" t="n">
         <v>753</v>
@@ -19704,16 +19704,16 @@
         <v>14537</v>
       </c>
       <c r="S242" t="n">
-        <v>10944</v>
+        <v>10973</v>
       </c>
       <c r="T242" t="n">
-        <v>5579</v>
+        <v>5588</v>
       </c>
       <c r="U242" t="n">
-        <v>2789</v>
+        <v>2794</v>
       </c>
       <c r="V242" t="n">
-        <v>2576</v>
+        <v>2592</v>
       </c>
       <c r="W242" t="n">
         <v>13.9</v>
@@ -19768,13 +19768,13 @@
         <v>0</v>
       </c>
       <c r="M243" t="n">
-        <v>9947</v>
+        <v>9938</v>
       </c>
       <c r="N243" t="n">
-        <v>41590</v>
+        <v>41561</v>
       </c>
       <c r="O243" t="n">
-        <v>22804</v>
+        <v>22833</v>
       </c>
       <c r="P243" t="n">
         <v>1753</v>
@@ -19786,19 +19786,19 @@
         <v>14537</v>
       </c>
       <c r="S243" t="n">
-        <v>8914</v>
+        <v>8943</v>
       </c>
       <c r="T243" t="n">
-        <v>6841</v>
+        <v>6850</v>
       </c>
       <c r="U243" t="n">
-        <v>3421</v>
+        <v>3425</v>
       </c>
       <c r="V243" t="n">
-        <v>-1348</v>
+        <v>-1332</v>
       </c>
       <c r="W243" t="n">
-        <v>-5.9</v>
+        <v>-5.8</v>
       </c>
       <c r="X243" t="inlineStr">
         <is>
@@ -19850,13 +19850,13 @@
         <v>0</v>
       </c>
       <c r="M244" t="n">
-        <v>9947</v>
+        <v>9938</v>
       </c>
       <c r="N244" t="n">
-        <v>41590</v>
+        <v>41561</v>
       </c>
       <c r="O244" t="n">
-        <v>22804</v>
+        <v>22833</v>
       </c>
       <c r="P244" t="n">
         <v>5279</v>
@@ -19868,16 +19868,16 @@
         <v>14537</v>
       </c>
       <c r="S244" t="n">
-        <v>7788</v>
+        <v>7817</v>
       </c>
       <c r="T244" t="n">
-        <v>6841</v>
+        <v>6850</v>
       </c>
       <c r="U244" t="n">
-        <v>3421</v>
+        <v>3425</v>
       </c>
       <c r="V244" t="n">
-        <v>-2474</v>
+        <v>-2458</v>
       </c>
       <c r="W244" t="n">
         <v>-10.8</v>
@@ -19932,13 +19932,13 @@
         <v>0</v>
       </c>
       <c r="M245" t="n">
-        <v>9947</v>
+        <v>9938</v>
       </c>
       <c r="N245" t="n">
-        <v>44547</v>
+        <v>44518</v>
       </c>
       <c r="O245" t="n">
-        <v>19847</v>
+        <v>19876</v>
       </c>
       <c r="P245" t="n">
         <v>4858</v>
@@ -19950,19 +19950,19 @@
         <v>14537</v>
       </c>
       <c r="S245" t="n">
-        <v>3852</v>
+        <v>3881</v>
       </c>
       <c r="T245" t="n">
-        <v>5954</v>
+        <v>5963</v>
       </c>
       <c r="U245" t="n">
-        <v>2977</v>
+        <v>2981</v>
       </c>
       <c r="V245" t="n">
-        <v>-5079</v>
+        <v>-5063</v>
       </c>
       <c r="W245" t="n">
-        <v>-25.6</v>
+        <v>-25.5</v>
       </c>
       <c r="X245" t="inlineStr">
         <is>
@@ -20014,13 +20014,13 @@
         <v>0</v>
       </c>
       <c r="M246" t="n">
-        <v>11234</v>
+        <v>11225</v>
       </c>
       <c r="N246" t="n">
-        <v>42877</v>
+        <v>42848</v>
       </c>
       <c r="O246" t="n">
-        <v>21517</v>
+        <v>21546</v>
       </c>
       <c r="P246" t="n">
         <v>753</v>
@@ -20032,19 +20032,19 @@
         <v>14537</v>
       </c>
       <c r="S246" t="n">
-        <v>8627</v>
+        <v>8656</v>
       </c>
       <c r="T246" t="n">
-        <v>6455</v>
+        <v>6464</v>
       </c>
       <c r="U246" t="n">
-        <v>3228</v>
+        <v>3232</v>
       </c>
       <c r="V246" t="n">
-        <v>-1056</v>
+        <v>-1040</v>
       </c>
       <c r="W246" t="n">
-        <v>-4.9</v>
+        <v>-4.8</v>
       </c>
       <c r="X246" t="inlineStr">
         <is>
@@ -20096,13 +20096,13 @@
         <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>11234</v>
+        <v>11225</v>
       </c>
       <c r="N247" t="n">
-        <v>42877</v>
+        <v>42848</v>
       </c>
       <c r="O247" t="n">
-        <v>21517</v>
+        <v>21546</v>
       </c>
       <c r="P247" t="n">
         <v>753</v>
@@ -20114,19 +20114,19 @@
         <v>14537</v>
       </c>
       <c r="S247" t="n">
-        <v>8926</v>
+        <v>8955</v>
       </c>
       <c r="T247" t="n">
-        <v>6455</v>
+        <v>6464</v>
       </c>
       <c r="U247" t="n">
-        <v>3228</v>
+        <v>3232</v>
       </c>
       <c r="V247" t="n">
-        <v>-757</v>
+        <v>-741</v>
       </c>
       <c r="W247" t="n">
-        <v>-3.5</v>
+        <v>-3.4</v>
       </c>
       <c r="X247" t="inlineStr">
         <is>
@@ -20178,13 +20178,13 @@
         <v>0</v>
       </c>
       <c r="M248" t="n">
-        <v>9947</v>
+        <v>9938</v>
       </c>
       <c r="N248" t="n">
-        <v>41590</v>
+        <v>41561</v>
       </c>
       <c r="O248" t="n">
-        <v>22804</v>
+        <v>22833</v>
       </c>
       <c r="P248" t="n">
         <v>753</v>
@@ -20196,19 +20196,19 @@
         <v>14537</v>
       </c>
       <c r="S248" t="n">
-        <v>10014</v>
+        <v>10043</v>
       </c>
       <c r="T248" t="n">
-        <v>6841</v>
+        <v>6850</v>
       </c>
       <c r="U248" t="n">
-        <v>3421</v>
+        <v>3425</v>
       </c>
       <c r="V248" t="n">
-        <v>-248</v>
+        <v>-232</v>
       </c>
       <c r="W248" t="n">
-        <v>-1.1</v>
+        <v>-1</v>
       </c>
       <c r="X248" t="inlineStr">
         <is>
@@ -20260,13 +20260,13 @@
         <v>0</v>
       </c>
       <c r="M249" t="n">
-        <v>5439</v>
+        <v>5430</v>
       </c>
       <c r="N249" t="n">
-        <v>37082</v>
+        <v>37053</v>
       </c>
       <c r="O249" t="n">
-        <v>27312</v>
+        <v>27341</v>
       </c>
       <c r="P249" t="n">
         <v>4923</v>
@@ -20278,16 +20278,16 @@
         <v>14537</v>
       </c>
       <c r="S249" t="n">
-        <v>12552</v>
+        <v>12581</v>
       </c>
       <c r="T249" t="n">
-        <v>8194</v>
+        <v>8202</v>
       </c>
       <c r="U249" t="n">
-        <v>4097</v>
+        <v>4101</v>
       </c>
       <c r="V249" t="n">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="W249" t="n">
         <v>1</v>
@@ -20342,13 +20342,13 @@
         <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>9947</v>
+        <v>9938</v>
       </c>
       <c r="N250" t="n">
-        <v>41590</v>
+        <v>41561</v>
       </c>
       <c r="O250" t="n">
-        <v>22804</v>
+        <v>22833</v>
       </c>
       <c r="P250" t="n">
         <v>4871</v>
@@ -20360,19 +20360,19 @@
         <v>14537</v>
       </c>
       <c r="S250" t="n">
-        <v>7096</v>
+        <v>7125</v>
       </c>
       <c r="T250" t="n">
-        <v>6841</v>
+        <v>6850</v>
       </c>
       <c r="U250" t="n">
-        <v>3421</v>
+        <v>3425</v>
       </c>
       <c r="V250" t="n">
-        <v>-3166</v>
+        <v>-3150</v>
       </c>
       <c r="W250" t="n">
-        <v>-13.9</v>
+        <v>-13.8</v>
       </c>
       <c r="X250" t="inlineStr">
         <is>
@@ -20424,13 +20424,13 @@
         <v>0</v>
       </c>
       <c r="M251" t="n">
-        <v>9947</v>
+        <v>9938</v>
       </c>
       <c r="N251" t="n">
-        <v>41590</v>
+        <v>41561</v>
       </c>
       <c r="O251" t="n">
-        <v>22804</v>
+        <v>22833</v>
       </c>
       <c r="P251" t="n">
         <v>753</v>
@@ -20442,19 +20442,19 @@
         <v>14537</v>
       </c>
       <c r="S251" t="n">
-        <v>11113</v>
+        <v>11142</v>
       </c>
       <c r="T251" t="n">
-        <v>6841</v>
+        <v>6850</v>
       </c>
       <c r="U251" t="n">
-        <v>3421</v>
+        <v>3425</v>
       </c>
       <c r="V251" t="n">
-        <v>851</v>
+        <v>867</v>
       </c>
       <c r="W251" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="X251" t="inlineStr">
         <is>
@@ -20506,13 +20506,13 @@
         <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>5439</v>
+        <v>5430</v>
       </c>
       <c r="N252" t="n">
-        <v>37082</v>
+        <v>37053</v>
       </c>
       <c r="O252" t="n">
-        <v>27312</v>
+        <v>27341</v>
       </c>
       <c r="P252" t="n">
         <v>4685</v>
@@ -20524,19 +20524,19 @@
         <v>14537</v>
       </c>
       <c r="S252" t="n">
-        <v>12290</v>
+        <v>12319</v>
       </c>
       <c r="T252" t="n">
-        <v>8194</v>
+        <v>8202</v>
       </c>
       <c r="U252" t="n">
-        <v>4097</v>
+        <v>4101</v>
       </c>
       <c r="V252" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W252" t="n">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="X252" t="inlineStr">
         <is>
@@ -20588,13 +20588,13 @@
         <v>0</v>
       </c>
       <c r="M253" t="n">
-        <v>9947</v>
+        <v>9938</v>
       </c>
       <c r="N253" t="n">
-        <v>41590</v>
+        <v>41561</v>
       </c>
       <c r="O253" t="n">
-        <v>22804</v>
+        <v>22833</v>
       </c>
       <c r="P253" t="n">
         <v>753</v>
@@ -20606,19 +20606,19 @@
         <v>14537</v>
       </c>
       <c r="S253" t="n">
-        <v>10014</v>
+        <v>10043</v>
       </c>
       <c r="T253" t="n">
-        <v>6841</v>
+        <v>6850</v>
       </c>
       <c r="U253" t="n">
-        <v>3421</v>
+        <v>3425</v>
       </c>
       <c r="V253" t="n">
-        <v>-248</v>
+        <v>-232</v>
       </c>
       <c r="W253" t="n">
-        <v>-1.1</v>
+        <v>-1</v>
       </c>
       <c r="X253" t="inlineStr">
         <is>
@@ -20670,13 +20670,13 @@
         <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>11234</v>
+        <v>11225</v>
       </c>
       <c r="N254" t="n">
-        <v>45719</v>
+        <v>45690</v>
       </c>
       <c r="O254" t="n">
-        <v>18675</v>
+        <v>18704</v>
       </c>
       <c r="P254" t="n">
         <v>6697</v>
@@ -20688,19 +20688,19 @@
         <v>14537</v>
       </c>
       <c r="S254" t="n">
-        <v>4641</v>
+        <v>4670</v>
       </c>
       <c r="T254" t="n">
-        <v>5602</v>
+        <v>5611</v>
       </c>
       <c r="U254" t="n">
-        <v>2801</v>
+        <v>2806</v>
       </c>
       <c r="V254" t="n">
-        <v>-3763</v>
+        <v>-3747</v>
       </c>
       <c r="W254" t="n">
-        <v>-20.1</v>
+        <v>-20</v>
       </c>
       <c r="X254" t="inlineStr">
         <is>
@@ -20752,13 +20752,13 @@
         <v>0</v>
       </c>
       <c r="M255" t="n">
-        <v>11234</v>
+        <v>11225</v>
       </c>
       <c r="N255" t="n">
-        <v>42877</v>
+        <v>42848</v>
       </c>
       <c r="O255" t="n">
-        <v>21517</v>
+        <v>21546</v>
       </c>
       <c r="P255" t="n">
         <v>5160</v>
@@ -20770,19 +20770,19 @@
         <v>14537</v>
       </c>
       <c r="S255" t="n">
-        <v>6520</v>
+        <v>6549</v>
       </c>
       <c r="T255" t="n">
-        <v>6455</v>
+        <v>6464</v>
       </c>
       <c r="U255" t="n">
-        <v>3228</v>
+        <v>3232</v>
       </c>
       <c r="V255" t="n">
-        <v>-3163</v>
+        <v>-3147</v>
       </c>
       <c r="W255" t="n">
-        <v>-14.7</v>
+        <v>-14.6</v>
       </c>
       <c r="X255" t="inlineStr">
         <is>
@@ -20834,13 +20834,13 @@
         <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>9947</v>
+        <v>9938</v>
       </c>
       <c r="N256" t="n">
-        <v>41590</v>
+        <v>41561</v>
       </c>
       <c r="O256" t="n">
-        <v>22804</v>
+        <v>22833</v>
       </c>
       <c r="P256" t="n">
         <v>5677</v>
@@ -20852,19 +20852,19 @@
         <v>14537</v>
       </c>
       <c r="S256" t="n">
-        <v>8439</v>
+        <v>8468</v>
       </c>
       <c r="T256" t="n">
-        <v>6841</v>
+        <v>6850</v>
       </c>
       <c r="U256" t="n">
-        <v>3421</v>
+        <v>3425</v>
       </c>
       <c r="V256" t="n">
-        <v>-1823</v>
+        <v>-1807</v>
       </c>
       <c r="W256" t="n">
-        <v>-8</v>
+        <v>-7.9</v>
       </c>
       <c r="X256" t="inlineStr">
         <is>
@@ -20916,13 +20916,13 @@
         <v>0</v>
       </c>
       <c r="M257" t="n">
-        <v>11234</v>
+        <v>11225</v>
       </c>
       <c r="N257" t="n">
-        <v>42877</v>
+        <v>42848</v>
       </c>
       <c r="O257" t="n">
-        <v>21517</v>
+        <v>21546</v>
       </c>
       <c r="P257" t="n">
         <v>4923</v>
@@ -20934,19 +20934,19 @@
         <v>14537</v>
       </c>
       <c r="S257" t="n">
-        <v>6357</v>
+        <v>6386</v>
       </c>
       <c r="T257" t="n">
-        <v>6455</v>
+        <v>6464</v>
       </c>
       <c r="U257" t="n">
-        <v>3228</v>
+        <v>3232</v>
       </c>
       <c r="V257" t="n">
-        <v>-3326</v>
+        <v>-3310</v>
       </c>
       <c r="W257" t="n">
-        <v>-15.5</v>
+        <v>-15.4</v>
       </c>
       <c r="X257" t="inlineStr">
         <is>
@@ -20998,13 +20998,13 @@
         <v>0</v>
       </c>
       <c r="M258" t="n">
-        <v>11234</v>
+        <v>11225</v>
       </c>
       <c r="N258" t="n">
-        <v>42877</v>
+        <v>42848</v>
       </c>
       <c r="O258" t="n">
-        <v>21517</v>
+        <v>21546</v>
       </c>
       <c r="P258" t="n">
         <v>11202</v>
@@ -21016,19 +21016,19 @@
         <v>14537</v>
       </c>
       <c r="S258" t="n">
-        <v>5778</v>
+        <v>5807</v>
       </c>
       <c r="T258" t="n">
-        <v>6455</v>
+        <v>6464</v>
       </c>
       <c r="U258" t="n">
-        <v>3228</v>
+        <v>3232</v>
       </c>
       <c r="V258" t="n">
-        <v>-3905</v>
+        <v>-3889</v>
       </c>
       <c r="W258" t="n">
-        <v>-18.1</v>
+        <v>-18</v>
       </c>
       <c r="X258" t="inlineStr">
         <is>
@@ -21080,13 +21080,13 @@
         <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>9947</v>
+        <v>9938</v>
       </c>
       <c r="N259" t="n">
-        <v>44548</v>
+        <v>44519</v>
       </c>
       <c r="O259" t="n">
-        <v>19846</v>
+        <v>19875</v>
       </c>
       <c r="P259" t="n">
         <v>3677</v>
@@ -21098,19 +21098,19 @@
         <v>14537</v>
       </c>
       <c r="S259" t="n">
-        <v>5232</v>
+        <v>5261</v>
       </c>
       <c r="T259" t="n">
-        <v>5954</v>
+        <v>5962</v>
       </c>
       <c r="U259" t="n">
-        <v>2977</v>
+        <v>2981</v>
       </c>
       <c r="V259" t="n">
-        <v>-3699</v>
+        <v>-3683</v>
       </c>
       <c r="W259" t="n">
-        <v>-18.6</v>
+        <v>-18.5</v>
       </c>
       <c r="X259" t="inlineStr">
         <is>
@@ -21162,13 +21162,13 @@
         <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>9947</v>
+        <v>9938</v>
       </c>
       <c r="N260" t="n">
-        <v>41590</v>
+        <v>41561</v>
       </c>
       <c r="O260" t="n">
-        <v>22804</v>
+        <v>22833</v>
       </c>
       <c r="P260" t="n">
         <v>3701</v>
@@ -21180,19 +21180,19 @@
         <v>14537</v>
       </c>
       <c r="S260" t="n">
-        <v>7465</v>
+        <v>7494</v>
       </c>
       <c r="T260" t="n">
-        <v>6841</v>
+        <v>6850</v>
       </c>
       <c r="U260" t="n">
-        <v>3421</v>
+        <v>3425</v>
       </c>
       <c r="V260" t="n">
-        <v>-2797</v>
+        <v>-2781</v>
       </c>
       <c r="W260" t="n">
-        <v>-12.3</v>
+        <v>-12.2</v>
       </c>
       <c r="X260" t="inlineStr">
         <is>
@@ -21241,16 +21241,16 @@
         <v>1471</v>
       </c>
       <c r="L261" t="n">
-        <v>0</v>
+        <v>4636</v>
       </c>
       <c r="M261" t="n">
-        <v>9915</v>
+        <v>9906</v>
       </c>
       <c r="N261" t="n">
-        <v>45973</v>
+        <v>45944</v>
       </c>
       <c r="O261" t="n">
-        <v>17963</v>
+        <v>17992</v>
       </c>
       <c r="P261" t="n">
         <v>753</v>
@@ -21262,19 +21262,19 @@
         <v>14537</v>
       </c>
       <c r="S261" t="n">
-        <v>9574</v>
+        <v>9603</v>
       </c>
       <c r="T261" t="n">
-        <v>5389</v>
+        <v>5398</v>
       </c>
       <c r="U261" t="n">
-        <v>2694</v>
+        <v>2699</v>
       </c>
       <c r="V261" t="n">
-        <v>1491</v>
+        <v>1507</v>
       </c>
       <c r="W261" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X261" t="inlineStr">
         <is>
@@ -21326,13 +21326,13 @@
         <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>11193</v>
+        <v>11184</v>
       </c>
       <c r="N262" t="n">
-        <v>42615</v>
+        <v>42586</v>
       </c>
       <c r="O262" t="n">
-        <v>21321</v>
+        <v>21350</v>
       </c>
       <c r="P262" t="n">
         <v>4889</v>
@@ -21344,19 +21344,19 @@
         <v>14537</v>
       </c>
       <c r="S262" t="n">
-        <v>5995</v>
+        <v>6024</v>
       </c>
       <c r="T262" t="n">
-        <v>6396</v>
+        <v>6405</v>
       </c>
       <c r="U262" t="n">
-        <v>3198</v>
+        <v>3202</v>
       </c>
       <c r="V262" t="n">
-        <v>-3599</v>
+        <v>-3584</v>
       </c>
       <c r="W262" t="n">
-        <v>-16.9</v>
+        <v>-16.8</v>
       </c>
       <c r="X262" t="inlineStr">
         <is>
@@ -21411,10 +21411,10 @@
         <v>4475</v>
       </c>
       <c r="N263" t="n">
-        <v>35989</v>
+        <v>35969</v>
       </c>
       <c r="O263" t="n">
-        <v>27936</v>
+        <v>27956</v>
       </c>
       <c r="P263" t="n">
         <v>10878</v>
@@ -21426,16 +21426,16 @@
         <v>12490</v>
       </c>
       <c r="S263" t="n">
-        <v>12818</v>
+        <v>12838</v>
       </c>
       <c r="T263" t="n">
-        <v>8381</v>
+        <v>8387</v>
       </c>
       <c r="U263" t="n">
-        <v>4190</v>
+        <v>4193</v>
       </c>
       <c r="V263" t="n">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="W263" t="n">
         <v>0.9</v>
@@ -21493,10 +21493,10 @@
         <v>0</v>
       </c>
       <c r="N264" t="n">
-        <v>30893</v>
+        <v>30873</v>
       </c>
       <c r="O264" t="n">
-        <v>33027</v>
+        <v>33047</v>
       </c>
       <c r="P264" t="n">
         <v>1689</v>
@@ -21508,19 +21508,19 @@
         <v>7605</v>
       </c>
       <c r="S264" t="n">
-        <v>26733</v>
+        <v>26753</v>
       </c>
       <c r="T264" t="n">
-        <v>9908</v>
+        <v>9914</v>
       </c>
       <c r="U264" t="n">
-        <v>4954</v>
+        <v>4957</v>
       </c>
       <c r="V264" t="n">
-        <v>11871</v>
+        <v>11882</v>
       </c>
       <c r="W264" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="X264" t="inlineStr">
         <is>
@@ -21575,10 +21575,10 @@
         <v>5751</v>
       </c>
       <c r="N265" t="n">
-        <v>40373</v>
+        <v>40353</v>
       </c>
       <c r="O265" t="n">
-        <v>23527</v>
+        <v>23547</v>
       </c>
       <c r="P265" t="n">
         <v>0</v>
@@ -21590,19 +21590,19 @@
         <v>12651</v>
       </c>
       <c r="S265" t="n">
-        <v>13375</v>
+        <v>13395</v>
       </c>
       <c r="T265" t="n">
-        <v>7058</v>
+        <v>7064</v>
       </c>
       <c r="U265" t="n">
-        <v>3529</v>
+        <v>3532</v>
       </c>
       <c r="V265" t="n">
-        <v>2788</v>
+        <v>2799</v>
       </c>
       <c r="W265" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="X265" t="inlineStr">
         <is>
@@ -21654,13 +21654,13 @@
         <v>0</v>
       </c>
       <c r="M266" t="n">
-        <v>11177</v>
+        <v>11168</v>
       </c>
       <c r="N266" t="n">
-        <v>42510</v>
+        <v>42481</v>
       </c>
       <c r="O266" t="n">
-        <v>21242</v>
+        <v>21271</v>
       </c>
       <c r="P266" t="n">
         <v>5718</v>
@@ -21672,19 +21672,19 @@
         <v>14537</v>
       </c>
       <c r="S266" t="n">
-        <v>6286</v>
+        <v>6315</v>
       </c>
       <c r="T266" t="n">
-        <v>6373</v>
+        <v>6381</v>
       </c>
       <c r="U266" t="n">
-        <v>3186</v>
+        <v>3191</v>
       </c>
       <c r="V266" t="n">
-        <v>-3273</v>
+        <v>-3257</v>
       </c>
       <c r="W266" t="n">
-        <v>-15.4</v>
+        <v>-15.3</v>
       </c>
       <c r="X266" t="inlineStr">
         <is>
@@ -21739,10 +21739,10 @@
         <v>5661</v>
       </c>
       <c r="N267" t="n">
-        <v>36682</v>
+        <v>36662</v>
       </c>
       <c r="O267" t="n">
-        <v>26218</v>
+        <v>26238</v>
       </c>
       <c r="P267" t="n">
         <v>2910</v>
@@ -21754,19 +21754,19 @@
         <v>14844</v>
       </c>
       <c r="S267" t="n">
-        <v>11363</v>
+        <v>11383</v>
       </c>
       <c r="T267" t="n">
-        <v>7865</v>
+        <v>7871</v>
       </c>
       <c r="U267" t="n">
-        <v>3933</v>
+        <v>3936</v>
       </c>
       <c r="V267" t="n">
-        <v>-435</v>
+        <v>-424</v>
       </c>
       <c r="W267" t="n">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="X267" t="inlineStr">
         <is>
@@ -21821,10 +21821,10 @@
         <v>5661</v>
       </c>
       <c r="N268" t="n">
-        <v>36682</v>
+        <v>36662</v>
       </c>
       <c r="O268" t="n">
-        <v>26218</v>
+        <v>26238</v>
       </c>
       <c r="P268" t="n">
         <v>3210</v>
@@ -21836,16 +21836,16 @@
         <v>14844</v>
       </c>
       <c r="S268" t="n">
-        <v>10564</v>
+        <v>10584</v>
       </c>
       <c r="T268" t="n">
-        <v>7865</v>
+        <v>7871</v>
       </c>
       <c r="U268" t="n">
-        <v>3933</v>
+        <v>3936</v>
       </c>
       <c r="V268" t="n">
-        <v>-1234</v>
+        <v>-1223</v>
       </c>
       <c r="W268" t="n">
         <v>-4.7</v>
@@ -21903,10 +21903,10 @@
         <v>4335</v>
       </c>
       <c r="N269" t="n">
-        <v>34875</v>
+        <v>34855</v>
       </c>
       <c r="O269" t="n">
-        <v>27052</v>
+        <v>27072</v>
       </c>
       <c r="P269" t="n">
         <v>7235</v>
@@ -21918,19 +21918,19 @@
         <v>13664</v>
       </c>
       <c r="S269" t="n">
-        <v>8453</v>
+        <v>8473</v>
       </c>
       <c r="T269" t="n">
-        <v>8116</v>
+        <v>8122</v>
       </c>
       <c r="U269" t="n">
-        <v>4058</v>
+        <v>4061</v>
       </c>
       <c r="V269" t="n">
-        <v>-3720</v>
+        <v>-3709</v>
       </c>
       <c r="W269" t="n">
-        <v>-13.8</v>
+        <v>-13.7</v>
       </c>
       <c r="X269" t="inlineStr">
         <is>
@@ -21985,10 +21985,10 @@
         <v>4333</v>
       </c>
       <c r="N270" t="n">
-        <v>37346</v>
+        <v>37326</v>
       </c>
       <c r="O270" t="n">
-        <v>24554</v>
+        <v>24574</v>
       </c>
       <c r="P270" t="n">
         <v>2385</v>
@@ -22000,19 +22000,19 @@
         <v>12651</v>
       </c>
       <c r="S270" t="n">
-        <v>14668</v>
+        <v>14688</v>
       </c>
       <c r="T270" t="n">
-        <v>7366</v>
+        <v>7372</v>
       </c>
       <c r="U270" t="n">
-        <v>3683</v>
+        <v>3686</v>
       </c>
       <c r="V270" t="n">
-        <v>3619</v>
+        <v>3630</v>
       </c>
       <c r="W270" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="X270" t="inlineStr">
         <is>
@@ -22067,10 +22067,10 @@
         <v>5562</v>
       </c>
       <c r="N271" t="n">
-        <v>36048</v>
+        <v>36028</v>
       </c>
       <c r="O271" t="n">
-        <v>25753</v>
+        <v>25773</v>
       </c>
       <c r="P271" t="n">
         <v>8278</v>
@@ -22082,16 +22082,16 @@
         <v>14537</v>
       </c>
       <c r="S271" t="n">
-        <v>8488</v>
+        <v>8508</v>
       </c>
       <c r="T271" t="n">
-        <v>7726</v>
+        <v>7732</v>
       </c>
       <c r="U271" t="n">
-        <v>3863</v>
+        <v>3866</v>
       </c>
       <c r="V271" t="n">
-        <v>-3101</v>
+        <v>-3090</v>
       </c>
       <c r="W271" t="n">
         <v>-12</v>
@@ -22149,10 +22149,10 @@
         <v>5895</v>
       </c>
       <c r="N272" t="n">
-        <v>36073</v>
+        <v>36053</v>
       </c>
       <c r="O272" t="n">
-        <v>25630</v>
+        <v>25650</v>
       </c>
       <c r="P272" t="n">
         <v>4185</v>
@@ -22164,16 +22164,16 @@
         <v>12464</v>
       </c>
       <c r="S272" t="n">
-        <v>12881</v>
+        <v>12901</v>
       </c>
       <c r="T272" t="n">
-        <v>7689</v>
+        <v>7695</v>
       </c>
       <c r="U272" t="n">
-        <v>3844</v>
+        <v>3848</v>
       </c>
       <c r="V272" t="n">
-        <v>1348</v>
+        <v>1358</v>
       </c>
       <c r="W272" t="n">
         <v>5.3</v>
@@ -22229,13 +22229,13 @@
         <v>0</v>
       </c>
       <c r="M273" t="n">
-        <v>9721</v>
+        <v>9712</v>
       </c>
       <c r="N273" t="n">
-        <v>42419</v>
+        <v>42390</v>
       </c>
       <c r="O273" t="n">
-        <v>18757</v>
+        <v>18786</v>
       </c>
       <c r="P273" t="n">
         <v>5154</v>
@@ -22247,19 +22247,19 @@
         <v>14537</v>
       </c>
       <c r="S273" t="n">
-        <v>3266</v>
+        <v>3295</v>
       </c>
       <c r="T273" t="n">
-        <v>5627</v>
+        <v>5636</v>
       </c>
       <c r="U273" t="n">
-        <v>2814</v>
+        <v>2818</v>
       </c>
       <c r="V273" t="n">
-        <v>-5175</v>
+        <v>-5159</v>
       </c>
       <c r="W273" t="n">
-        <v>-27.6</v>
+        <v>-27.5</v>
       </c>
       <c r="X273" t="inlineStr">
         <is>
@@ -22314,10 +22314,10 @@
         <v>9721</v>
       </c>
       <c r="N274" t="n">
-        <v>39820</v>
+        <v>39800</v>
       </c>
       <c r="O274" t="n">
-        <v>21355</v>
+        <v>21375</v>
       </c>
       <c r="P274" t="n">
         <v>4920</v>
@@ -22329,19 +22329,19 @@
         <v>14537</v>
       </c>
       <c r="S274" t="n">
-        <v>6298</v>
+        <v>6318</v>
       </c>
       <c r="T274" t="n">
-        <v>6406</v>
+        <v>6412</v>
       </c>
       <c r="U274" t="n">
-        <v>3203</v>
+        <v>3206</v>
       </c>
       <c r="V274" t="n">
-        <v>-3312</v>
+        <v>-3301</v>
       </c>
       <c r="W274" t="n">
-        <v>-15.5</v>
+        <v>-15.4</v>
       </c>
       <c r="X274" t="inlineStr">
         <is>
@@ -22396,10 +22396,10 @@
         <v>0</v>
       </c>
       <c r="N275" t="n">
-        <v>30201</v>
+        <v>30181</v>
       </c>
       <c r="O275" t="n">
-        <v>30887</v>
+        <v>30907</v>
       </c>
       <c r="P275" t="n">
         <v>3099</v>
@@ -22411,19 +22411,19 @@
         <v>13664</v>
       </c>
       <c r="S275" t="n">
-        <v>16723</v>
+        <v>16743</v>
       </c>
       <c r="T275" t="n">
-        <v>9266</v>
+        <v>9272</v>
       </c>
       <c r="U275" t="n">
-        <v>4633</v>
+        <v>4636</v>
       </c>
       <c r="V275" t="n">
-        <v>2824</v>
+        <v>2835</v>
       </c>
       <c r="W275" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X275" t="inlineStr">
         <is>
@@ -22472,16 +22472,16 @@
         <v>1369</v>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>5922</v>
       </c>
       <c r="M276" t="n">
         <v>0</v>
       </c>
       <c r="N276" t="n">
-        <v>35323</v>
+        <v>35303</v>
       </c>
       <c r="O276" t="n">
-        <v>24207</v>
+        <v>24227</v>
       </c>
       <c r="P276" t="n">
         <v>1507</v>
@@ -22493,16 +22493,16 @@
         <v>13664</v>
       </c>
       <c r="S276" t="n">
-        <v>19240</v>
+        <v>19260</v>
       </c>
       <c r="T276" t="n">
-        <v>7262</v>
+        <v>7268</v>
       </c>
       <c r="U276" t="n">
-        <v>3631</v>
+        <v>3634</v>
       </c>
       <c r="V276" t="n">
-        <v>8347</v>
+        <v>8358</v>
       </c>
       <c r="W276" t="n">
         <v>34.5</v>
@@ -22560,10 +22560,10 @@
         <v>0</v>
       </c>
       <c r="N277" t="n">
-        <v>29401</v>
+        <v>29381</v>
       </c>
       <c r="O277" t="n">
-        <v>30129</v>
+        <v>30149</v>
       </c>
       <c r="P277" t="n">
         <v>9925</v>
@@ -22575,16 +22575,16 @@
         <v>13664</v>
       </c>
       <c r="S277" t="n">
-        <v>14039</v>
+        <v>14059</v>
       </c>
       <c r="T277" t="n">
-        <v>9039</v>
+        <v>9045</v>
       </c>
       <c r="U277" t="n">
-        <v>4519</v>
+        <v>4522</v>
       </c>
       <c r="V277" t="n">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="W277" t="n">
         <v>1.6</v>
@@ -22642,10 +22642,10 @@
         <v>5211</v>
       </c>
       <c r="N278" t="n">
-        <v>33300</v>
+        <v>33280</v>
       </c>
       <c r="O278" t="n">
-        <v>24600</v>
+        <v>24620</v>
       </c>
       <c r="P278" t="n">
         <v>3932</v>
@@ -22657,19 +22657,19 @@
         <v>10373</v>
       </c>
       <c r="S278" t="n">
-        <v>14495</v>
+        <v>14515</v>
       </c>
       <c r="T278" t="n">
-        <v>7380</v>
+        <v>7386</v>
       </c>
       <c r="U278" t="n">
-        <v>3690</v>
+        <v>3693</v>
       </c>
       <c r="V278" t="n">
-        <v>3425</v>
+        <v>3436</v>
       </c>
       <c r="W278" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="X278" t="inlineStr">
         <is>
@@ -22721,13 +22721,13 @@
         <v>0</v>
       </c>
       <c r="M279" t="n">
-        <v>35037</v>
+        <v>34922</v>
       </c>
       <c r="N279" t="n">
-        <v>63233</v>
+        <v>63098</v>
       </c>
       <c r="O279" t="n">
-        <v>-5333</v>
+        <v>-5198</v>
       </c>
       <c r="P279" t="n">
         <v>1344</v>
@@ -22739,16 +22739,16 @@
         <v>10373</v>
       </c>
       <c r="S279" t="n">
-        <v>-12000</v>
+        <v>-11865</v>
       </c>
       <c r="T279" t="n">
-        <v>-1600</v>
+        <v>-1559</v>
       </c>
       <c r="U279" t="n">
-        <v>-800</v>
+        <v>-780</v>
       </c>
       <c r="V279" t="n">
-        <v>-9600</v>
+        <v>-9526</v>
       </c>
       <c r="X279" t="inlineStr">
         <is>
@@ -22800,13 +22800,13 @@
         <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>35037</v>
+        <v>34922</v>
       </c>
       <c r="N280" t="n">
-        <v>63233</v>
+        <v>63098</v>
       </c>
       <c r="O280" t="n">
-        <v>-5333</v>
+        <v>-5198</v>
       </c>
       <c r="P280" t="n">
         <v>1344</v>
@@ -22818,16 +22818,16 @@
         <v>10373</v>
       </c>
       <c r="S280" t="n">
-        <v>-17050</v>
+        <v>-16915</v>
       </c>
       <c r="T280" t="n">
-        <v>-1600</v>
+        <v>-1559</v>
       </c>
       <c r="U280" t="n">
-        <v>-800</v>
+        <v>-780</v>
       </c>
       <c r="V280" t="n">
-        <v>-14650</v>
+        <v>-14576</v>
       </c>
       <c r="X280" t="inlineStr">
         <is>
@@ -22876,16 +22876,16 @@
         <v>1332</v>
       </c>
       <c r="L281" t="n">
-        <v>0</v>
+        <v>7707</v>
       </c>
       <c r="M281" t="n">
-        <v>30983</v>
+        <v>30869</v>
       </c>
       <c r="N281" t="n">
-        <v>66884</v>
+        <v>66750</v>
       </c>
       <c r="O281" t="n">
-        <v>-8984</v>
+        <v>-8850</v>
       </c>
       <c r="P281" t="n">
         <v>1342</v>
@@ -22897,16 +22897,16 @@
         <v>10373</v>
       </c>
       <c r="S281" t="n">
-        <v>-12976</v>
+        <v>-12842</v>
       </c>
       <c r="T281" t="n">
-        <v>-2695</v>
+        <v>-2655</v>
       </c>
       <c r="U281" t="n">
-        <v>-1348</v>
+        <v>-1328</v>
       </c>
       <c r="V281" t="n">
-        <v>-8933</v>
+        <v>-8860</v>
       </c>
       <c r="X281" t="inlineStr">
         <is>
@@ -22961,10 +22961,10 @@
         <v>7952</v>
       </c>
       <c r="N282" t="n">
-        <v>36211</v>
+        <v>36191</v>
       </c>
       <c r="O282" t="n">
-        <v>21321</v>
+        <v>21341</v>
       </c>
       <c r="P282" t="n">
         <v>3099</v>
@@ -22976,19 +22976,19 @@
         <v>13482</v>
       </c>
       <c r="S282" t="n">
-        <v>7439</v>
+        <v>7459</v>
       </c>
       <c r="T282" t="n">
-        <v>6396</v>
+        <v>6402</v>
       </c>
       <c r="U282" t="n">
-        <v>3198</v>
+        <v>3201</v>
       </c>
       <c r="V282" t="n">
-        <v>-2155</v>
+        <v>-2144</v>
       </c>
       <c r="W282" t="n">
-        <v>-10.1</v>
+        <v>-10</v>
       </c>
       <c r="X282" t="inlineStr">
         <is>
@@ -23043,10 +23043,10 @@
         <v>3966</v>
       </c>
       <c r="N283" t="n">
-        <v>31885</v>
+        <v>31865</v>
       </c>
       <c r="O283" t="n">
-        <v>24769</v>
+        <v>24789</v>
       </c>
       <c r="P283" t="n">
         <v>14378</v>
@@ -23058,19 +23058,19 @@
         <v>13482</v>
       </c>
       <c r="S283" t="n">
-        <v>1109</v>
+        <v>1129</v>
       </c>
       <c r="T283" t="n">
-        <v>7431</v>
+        <v>7437</v>
       </c>
       <c r="U283" t="n">
-        <v>3715</v>
+        <v>3718</v>
       </c>
       <c r="V283" t="n">
-        <v>-10037</v>
+        <v>-10026</v>
       </c>
       <c r="W283" t="n">
-        <v>-40.5</v>
+        <v>-40.4</v>
       </c>
       <c r="X283" t="inlineStr">
         <is>
@@ -23125,10 +23125,10 @@
         <v>3913</v>
       </c>
       <c r="N284" t="n">
-        <v>31537</v>
+        <v>31517</v>
       </c>
       <c r="O284" t="n">
-        <v>24363</v>
+        <v>24383</v>
       </c>
       <c r="P284" t="n">
         <v>6747</v>
@@ -23140,16 +23140,16 @@
         <v>11225</v>
       </c>
       <c r="S284" t="n">
-        <v>11391</v>
+        <v>11411</v>
       </c>
       <c r="T284" t="n">
-        <v>7309</v>
+        <v>7315</v>
       </c>
       <c r="U284" t="n">
-        <v>3654</v>
+        <v>3657</v>
       </c>
       <c r="V284" t="n">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="W284" t="n">
         <v>1.8</v>
@@ -23207,10 +23207,10 @@
         <v>3773</v>
       </c>
       <c r="N285" t="n">
-        <v>30062</v>
+        <v>30042</v>
       </c>
       <c r="O285" t="n">
-        <v>23838</v>
+        <v>23858</v>
       </c>
       <c r="P285" t="n">
         <v>2107</v>
@@ -23222,16 +23222,16 @@
         <v>9760</v>
       </c>
       <c r="S285" t="n">
-        <v>16570</v>
+        <v>16590</v>
       </c>
       <c r="T285" t="n">
-        <v>7151</v>
+        <v>7157</v>
       </c>
       <c r="U285" t="n">
-        <v>3576</v>
+        <v>3579</v>
       </c>
       <c r="V285" t="n">
-        <v>5843</v>
+        <v>5854</v>
       </c>
       <c r="W285" t="n">
         <v>24.5</v>
@@ -23361,16 +23361,16 @@
         <v>2281</v>
       </c>
       <c r="L287" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M287" t="n">
         <v>2841</v>
       </c>
       <c r="N287" t="n">
-        <v>23389</v>
+        <v>23397</v>
       </c>
       <c r="O287" t="n">
-        <v>8177</v>
+        <v>8169</v>
       </c>
       <c r="P287" t="n">
         <v>0</v>
@@ -23382,19 +23382,19 @@
         <v>4411</v>
       </c>
       <c r="S287" t="n">
-        <v>3766</v>
+        <v>3758</v>
       </c>
       <c r="T287" t="n">
-        <v>2453</v>
+        <v>2451</v>
       </c>
       <c r="U287" t="n">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="V287" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="W287" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="X287" t="inlineStr"/>
     </row>
@@ -23598,13 +23598,13 @@
         <v>0</v>
       </c>
       <c r="M290" t="n">
-        <v>27452</v>
+        <v>27337</v>
       </c>
       <c r="N290" t="n">
-        <v>30479</v>
+        <v>30344</v>
       </c>
       <c r="O290" t="n">
-        <v>-24688</v>
+        <v>-24553</v>
       </c>
       <c r="P290" t="n">
         <v>1344</v>
@@ -23616,16 +23616,16 @@
         <v>10373</v>
       </c>
       <c r="S290" t="n">
-        <v>-34405</v>
+        <v>-34270</v>
       </c>
       <c r="T290" t="n">
-        <v>-7406</v>
+        <v>-7366</v>
       </c>
       <c r="U290" t="n">
-        <v>-3703</v>
+        <v>-3683</v>
       </c>
       <c r="V290" t="n">
-        <v>-23295</v>
+        <v>-23221</v>
       </c>
       <c r="X290" t="inlineStr">
         <is>
@@ -23680,10 +23680,10 @@
         <v>521</v>
       </c>
       <c r="N291" t="n">
-        <v>3439</v>
+        <v>3419</v>
       </c>
       <c r="O291" t="n">
-        <v>2350</v>
+        <v>2370</v>
       </c>
       <c r="P291" t="n">
         <v>0</v>
@@ -23695,19 +23695,19 @@
         <v>10373</v>
       </c>
       <c r="S291" t="n">
-        <v>-5923</v>
+        <v>-5903</v>
       </c>
       <c r="T291" t="n">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="U291" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="V291" t="n">
-        <v>-6980</v>
+        <v>-6970</v>
       </c>
       <c r="W291" t="n">
-        <v>-297</v>
+        <v>-294.1</v>
       </c>
       <c r="X291" t="inlineStr">
         <is>
@@ -23762,10 +23762,10 @@
         <v>340</v>
       </c>
       <c r="N292" t="n">
-        <v>2937</v>
+        <v>2917</v>
       </c>
       <c r="O292" t="n">
-        <v>1914</v>
+        <v>1934</v>
       </c>
       <c r="P292" t="n">
         <v>0</v>
@@ -23777,19 +23777,19 @@
         <v>9760</v>
       </c>
       <c r="S292" t="n">
-        <v>-4646</v>
+        <v>-4626</v>
       </c>
       <c r="T292" t="n">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="U292" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="V292" t="n">
-        <v>-5507</v>
+        <v>-5496</v>
       </c>
       <c r="W292" t="n">
-        <v>-287.7</v>
+        <v>-284.2</v>
       </c>
       <c r="X292" t="inlineStr">
         <is>
@@ -23841,13 +23841,13 @@
         <v>0</v>
       </c>
       <c r="M293" t="n">
-        <v>11360</v>
+        <v>11339</v>
       </c>
       <c r="N293" t="n">
-        <v>13818</v>
+        <v>13777</v>
       </c>
       <c r="O293" t="n">
-        <v>-13818</v>
+        <v>-13777</v>
       </c>
       <c r="P293" t="n">
         <v>8553</v>
@@ -23859,16 +23859,16 @@
         <v>17660</v>
       </c>
       <c r="S293" t="n">
-        <v>-40031</v>
+        <v>-39990</v>
       </c>
       <c r="T293" t="n">
-        <v>-4145</v>
+        <v>-4133</v>
       </c>
       <c r="U293" t="n">
-        <v>-2073</v>
+        <v>-2067</v>
       </c>
       <c r="V293" t="n">
-        <v>-33813</v>
+        <v>-33790</v>
       </c>
       <c r="X293" t="inlineStr">
         <is>
@@ -23923,10 +23923,10 @@
         <v>8451</v>
       </c>
       <c r="N294" t="n">
-        <v>11332</v>
+        <v>11312</v>
       </c>
       <c r="O294" t="n">
-        <v>-11332</v>
+        <v>-11312</v>
       </c>
       <c r="P294" t="n">
         <v>1000</v>
@@ -23938,16 +23938,16 @@
         <v>13482</v>
       </c>
       <c r="S294" t="n">
-        <v>-23115</v>
+        <v>-23095</v>
       </c>
       <c r="T294" t="n">
-        <v>-3400</v>
+        <v>-3394</v>
       </c>
       <c r="U294" t="n">
-        <v>-1700</v>
+        <v>-1697</v>
       </c>
       <c r="V294" t="n">
-        <v>-18016</v>
+        <v>-18005</v>
       </c>
       <c r="X294" t="inlineStr">
         <is>
@@ -24104,16 +24104,16 @@
         <v>757</v>
       </c>
       <c r="L297" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M297" t="n">
         <v>2961</v>
       </c>
       <c r="N297" t="n">
-        <v>20974</v>
+        <v>20985</v>
       </c>
       <c r="O297" t="n">
-        <v>11926</v>
+        <v>11915</v>
       </c>
       <c r="P297" t="n">
         <v>0</v>
@@ -24125,16 +24125,16 @@
         <v>3744</v>
       </c>
       <c r="S297" t="n">
-        <v>8182</v>
+        <v>8171</v>
       </c>
       <c r="T297" t="n">
-        <v>3578</v>
+        <v>3574</v>
       </c>
       <c r="U297" t="n">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="V297" t="n">
-        <v>2815</v>
+        <v>2809</v>
       </c>
       <c r="W297" t="n">
         <v>23.6</v>
@@ -24260,16 +24260,16 @@
         <v>711</v>
       </c>
       <c r="L299" t="n">
-        <v>0</v>
+        <v>1760</v>
       </c>
       <c r="M299" t="n">
         <v>2781</v>
       </c>
       <c r="N299" t="n">
-        <v>21320</v>
+        <v>21300</v>
       </c>
       <c r="O299" t="n">
-        <v>9580</v>
+        <v>9600</v>
       </c>
       <c r="P299" t="n">
         <v>0</v>
@@ -24281,19 +24281,19 @@
         <v>3744</v>
       </c>
       <c r="S299" t="n">
-        <v>6106</v>
+        <v>6126</v>
       </c>
       <c r="T299" t="n">
-        <v>2874</v>
+        <v>2880</v>
       </c>
       <c r="U299" t="n">
-        <v>1437</v>
+        <v>1440</v>
       </c>
       <c r="V299" t="n">
-        <v>1795</v>
+        <v>1806</v>
       </c>
       <c r="W299" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="X299" t="inlineStr"/>
     </row>
@@ -24494,16 +24494,16 @@
         <v>711</v>
       </c>
       <c r="L302" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M302" t="n">
         <v>0</v>
       </c>
       <c r="N302" t="n">
-        <v>16342</v>
+        <v>16351</v>
       </c>
       <c r="O302" t="n">
-        <v>14558</v>
+        <v>14549</v>
       </c>
       <c r="P302" t="n">
         <v>0</v>
@@ -24515,16 +24515,16 @@
         <v>3744</v>
       </c>
       <c r="S302" t="n">
-        <v>10814</v>
+        <v>10805</v>
       </c>
       <c r="T302" t="n">
-        <v>4367</v>
+        <v>4365</v>
       </c>
       <c r="U302" t="n">
-        <v>2184</v>
+        <v>2182</v>
       </c>
       <c r="V302" t="n">
-        <v>4263</v>
+        <v>4258</v>
       </c>
       <c r="W302" t="n">
         <v>29.3</v>
@@ -24572,16 +24572,16 @@
         <v>688</v>
       </c>
       <c r="L303" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M303" t="n">
         <v>0</v>
       </c>
       <c r="N303" t="n">
-        <v>18851</v>
+        <v>18861</v>
       </c>
       <c r="O303" t="n">
-        <v>11049</v>
+        <v>11039</v>
       </c>
       <c r="P303" t="n">
         <v>0</v>
@@ -24593,19 +24593,19 @@
         <v>3230</v>
       </c>
       <c r="S303" t="n">
-        <v>7819</v>
+        <v>7809</v>
       </c>
       <c r="T303" t="n">
-        <v>3315</v>
+        <v>3312</v>
       </c>
       <c r="U303" t="n">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="V303" t="n">
-        <v>2847</v>
+        <v>2841</v>
       </c>
       <c r="W303" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="X303" t="inlineStr"/>
     </row>
@@ -24812,10 +24812,10 @@
         <v>1953</v>
       </c>
       <c r="N306" t="n">
-        <v>17103</v>
+        <v>17083</v>
       </c>
       <c r="O306" t="n">
-        <v>10797</v>
+        <v>10817</v>
       </c>
       <c r="P306" t="n">
         <v>3556</v>
@@ -24827,19 +24827,19 @@
         <v>3230</v>
       </c>
       <c r="S306" t="n">
-        <v>4011</v>
+        <v>4031</v>
       </c>
       <c r="T306" t="n">
-        <v>3239</v>
+        <v>3245</v>
       </c>
       <c r="U306" t="n">
-        <v>1620</v>
+        <v>1623</v>
       </c>
       <c r="V306" t="n">
-        <v>-848</v>
+        <v>-837</v>
       </c>
       <c r="W306" t="n">
-        <v>-7.9</v>
+        <v>-7.7</v>
       </c>
       <c r="X306" t="inlineStr">
         <is>
@@ -24888,16 +24888,16 @@
         <v>688</v>
       </c>
       <c r="L307" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M307" t="n">
         <v>0</v>
       </c>
       <c r="N307" t="n">
-        <v>2083</v>
+        <v>2093</v>
       </c>
       <c r="O307" t="n">
-        <v>-2083</v>
+        <v>-2093</v>
       </c>
       <c r="P307" t="n">
         <v>0</v>
@@ -24909,16 +24909,16 @@
         <v>3230</v>
       </c>
       <c r="S307" t="n">
-        <v>-5313</v>
+        <v>-5323</v>
       </c>
       <c r="T307" t="n">
-        <v>-625</v>
+        <v>-628</v>
       </c>
       <c r="U307" t="n">
-        <v>-312</v>
+        <v>-314</v>
       </c>
       <c r="V307" t="n">
-        <v>-4376</v>
+        <v>-4381</v>
       </c>
       <c r="X307" t="inlineStr"/>
     </row>
@@ -24952,19 +24952,19 @@
         <v>0</v>
       </c>
       <c r="K308" s="3" t="n">
-        <v>637464</v>
+        <v>639043</v>
       </c>
       <c r="L308" s="3" t="n">
-        <v>148256</v>
+        <v>69430</v>
       </c>
       <c r="M308" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N308" s="3" t="n">
-        <v>785720</v>
+        <v>708473</v>
       </c>
       <c r="O308" s="3" t="n">
-        <v>-785720</v>
+        <v>-708473</v>
       </c>
       <c r="P308" s="3" t="n">
         <v>117826</v>
@@ -24976,16 +24976,16 @@
         <v>0</v>
       </c>
       <c r="S308" s="3" t="n">
-        <v>-777834</v>
+        <v>-700587</v>
       </c>
       <c r="T308" s="3" t="n">
-        <v>-235716</v>
+        <v>-212542</v>
       </c>
       <c r="U308" s="3" t="n">
-        <v>-117858</v>
+        <v>-106271</v>
       </c>
       <c r="V308" s="3" t="n">
-        <v>-424260</v>
+        <v>-381774</v>
       </c>
       <c r="W308" s="3" t="n"/>
       <c r="X308" s="3" t="inlineStr"/>
@@ -25020,19 +25020,19 @@
         <v>11781</v>
       </c>
       <c r="K309" s="4" t="n">
-        <v>1080956</v>
+        <v>1082535</v>
       </c>
       <c r="L309" s="4" t="n">
         <v>148256</v>
       </c>
       <c r="M309" s="4" t="n">
-        <v>1720769</v>
+        <v>1719190</v>
       </c>
       <c r="N309" s="4" t="n">
-        <v>11607573</v>
+        <v>11526448</v>
       </c>
       <c r="O309" s="4" t="n">
-        <v>5628734</v>
+        <v>5709859</v>
       </c>
       <c r="P309" s="4" t="n">
         <v>720903</v>
@@ -25044,19 +25044,19 @@
         <v>3075163</v>
       </c>
       <c r="S309" s="4" t="n">
-        <v>2557956</v>
+        <v>2639081</v>
       </c>
       <c r="T309" s="4" t="n">
-        <v>1688620</v>
+        <v>1712958</v>
       </c>
       <c r="U309" s="4" t="n">
-        <v>844310</v>
+        <v>856479</v>
       </c>
       <c r="V309" s="4" t="n">
-        <v>25026</v>
+        <v>69644</v>
       </c>
       <c r="W309" s="4" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="X309" s="4" t="inlineStr"/>
     </row>

--- a/analytics-mvp/exports/orders_analytics_2026-07.xlsx
+++ b/analytics-mvp/exports/orders_analytics_2026-07.xlsx
@@ -24955,16 +24955,16 @@
         <v>639043</v>
       </c>
       <c r="L308" s="3" t="n">
-        <v>69430</v>
+        <v>18</v>
       </c>
       <c r="M308" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N308" s="3" t="n">
-        <v>708473</v>
+        <v>639061</v>
       </c>
       <c r="O308" s="3" t="n">
-        <v>-708473</v>
+        <v>-639061</v>
       </c>
       <c r="P308" s="3" t="n">
         <v>117826</v>
@@ -24976,16 +24976,16 @@
         <v>0</v>
       </c>
       <c r="S308" s="3" t="n">
-        <v>-700587</v>
+        <v>-631175</v>
       </c>
       <c r="T308" s="3" t="n">
-        <v>-212542</v>
+        <v>-191718</v>
       </c>
       <c r="U308" s="3" t="n">
-        <v>-106271</v>
+        <v>-95859</v>
       </c>
       <c r="V308" s="3" t="n">
-        <v>-381774</v>
+        <v>-343598</v>
       </c>
       <c r="W308" s="3" t="n"/>
       <c r="X308" s="3" t="inlineStr"/>
@@ -25023,16 +25023,16 @@
         <v>1082535</v>
       </c>
       <c r="L309" s="4" t="n">
-        <v>148256</v>
+        <v>78844</v>
       </c>
       <c r="M309" s="4" t="n">
         <v>1719190</v>
       </c>
       <c r="N309" s="4" t="n">
-        <v>11526448</v>
+        <v>11457036</v>
       </c>
       <c r="O309" s="4" t="n">
-        <v>5709859</v>
+        <v>5779271</v>
       </c>
       <c r="P309" s="4" t="n">
         <v>720903</v>
@@ -25044,19 +25044,19 @@
         <v>3075163</v>
       </c>
       <c r="S309" s="4" t="n">
-        <v>2639081</v>
+        <v>2708493</v>
       </c>
       <c r="T309" s="4" t="n">
-        <v>1712958</v>
+        <v>1733781</v>
       </c>
       <c r="U309" s="4" t="n">
-        <v>856479</v>
+        <v>866891</v>
       </c>
       <c r="V309" s="4" t="n">
-        <v>69644</v>
+        <v>107821</v>
       </c>
       <c r="W309" s="4" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="X309" s="4" t="inlineStr"/>
     </row>
